--- a/yandex-direct/audit/2026-09-28-deystviya-po-gruppam.xlsx
+++ b/yandex-direct/audit/2026-09-28-deystviya-po-gruppam.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2345" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2334" uniqueCount="655">
   <si>
     <t>Этап</t>
   </si>
@@ -214,13 +214,13 @@
     <t>ДОБАВИТЬ ФРАЗЫ</t>
   </si>
   <si>
-    <t>Добавить фразы: «перегородка гармошка», «дверь гармошка», «двери гармошка на заказ», «межкомнатные перегородки гармошка»</t>
-  </si>
-  <si>
-    <t>Принимающий ключ для спроса «гармошка» до паузы гармошек в СЧ. Сейчас все ключи НЧ требуют слово «складные», а 99% запросов СЧ-гармошек его не содержат (замечание ФЕНИКСА).</t>
-  </si>
-  <si>
-    <t>14.10: показы по новым фразам &gt; 0, CPC не выше 150 ₽</t>
+    <t>Добавить фразы (все со словом «гармошка», разделение со «Складными» сохраняется): [перегородка] [гармошка] / [перегородки] [гармошка] [межкомнатные] / [дверь] [гармошка] / [дверь] [гармошка] [заказ]</t>
+  </si>
+  <si>
+    <t>Сейчас фраза группы [складные] [перегородки] [гармошка] дала 7 кликов из 120, остальные 113 - автотаргетинг. Лиды пришли по «дверь гармошка на заказ», «перегородка гармошка», «межкомнатные перегородки гармошка». Фразы переводят этот спрос из автотаргетинга в управляемые ключи. Базовая «Складные» 5774336419 их не заберёт: у неё минус-слово «гармошка» на группе. Это и принимающий ключ перед паузой гармошек в СЧ.</t>
+  </si>
+  <si>
+    <t>14.10: клики по новым фразам &gt; 0, доля автотаргетинга в группе &lt; 70%, CPC ≤ 150 ₽</t>
   </si>
   <si>
     <t>[складные] [перегородки] [гармошка]</t>
@@ -238,10 +238,10 @@
     <t>Остановить после добавления фраз в НЧ 5774336420</t>
   </si>
   <si>
-    <t>Семейство СЧ: 18 644 ₽, 3 лида (по меткам), CPL 6 215 ₽ против 2 417 ₽ у НЧ «Складные». Половина кликов дублирует те же запросы в НЧ. Спрос уходит в НЧ, где он дешевле. У группы есть лид - остановка как дубль, спрос забирает НЧ.</t>
-  </si>
-  <si>
-    <t>14.10 и 04.11: лиды «гармошка» в НЧ не ниже, чем было суммарно в НЧ+СЧ за те же недели</t>
+    <t>Один и тот же спрос «гармошка» покупают две РК: запросы с «гармошка» в НЧ - 129 визитов, 5 лидов; в СЧ - 142 визита, 2 лида. В СЧ-гармошках слово «складные» есть лишь в 2 кликах из 179 - это не складные, а именно гармошки и двери-гармошки. Оставляем спрос в НЧ, где он конвертит лучше. У группы есть лид - остановка как дубль, спрос забирает НЧ 5774336420.</t>
+  </si>
+  <si>
+    <t>14.10 и 04.11: лиды по «гармошка» в НЧ не ниже, чем было суммарно в НЧ+СЧ</t>
   </si>
   <si>
     <t>[перегородки] [гармошка] -заказ -зонирования -купить -межкомнатная -складные -стеклянные</t>
@@ -253,7 +253,7 @@
     <t>Перегородки-гармошки | Купить</t>
   </si>
   <si>
-    <t>Семейство СЧ: 18 644 ₽, 3 лида (по меткам), CPL 6 215 ₽ против 2 417 ₽ у НЧ «Складные». Половина кликов дублирует те же запросы в НЧ. Спрос уходит в НЧ, где он дешевле.</t>
+    <t>Один и тот же спрос «гармошка» покупают две РК: запросы с «гармошка» в НЧ - 129 визитов, 5 лидов; в СЧ - 142 визита, 2 лида. В СЧ-гармошках слово «складные» есть лишь в 2 кликах из 179 - это не складные, а именно гармошки и двери-гармошки. Оставляем спрос в НЧ, где он конвертит лучше.</t>
   </si>
   <si>
     <t>[перегородка] [гармошка] [купить]</t>
@@ -295,352 +295,346 @@
     <t>[перегородка] [книжка]</t>
   </si>
   <si>
+    <t>07.10</t>
+  </si>
+  <si>
+    <t>5774336417</t>
+  </si>
+  <si>
+    <t>Складные перегородки | Заказ</t>
+  </si>
+  <si>
+    <t>ВЫКЛЮЧИТЬ АВТОТАРГЕТИНГ</t>
+  </si>
+  <si>
+    <t>Выключить автотаргетинг в группе, фразу оставить (группу не останавливать)</t>
+  </si>
+  <si>
+    <t>Фраза группы ни разу не сработала, все клики - автотаргетинг, и он приводит сюда общие запросы базовой группы («складная перегородка», «межкомнатные перегородки складные»): 0 лидов. Без автотаргетинга группа ловит только свои «заказ / цена», остальное уходит в базовую 5774336419 (5 лидов, CPL 1 047). Разделение сохраняется, фразу базовой группы не трогаем.</t>
+  </si>
+  <si>
+    <t>14.10: у группы расход ≈ 0 или только запросы с «заказ / цена»; клики базовой 5774336419 выросли</t>
+  </si>
+  <si>
+    <t>[складные] [перегородки] [заказ]</t>
+  </si>
+  <si>
+    <t>5774336421</t>
+  </si>
+  <si>
+    <t>Складные перегородки | Цена</t>
+  </si>
+  <si>
+    <t>[складные] [перегородки] [цена]</t>
+  </si>
+  <si>
+    <t>5774336418</t>
+  </si>
+  <si>
+    <t>Складные перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>Остановить</t>
+  </si>
+  <si>
+    <t>Интент «зонирование»: 12 кликов, 579 ₽, 0 лидов. По всем РК зонирование - худший кластер (CR 1,1%).</t>
+  </si>
+  <si>
+    <t>04.11: лиды семейства «Складные» не упали</t>
+  </si>
+  <si>
+    <t>[складные] [перегородки] [зонирования]</t>
+  </si>
+  <si>
+    <t>07.10 (до пауз в ВЧ)</t>
+  </si>
+  <si>
+    <t>5774336335</t>
+  </si>
+  <si>
+    <t>Интерьерные перегородки | Стеклянные</t>
+  </si>
+  <si>
+    <t>Добавить фразы: «[стеклянные] [перегородки]», «стеклянная перегородка в комнату», «стеклянные перегородки на заказ»</t>
+  </si>
+  <si>
+    <t>Принимающий ключ для общих стеклянных запросов: сейчас в СЧ нет ключа под «стеклянные перегородки», закрепление держится только на автотаргетинге (замечание ФЕНИКСА). Группа даёт 13 лидов при CPL 2 032 ₽.</t>
+  </si>
+  <si>
+    <t>14.10: показы по новым фразам, CPL группы не выше 2 500 ₽</t>
+  </si>
+  <si>
+    <t>[интерьерные] [стеклянные] [перегородки]</t>
+  </si>
+  <si>
+    <t>5774336333</t>
+  </si>
+  <si>
+    <t>Интерьерные перегородки | Купить</t>
+  </si>
+  <si>
+    <t>ДОБАВИТЬ ФРАЗУ</t>
+  </si>
+  <si>
+    <t>Добавить фразу «[межкомнатные] [перегородки]»</t>
+  </si>
+  <si>
+    <t>Запрос «межкомнатные перегородки» дал 2 лида именно в этой группе. Принимающий ключ перед паузой 8 групп «Межкомнатные» в ВЧ.</t>
+  </si>
+  <si>
+    <t>14.10: показы по фразе &gt; 0</t>
+  </si>
+  <si>
+    <t>[интерьерные] [перегородки] [купить]</t>
+  </si>
+  <si>
+    <t>07.10 (после фраз в СЧ)</t>
+  </si>
+  <si>
+    <t>ВЧ</t>
+  </si>
+  <si>
+    <t>712877513</t>
+  </si>
+  <si>
+    <t>5774336213</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки</t>
+  </si>
+  <si>
+    <t>Остановить после добавления фраз в СЧ 5774336335 и «Купить»</t>
+  </si>
+  <si>
+    <t>Семейство «Межкомнатные» в ВЧ: 53 клика, 6 680 ₽, 0 лидов. Тот же спрос дал 5 лидов в СЧ. ВЧ упирается в НБ - высвобожденные деньги пойдут раздвижным и дверям.</t>
+  </si>
+  <si>
+    <t>14.10: лиды СЧ по «стеклянным» и «межкомнатным» не упали</t>
+  </si>
+  <si>
+    <t>[межкомнатные] [перегородки] -гармошка -дверью -заказ -зеркальные -каскадная -квартиру -купить -металлические -москве -производителя -раздвижные -стеклянные -цена</t>
+  </si>
+  <si>
+    <t>5774336214</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки | Заказ</t>
+  </si>
+  <si>
+    <t>[межкомнатные] [перегородки] [заказ]</t>
+  </si>
+  <si>
+    <t>5774336215</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки | Купить</t>
+  </si>
+  <si>
+    <t>[межкомнатные] [перегородки] [купить]</t>
+  </si>
+  <si>
+    <t>5774336216</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки | Цена</t>
+  </si>
+  <si>
+    <t>[межкомнатные] [перегородки] [цена]</t>
+  </si>
+  <si>
+    <t>5774336217</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки | Москве</t>
+  </si>
+  <si>
+    <t>[межкомнатные] [перегородки] [москве]</t>
+  </si>
+  <si>
+    <t>5774336218</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки | Производителя</t>
+  </si>
+  <si>
+    <t>[межкомнатные] [перегородки] [производителя]</t>
+  </si>
+  <si>
+    <t>5774336219</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки | Квартиру</t>
+  </si>
+  <si>
+    <t>[межкомнатные] [перегородки] [квартиру]</t>
+  </si>
+  <si>
+    <t>5774336220</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки | Стеклянные</t>
+  </si>
+  <si>
+    <t>[стеклянные] [межкомнатные] [перегородки]</t>
+  </si>
+  <si>
+    <t>5774336274</t>
+  </si>
+  <si>
+    <t>Стеклянные перегородки</t>
+  </si>
+  <si>
+    <t>База ВЧ: 20 кликов, 2 998 ₽, 0 лидов, отказы 68%, позиция 4. Этот спрос конвертит в СЧ «Интерьерные | Стеклянные» (13 лидов).</t>
+  </si>
+  <si>
+    <t>[стеклянные] [перегородки] -арочные -гармошка -гостиной -дверью -дизайнерские -заказ -зонирования -интерьерные -квартиру -купить -кухни -лофт -межкомнатные -москве -производителя -раздвижные -распашные -складные -студии -телескопические -цена</t>
+  </si>
+  <si>
+    <t>5774336360</t>
+  </si>
+  <si>
+    <t>Дизайнерские перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>Интент «зонирование»: по реальным запросам 380 визитов, 4 лида (CR 1,1%) - худший кластер. У этой группы 0 лидов. Группы зонирования с лидами оставлены.</t>
+  </si>
+  <si>
+    <t>04.11: лиды РК не упали</t>
+  </si>
+  <si>
+    <t>[дизайнерские] [перегородки] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336370</t>
+  </si>
+  <si>
+    <t>Зеркальные перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>[зеркальные] [перегородки] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336382</t>
+  </si>
+  <si>
+    <t>Матовые перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>[матовые] [перегородки] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336407</t>
+  </si>
+  <si>
+    <t>Каскадные перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>[каскадная] [перегородка] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336430</t>
+  </si>
+  <si>
+    <t>Стальные перегородки | Металлические Зонирования</t>
+  </si>
+  <si>
+    <t>[металлические] [перегородки] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336436</t>
+  </si>
+  <si>
+    <t>Стационарные перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>[стационарная] [перегородка] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336449</t>
+  </si>
+  <si>
+    <t>Перегородки для гостиной | Зонирования</t>
+  </si>
+  <si>
+    <t>[перегородки] [для] [зонирования] [гостиной]</t>
+  </si>
+  <si>
+    <t>5774336228</t>
+  </si>
+  <si>
+    <t>Перегородки для зонирования комнаты | Пространства</t>
+  </si>
+  <si>
+    <t>[перегородки] [зонирования] [пространства]</t>
+  </si>
+  <si>
+    <t>5774336255</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>[раздвижные] [перегородки] [зонирования] -комнаты -межкомнатные</t>
+  </si>
+  <si>
+    <t>5774336257</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Межкомнатные Зонирования</t>
+  </si>
+  <si>
+    <t>[раздвижные] [межкомнатные] [перегородки] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336377</t>
+  </si>
+  <si>
+    <t>Перегородки стекло металл</t>
+  </si>
+  <si>
+    <t>КОРРЕКТИРОВКА −30%</t>
+  </si>
+  <si>
+    <t>Корректировка ставки −30% на смартфоны, ПК, планшеты (вместо паузы)</t>
+  </si>
+  <si>
+    <t>Вариант ФЕНИКСА вместо остановки: CR 3,4% (средний уровень), дорогой только клик - 223 ₽ против 119 ₽ по НЧ. Один из двух лидов - «стеклянные двери в москве на заказ». Снижаем цену клика, не теряя спрос.</t>
+  </si>
+  <si>
+    <t>21.10: CPC группы ≤ 170 ₽; если лидов 0 и расход &gt; 2 CPL - пауза</t>
+  </si>
+  <si>
+    <t>[перегородки] [стекло] [металл] -лофт</t>
+  </si>
+  <si>
+    <t>КОРРЕКТИРОВКА +40%</t>
+  </si>
+  <si>
+    <t>+40% на смартфоны, ПК, планшеты</t>
+  </si>
+  <si>
+    <t>13 лида, CPL 2032 ₽ (среднее 3622 ₽), объём трафика 69 (цель 85+), премиум 42% показов, позиция 2.6. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
+  </si>
+  <si>
+    <t>14.10: объём ≥ 85, CPC рост ≤ 25%; 04.11: CPL группы ≤ 1,3× текущего</t>
+  </si>
+  <si>
     <t>5774336419</t>
   </si>
   <si>
     <t>Складные перегородки</t>
   </si>
   <si>
-    <t>ПРАВКА ФРАЗЫ</t>
-  </si>
-  <si>
-    <t>В фразе «[складные] [перегородки] -гармошка -заказ -зонирования -москве -стеклянные -цена» удалить минус-слова -заказ -цена -зонирования (оставить -гармошка -москве -стеклянные)</t>
-  </si>
-  <si>
-    <t>Базовая группа с лучшим CPL семейства (5 лидов по меткам). Её подгруппы Заказ / Цена / Зонирования останавливаются, их запросы должны вернуться сюда.</t>
-  </si>
-  <si>
-    <t>14.10: клики базовой группы выросли, CPC не выше 130 ₽</t>
+    <t>КОРРЕКТИРОВКА +25%</t>
+  </si>
+  <si>
+    <t>+25% на смартфоны, ПК, планшеты</t>
+  </si>
+  <si>
+    <t>5 лида, CPL 1047 ₽ (среднее 3622 ₽), объём трафика 80 (цель 85+), премиум 64% показов, позиция 2.9. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
   </si>
   <si>
     <t>[складные] [перегородки] -гармошка -заказ -зонирования -москве -стеклянные -цена</t>
-  </si>
-  <si>
-    <t>07.10 (после правки фразы)</t>
-  </si>
-  <si>
-    <t>5774336417</t>
-  </si>
-  <si>
-    <t>Складные перегородки | Заказ</t>
-  </si>
-  <si>
-    <t>Остановить после правки фразы базовой группы 5774336419</t>
-  </si>
-  <si>
-    <t>Перехватывает запросы базовой группы, 0 лидов. Запросы вернутся в базовую группу без минус-слов.</t>
-  </si>
-  <si>
-    <t>14.10: базовая группа 5774336419 получает эти запросы</t>
-  </si>
-  <si>
-    <t>[складные] [перегородки] [заказ]</t>
-  </si>
-  <si>
-    <t>5774336421</t>
-  </si>
-  <si>
-    <t>Складные перегородки | Цена</t>
-  </si>
-  <si>
-    <t>[складные] [перегородки] [цена]</t>
-  </si>
-  <si>
-    <t>5774336418</t>
-  </si>
-  <si>
-    <t>Складные перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>[складные] [перегородки] [зонирования]</t>
-  </si>
-  <si>
-    <t>07.10 (до пауз в ВЧ)</t>
-  </si>
-  <si>
-    <t>5774336335</t>
-  </si>
-  <si>
-    <t>Интерьерные перегородки | Стеклянные</t>
-  </si>
-  <si>
-    <t>Добавить фразы: «[стеклянные] [перегородки]», «стеклянная перегородка в комнату», «стеклянные перегородки на заказ»</t>
-  </si>
-  <si>
-    <t>Принимающий ключ для общих стеклянных запросов: сейчас в СЧ нет ключа под «стеклянные перегородки», закрепление держится только на автотаргетинге (замечание ФЕНИКСА). Группа даёт 13 лидов при CPL 2 032 ₽.</t>
-  </si>
-  <si>
-    <t>14.10: показы по новым фразам, CPL группы не выше 2 500 ₽</t>
-  </si>
-  <si>
-    <t>[интерьерные] [стеклянные] [перегородки]</t>
-  </si>
-  <si>
-    <t>5774336333</t>
-  </si>
-  <si>
-    <t>Интерьерные перегородки | Купить</t>
-  </si>
-  <si>
-    <t>ДОБАВИТЬ ФРАЗУ</t>
-  </si>
-  <si>
-    <t>Добавить фразу «[межкомнатные] [перегородки]»</t>
-  </si>
-  <si>
-    <t>Запрос «межкомнатные перегородки» дал 2 лида именно в этой группе. Принимающий ключ перед паузой 8 групп «Межкомнатные» в ВЧ.</t>
-  </si>
-  <si>
-    <t>14.10: показы по фразе &gt; 0</t>
-  </si>
-  <si>
-    <t>[интерьерные] [перегородки] [купить]</t>
-  </si>
-  <si>
-    <t>07.10 (после фраз в СЧ)</t>
-  </si>
-  <si>
-    <t>ВЧ</t>
-  </si>
-  <si>
-    <t>712877513</t>
-  </si>
-  <si>
-    <t>5774336213</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки</t>
-  </si>
-  <si>
-    <t>Остановить после добавления фраз в СЧ 5774336335 и «Купить»</t>
-  </si>
-  <si>
-    <t>Семейство «Межкомнатные» в ВЧ: 53 клика, 6 680 ₽, 0 лидов. Тот же спрос дал 5 лидов в СЧ. ВЧ упирается в НБ - высвобожденные деньги пойдут раздвижным и дверям.</t>
-  </si>
-  <si>
-    <t>14.10: лиды СЧ по «стеклянным» и «межкомнатным» не упали</t>
-  </si>
-  <si>
-    <t>[межкомнатные] [перегородки] -гармошка -дверью -заказ -зеркальные -каскадная -квартиру -купить -металлические -москве -производителя -раздвижные -стеклянные -цена</t>
-  </si>
-  <si>
-    <t>5774336214</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки | Заказ</t>
-  </si>
-  <si>
-    <t>[межкомнатные] [перегородки] [заказ]</t>
-  </si>
-  <si>
-    <t>5774336215</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки | Купить</t>
-  </si>
-  <si>
-    <t>[межкомнатные] [перегородки] [купить]</t>
-  </si>
-  <si>
-    <t>5774336216</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки | Цена</t>
-  </si>
-  <si>
-    <t>[межкомнатные] [перегородки] [цена]</t>
-  </si>
-  <si>
-    <t>5774336217</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки | Москве</t>
-  </si>
-  <si>
-    <t>[межкомнатные] [перегородки] [москве]</t>
-  </si>
-  <si>
-    <t>5774336218</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки | Производителя</t>
-  </si>
-  <si>
-    <t>[межкомнатные] [перегородки] [производителя]</t>
-  </si>
-  <si>
-    <t>5774336219</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки | Квартиру</t>
-  </si>
-  <si>
-    <t>[межкомнатные] [перегородки] [квартиру]</t>
-  </si>
-  <si>
-    <t>5774336220</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки | Стеклянные</t>
-  </si>
-  <si>
-    <t>[стеклянные] [межкомнатные] [перегородки]</t>
-  </si>
-  <si>
-    <t>5774336274</t>
-  </si>
-  <si>
-    <t>Стеклянные перегородки</t>
-  </si>
-  <si>
-    <t>База ВЧ: 20 кликов, 2 998 ₽, 0 лидов, отказы 68%, позиция 4. Этот спрос конвертит в СЧ «Интерьерные | Стеклянные» (13 лидов).</t>
-  </si>
-  <si>
-    <t>[стеклянные] [перегородки] -арочные -гармошка -гостиной -дверью -дизайнерские -заказ -зонирования -интерьерные -квартиру -купить -кухни -лофт -межкомнатные -москве -производителя -раздвижные -распашные -складные -студии -телескопические -цена</t>
-  </si>
-  <si>
-    <t>07.10</t>
-  </si>
-  <si>
-    <t>5774336360</t>
-  </si>
-  <si>
-    <t>Дизайнерские перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>Остановить</t>
-  </si>
-  <si>
-    <t>Интент «зонирование»: по реальным запросам 380 визитов, 4 лида (CR 1,1%) - худший кластер. У этой группы 0 лидов. Группы зонирования с лидами оставлены.</t>
-  </si>
-  <si>
-    <t>04.11: лиды РК не упали</t>
-  </si>
-  <si>
-    <t>[дизайнерские] [перегородки] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336370</t>
-  </si>
-  <si>
-    <t>Зеркальные перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>[зеркальные] [перегородки] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336382</t>
-  </si>
-  <si>
-    <t>Матовые перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>[матовые] [перегородки] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336407</t>
-  </si>
-  <si>
-    <t>Каскадные перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>[каскадная] [перегородка] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336430</t>
-  </si>
-  <si>
-    <t>Стальные перегородки | Металлические Зонирования</t>
-  </si>
-  <si>
-    <t>[металлические] [перегородки] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336436</t>
-  </si>
-  <si>
-    <t>Стационарные перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>[стационарная] [перегородка] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336449</t>
-  </si>
-  <si>
-    <t>Перегородки для гостиной | Зонирования</t>
-  </si>
-  <si>
-    <t>[перегородки] [для] [зонирования] [гостиной]</t>
-  </si>
-  <si>
-    <t>5774336228</t>
-  </si>
-  <si>
-    <t>Перегородки для зонирования комнаты | Пространства</t>
-  </si>
-  <si>
-    <t>[перегородки] [зонирования] [пространства]</t>
-  </si>
-  <si>
-    <t>5774336255</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>[раздвижные] [перегородки] [зонирования] -комнаты -межкомнатные</t>
-  </si>
-  <si>
-    <t>5774336257</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Межкомнатные Зонирования</t>
-  </si>
-  <si>
-    <t>[раздвижные] [межкомнатные] [перегородки] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336377</t>
-  </si>
-  <si>
-    <t>Перегородки стекло металл</t>
-  </si>
-  <si>
-    <t>КОРРЕКТИРОВКА −30%</t>
-  </si>
-  <si>
-    <t>Корректировка ставки −30% на смартфоны, ПК, планшеты (вместо паузы)</t>
-  </si>
-  <si>
-    <t>Вариант ФЕНИКСА вместо остановки: CR 3,4% (средний уровень), дорогой только клик - 223 ₽ против 119 ₽ по НЧ. Один из двух лидов - «стеклянные двери в москве на заказ». Снижаем цену клика, не теряя спрос.</t>
-  </si>
-  <si>
-    <t>21.10: CPC группы ≤ 170 ₽; если лидов 0 и расход &gt; 2 CPL - пауза</t>
-  </si>
-  <si>
-    <t>[перегородки] [стекло] [металл] -лофт</t>
-  </si>
-  <si>
-    <t>КОРРЕКТИРОВКА +40%</t>
-  </si>
-  <si>
-    <t>+40% на смартфоны, ПК, планшеты</t>
-  </si>
-  <si>
-    <t>13 лида, CPL 2032 ₽ (среднее 3622 ₽), объём трафика 69 (цель 85+), премиум 42% показов, позиция 2.6. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
-  </si>
-  <si>
-    <t>14.10: объём ≥ 85, CPC рост ≤ 25%; 04.11: CPL группы ≤ 1,3× текущего</t>
-  </si>
-  <si>
-    <t>КОРРЕКТИРОВКА +25%</t>
-  </si>
-  <si>
-    <t>+25% на смартфоны, ПК, планшеты</t>
-  </si>
-  <si>
-    <t>5 лида, CPL 1047 ₽ (среднее 3622 ₽), объём трафика 80 (цель 85+), премиум 64% показов, позиция 2.9. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
   </si>
   <si>
     <t>4 лида, CPL 1361 ₽ (среднее 3622 ₽), объём трафика 77 (цель 85+), премиум 37% показов, позиция 2. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
@@ -2416,7 +2410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S56"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3563,7 +3557,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>61</v>
@@ -3572,46 +3566,46 @@
         <v>62</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G20" s="4" t="s">
         <v>95</v>
       </c>
+      <c r="G20" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="H20" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I20" s="2">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="J20" s="2">
-        <v>5233</v>
+        <v>1774</v>
       </c>
       <c r="K20" s="2">
-        <v>5</v>
-      </c>
-      <c r="L20" s="2">
-        <v>1047</v>
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="M20" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="N20" s="2">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="O20" s="2">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S20" s="2" t="s">
         <v>26</v>
@@ -3622,7 +3616,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>61</v>
@@ -3636,41 +3630,41 @@
       <c r="F21" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>24</v>
+      <c r="G21" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I21" s="2">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2">
+        <v>531</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="2">
+        <v>86</v>
+      </c>
+      <c r="N21" s="2">
+        <v>84</v>
+      </c>
+      <c r="O21" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="R21" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="I21" s="2">
-        <v>20</v>
-      </c>
-      <c r="J21" s="2">
-        <v>1774</v>
-      </c>
-      <c r="K21" s="2">
-        <v>0</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M21" s="2">
-        <v>88</v>
-      </c>
-      <c r="N21" s="2">
-        <v>79</v>
-      </c>
-      <c r="O21" s="2">
-        <v>2.7</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>26</v>
@@ -3681,7 +3675,7 @@
         <v>2</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>61</v>
@@ -3690,22 +3684,22 @@
         <v>62</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I22" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J22" s="2">
-        <v>531</v>
+        <v>579</v>
       </c>
       <c r="K22" s="2">
         <v>0</v>
@@ -3714,19 +3708,19 @@
         <v>26</v>
       </c>
       <c r="M22" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="N22" s="2">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="O22" s="2">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="R22" s="2" t="s">
         <v>109</v>
@@ -3740,55 +3734,55 @@
         <v>2</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>24</v>
+        <v>112</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="I23" s="2">
-        <v>12</v>
+        <v>135</v>
       </c>
       <c r="J23" s="2">
-        <v>579</v>
+        <v>26421</v>
       </c>
       <c r="K23" s="2">
-        <v>0</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>26</v>
+        <v>13</v>
+      </c>
+      <c r="L23" s="2">
+        <v>2032</v>
       </c>
       <c r="M23" s="2">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="N23" s="2">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="O23" s="2">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>26</v>
@@ -3799,7 +3793,7 @@
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>20</v>
@@ -3808,46 +3802,46 @@
         <v>21</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I24" s="2">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="J24" s="2">
-        <v>26421</v>
+        <v>5443</v>
       </c>
       <c r="K24" s="2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L24" s="2">
-        <v>2032</v>
+        <v>1361</v>
       </c>
       <c r="M24" s="2">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="N24" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="O24" s="2">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="S24" s="2" t="s">
         <v>26</v>
@@ -3858,55 +3852,55 @@
         <v>2</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="I25" s="2">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J25" s="2">
-        <v>5443</v>
+        <v>2468</v>
       </c>
       <c r="K25" s="2">
-        <v>4</v>
-      </c>
-      <c r="L25" s="2">
-        <v>1361</v>
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="M25" s="2">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="N25" s="2">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="O25" s="2">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="S25" s="2" t="s">
         <v>26</v>
@@ -3917,31 +3911,31 @@
         <v>2</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I26" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2">
-        <v>2468</v>
+        <v>192</v>
       </c>
       <c r="K26" s="2">
         <v>0</v>
@@ -3950,19 +3944,19 @@
         <v>26</v>
       </c>
       <c r="M26" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="N26" s="2">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="O26" s="2">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="R26" s="2" t="s">
         <v>135</v>
@@ -3976,13 +3970,13 @@
         <v>2</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>136</v>
@@ -3994,13 +3988,13 @@
         <v>24</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I27" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J27" s="2">
-        <v>192</v>
+        <v>1191</v>
       </c>
       <c r="K27" s="2">
         <v>0</v>
@@ -4009,19 +4003,19 @@
         <v>26</v>
       </c>
       <c r="M27" s="2">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="N27" s="2">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="O27" s="2">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>138</v>
@@ -4035,13 +4029,13 @@
         <v>2</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>139</v>
@@ -4053,13 +4047,13 @@
         <v>24</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I28" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J28" s="2">
-        <v>1191</v>
+        <v>965</v>
       </c>
       <c r="K28" s="2">
         <v>0</v>
@@ -4068,19 +4062,19 @@
         <v>26</v>
       </c>
       <c r="M28" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="N28" s="2">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="O28" s="2">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="R28" s="2" t="s">
         <v>141</v>
@@ -4094,13 +4088,13 @@
         <v>2</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>142</v>
@@ -4112,13 +4106,13 @@
         <v>24</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I29" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J29" s="2">
-        <v>965</v>
+        <v>410</v>
       </c>
       <c r="K29" s="2">
         <v>0</v>
@@ -4127,19 +4121,19 @@
         <v>26</v>
       </c>
       <c r="M29" s="2">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="N29" s="2">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="O29" s="2">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="R29" s="2" t="s">
         <v>144</v>
@@ -4153,13 +4147,13 @@
         <v>2</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>145</v>
@@ -4171,13 +4165,13 @@
         <v>24</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I30" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J30" s="2">
-        <v>410</v>
+        <v>23</v>
       </c>
       <c r="K30" s="2">
         <v>0</v>
@@ -4186,19 +4180,19 @@
         <v>26</v>
       </c>
       <c r="M30" s="2">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="N30" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="O30" s="2">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="R30" s="2" t="s">
         <v>147</v>
@@ -4212,13 +4206,13 @@
         <v>2</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>148</v>
@@ -4230,13 +4224,13 @@
         <v>24</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I31" s="2">
         <v>1</v>
       </c>
       <c r="J31" s="2">
-        <v>23</v>
+        <v>483</v>
       </c>
       <c r="K31" s="2">
         <v>0</v>
@@ -4245,19 +4239,19 @@
         <v>26</v>
       </c>
       <c r="M31" s="2">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="N31" s="2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="O31" s="2">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="R31" s="2" t="s">
         <v>150</v>
@@ -4271,13 +4265,13 @@
         <v>2</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>151</v>
@@ -4289,13 +4283,13 @@
         <v>24</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I32" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J32" s="2">
-        <v>483</v>
+        <v>949</v>
       </c>
       <c r="K32" s="2">
         <v>0</v>
@@ -4304,19 +4298,19 @@
         <v>26</v>
       </c>
       <c r="M32" s="2">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="N32" s="2">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="O32" s="2">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="R32" s="2" t="s">
         <v>153</v>
@@ -4330,13 +4324,13 @@
         <v>2</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>154</v>
@@ -4348,13 +4342,13 @@
         <v>24</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I33" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J33" s="2">
-        <v>949</v>
+        <v>2998</v>
       </c>
       <c r="K33" s="2">
         <v>0</v>
@@ -4363,22 +4357,22 @@
         <v>26</v>
       </c>
       <c r="M33" s="2">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N33" s="2">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="O33" s="2">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="S33" s="2" t="s">
         <v>26</v>
@@ -4389,31 +4383,31 @@
         <v>2</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="I34" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J34" s="2">
-        <v>2998</v>
+        <v>586</v>
       </c>
       <c r="K34" s="2">
         <v>0</v>
@@ -4422,22 +4416,22 @@
         <v>26</v>
       </c>
       <c r="M34" s="2">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="N34" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="O34" s="2">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="S34" s="2" t="s">
         <v>26</v>
@@ -4448,7 +4442,7 @@
         <v>2</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>61</v>
@@ -4457,22 +4451,22 @@
         <v>62</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="I35" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J35" s="2">
-        <v>586</v>
+        <v>609</v>
       </c>
       <c r="K35" s="2">
         <v>0</v>
@@ -4481,22 +4475,22 @@
         <v>26</v>
       </c>
       <c r="M35" s="2">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="N35" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="O35" s="2">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="P35" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="R35" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="S35" s="2" t="s">
         <v>26</v>
@@ -4507,7 +4501,7 @@
         <v>2</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>61</v>
@@ -4516,22 +4510,22 @@
         <v>62</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="I36" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J36" s="2">
-        <v>609</v>
+        <v>1338</v>
       </c>
       <c r="K36" s="2">
         <v>0</v>
@@ -4540,22 +4534,22 @@
         <v>26</v>
       </c>
       <c r="M36" s="2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N36" s="2">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="O36" s="2">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="S36" s="2" t="s">
         <v>26</v>
@@ -4566,7 +4560,7 @@
         <v>2</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>61</v>
@@ -4575,22 +4569,22 @@
         <v>62</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="I37" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J37" s="2">
-        <v>1338</v>
+        <v>432</v>
       </c>
       <c r="K37" s="2">
         <v>0</v>
@@ -4599,22 +4593,22 @@
         <v>26</v>
       </c>
       <c r="M37" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="N37" s="2">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="O37" s="2">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S37" s="2" t="s">
         <v>26</v>
@@ -4625,7 +4619,7 @@
         <v>2</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>61</v>
@@ -4634,22 +4628,22 @@
         <v>62</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="I38" s="2">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="J38" s="2">
-        <v>432</v>
+        <v>1803</v>
       </c>
       <c r="K38" s="2">
         <v>0</v>
@@ -4658,22 +4652,22 @@
         <v>26</v>
       </c>
       <c r="M38" s="2">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="N38" s="2">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="O38" s="2">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>26</v>
@@ -4684,7 +4678,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>61</v>
@@ -4693,22 +4687,22 @@
         <v>62</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="I39" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J39" s="2">
-        <v>1803</v>
+        <v>760</v>
       </c>
       <c r="K39" s="2">
         <v>0</v>
@@ -4717,22 +4711,22 @@
         <v>26</v>
       </c>
       <c r="M39" s="2">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N39" s="2">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="O39" s="2">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="S39" s="2" t="s">
         <v>26</v>
@@ -4743,7 +4737,7 @@
         <v>2</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>61</v>
@@ -4752,22 +4746,22 @@
         <v>62</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="I40" s="2">
         <v>5</v>
       </c>
       <c r="J40" s="2">
-        <v>760</v>
+        <v>481</v>
       </c>
       <c r="K40" s="2">
         <v>0</v>
@@ -4776,22 +4770,22 @@
         <v>26</v>
       </c>
       <c r="M40" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N40" s="2">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O40" s="2">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="S40" s="2" t="s">
         <v>26</v>
@@ -4802,31 +4796,31 @@
         <v>2</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>62</v>
+        <v>126</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="I41" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J41" s="2">
-        <v>481</v>
+        <v>231</v>
       </c>
       <c r="K41" s="2">
         <v>0</v>
@@ -4835,22 +4829,22 @@
         <v>26</v>
       </c>
       <c r="M41" s="2">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="N41" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O41" s="2">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="S41" s="2" t="s">
         <v>26</v>
@@ -4861,31 +4855,31 @@
         <v>2</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="I42" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J42" s="2">
-        <v>231</v>
+        <v>1650</v>
       </c>
       <c r="K42" s="2">
         <v>0</v>
@@ -4894,22 +4888,22 @@
         <v>26</v>
       </c>
       <c r="M42" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N42" s="2">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="O42" s="2">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="S42" s="2" t="s">
         <v>26</v>
@@ -4920,31 +4914,31 @@
         <v>2</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="I43" s="2">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="J43" s="2">
-        <v>1650</v>
+        <v>3870</v>
       </c>
       <c r="K43" s="2">
         <v>0</v>
@@ -4953,22 +4947,22 @@
         <v>26</v>
       </c>
       <c r="M43" s="2">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N43" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="O43" s="2">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="S43" s="2" t="s">
         <v>26</v>
@@ -4979,55 +4973,55 @@
         <v>2</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="E44" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="H44" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="I44" s="2">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="J44" s="2">
-        <v>3870</v>
+        <v>12949</v>
       </c>
       <c r="K44" s="2">
-        <v>0</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>26</v>
+        <v>2</v>
+      </c>
+      <c r="L44" s="2">
+        <v>6475</v>
       </c>
       <c r="M44" s="2">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="N44" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O44" s="2">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>26</v>
@@ -5035,49 +5029,49 @@
     </row>
     <row r="45" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>195</v>
+        <v>111</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G45" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G45" s="6" t="s">
         <v>197</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>198</v>
       </c>
       <c r="I45" s="2">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="J45" s="2">
-        <v>12949</v>
+        <v>26421</v>
       </c>
       <c r="K45" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L45" s="2">
-        <v>6475</v>
+        <v>2032</v>
       </c>
       <c r="M45" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N45" s="2">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="O45" s="2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>199</v>
@@ -5086,7 +5080,7 @@
         <v>200</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>201</v>
+        <v>116</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>26</v>
@@ -5097,55 +5091,55 @@
         <v>3</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>114</v>
+        <v>201</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>115</v>
+        <v>202</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I46" s="2">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="J46" s="2">
-        <v>26421</v>
+        <v>5233</v>
       </c>
       <c r="K46" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L46" s="2">
-        <v>2032</v>
+        <v>1047</v>
       </c>
       <c r="M46" s="2">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="N46" s="2">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="O46" s="2">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>119</v>
+        <v>206</v>
       </c>
       <c r="S46" s="2" t="s">
         <v>26</v>
@@ -5156,55 +5150,55 @@
         <v>3</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H47" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I47" s="2">
+        <v>35</v>
+      </c>
+      <c r="J47" s="2">
+        <v>5443</v>
+      </c>
+      <c r="K47" s="2">
+        <v>4</v>
+      </c>
+      <c r="L47" s="2">
+        <v>1361</v>
+      </c>
+      <c r="M47" s="2">
+        <v>77</v>
+      </c>
+      <c r="N47" s="2">
+        <v>37</v>
+      </c>
+      <c r="O47" s="2">
+        <v>2</v>
+      </c>
+      <c r="P47" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="I47" s="2">
-        <v>52</v>
-      </c>
-      <c r="J47" s="2">
-        <v>5233</v>
-      </c>
-      <c r="K47" s="2">
-        <v>5</v>
-      </c>
-      <c r="L47" s="2">
-        <v>1047</v>
-      </c>
-      <c r="M47" s="2">
-        <v>80</v>
-      </c>
-      <c r="N47" s="2">
-        <v>64</v>
-      </c>
-      <c r="O47" s="2">
-        <v>2.9</v>
-      </c>
-      <c r="P47" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="Q47" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="S47" s="2" t="s">
         <v>26</v>
@@ -5215,7 +5209,7 @@
         <v>3</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>20</v>
@@ -5224,46 +5218,46 @@
         <v>21</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>120</v>
+        <v>208</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="I48" s="2">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="J48" s="2">
-        <v>5443</v>
+        <v>6121</v>
       </c>
       <c r="K48" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L48" s="2">
-        <v>1361</v>
+        <v>2040</v>
       </c>
       <c r="M48" s="2">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="N48" s="2">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="O48" s="2">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>126</v>
+        <v>211</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>26</v>
@@ -5274,7 +5268,7 @@
         <v>3</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>20</v>
@@ -5283,46 +5277,46 @@
         <v>21</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I49" s="2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J49" s="2">
-        <v>6121</v>
+        <v>7096</v>
       </c>
       <c r="K49" s="2">
         <v>3</v>
       </c>
       <c r="L49" s="2">
-        <v>2040</v>
+        <v>2365</v>
       </c>
       <c r="M49" s="2">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="N49" s="2">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="O49" s="2">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>26</v>
@@ -5333,55 +5327,55 @@
         <v>3</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="I50" s="2">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="J50" s="2">
-        <v>7096</v>
+        <v>4522</v>
       </c>
       <c r="K50" s="2">
         <v>3</v>
       </c>
       <c r="L50" s="2">
-        <v>2365</v>
+        <v>1507</v>
       </c>
       <c r="M50" s="2">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N50" s="2">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="O50" s="2">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="S50" s="2" t="s">
         <v>26</v>
@@ -5392,55 +5386,55 @@
         <v>3</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>218</v>
+        <v>93</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="I51" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J51" s="2">
-        <v>4522</v>
+        <v>1852</v>
       </c>
       <c r="K51" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2">
-        <v>1507</v>
+        <v>926</v>
       </c>
       <c r="M51" s="2">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="N51" s="2">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="O51" s="2">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="S51" s="2" t="s">
         <v>26</v>
@@ -5451,7 +5445,7 @@
         <v>3</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>61</v>
@@ -5460,46 +5454,46 @@
         <v>62</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I52" s="2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J52" s="2">
-        <v>1852</v>
+        <v>2198</v>
       </c>
       <c r="K52" s="2">
         <v>2</v>
       </c>
       <c r="L52" s="2">
-        <v>926</v>
+        <v>1099</v>
       </c>
       <c r="M52" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N52" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O52" s="2">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="S52" s="2" t="s">
         <v>26</v>
@@ -5510,55 +5504,55 @@
         <v>3</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I53" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J53" s="2">
-        <v>2198</v>
+        <v>2041</v>
       </c>
       <c r="K53" s="2">
         <v>2</v>
       </c>
       <c r="L53" s="2">
-        <v>1099</v>
+        <v>1021</v>
       </c>
       <c r="M53" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N53" s="2">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="O53" s="2">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="S53" s="2" t="s">
         <v>26</v>
@@ -5569,7 +5563,7 @@
         <v>3</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>20</v>
@@ -5578,46 +5572,46 @@
         <v>21</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>206</v>
+        <v>237</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>238</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="I54" s="2">
-        <v>14</v>
-      </c>
-      <c r="J54" s="2">
-        <v>2041</v>
-      </c>
-      <c r="K54" s="2">
-        <v>2</v>
-      </c>
-      <c r="L54" s="2">
-        <v>1021</v>
-      </c>
-      <c r="M54" s="2">
-        <v>77</v>
-      </c>
-      <c r="N54" s="2">
-        <v>48</v>
-      </c>
-      <c r="O54" s="2">
-        <v>2.4</v>
+        <v>239</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>237</v>
+        <v>26</v>
       </c>
       <c r="S54" s="2" t="s">
         <v>26</v>
@@ -5628,25 +5622,25 @@
         <v>3</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>242</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>26</v>
@@ -5670,74 +5664,15 @@
         <v>26</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="R55" s="2" t="s">
         <v>26</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>3</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L56" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N56" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q56" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="R56" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="S56" s="2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -5764,10 +5699,10 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>15</v>
@@ -5775,184 +5710,184 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5960,13 +5895,13 @@
         <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5974,13 +5909,13 @@
         <v>61</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5988,13 +5923,13 @@
         <v>61</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6002,13 +5937,13 @@
         <v>61</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6016,13 +5951,13 @@
         <v>20</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6030,13 +5965,13 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -6057,82 +5992,82 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -6172,7 +6107,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>8</v>
@@ -6181,7 +6116,7 @@
         <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>11</v>
@@ -6201,19 +6136,19 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F2">
         <v>26</v>
@@ -6237,24 +6172,24 @@
         <v>3.1</v>
       </c>
       <c r="M2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F3">
         <v>32</v>
@@ -6283,19 +6218,19 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D4" t="s">
+        <v>298</v>
+      </c>
+      <c r="E4" t="s">
         <v>299</v>
-      </c>
-      <c r="D4" t="s">
-        <v>300</v>
-      </c>
-      <c r="E4" t="s">
-        <v>301</v>
       </c>
       <c r="F4">
         <v>29</v>
@@ -6319,24 +6254,24 @@
         <v>2.6</v>
       </c>
       <c r="M4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F5">
         <v>14</v>
@@ -6360,24 +6295,24 @@
         <v>3.2</v>
       </c>
       <c r="M5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
+        <v>303</v>
+      </c>
+      <c r="D6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E6" t="s">
         <v>305</v>
-      </c>
-      <c r="D6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E6" t="s">
-        <v>307</v>
       </c>
       <c r="F6">
         <v>23</v>
@@ -6401,24 +6336,24 @@
         <v>3.5</v>
       </c>
       <c r="M6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -6447,19 +6382,19 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" t="s">
         <v>128</v>
       </c>
-      <c r="B8" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" t="s">
-        <v>131</v>
-      </c>
       <c r="E8" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F8">
         <v>18</v>
@@ -6488,19 +6423,19 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C9" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F9">
         <v>19</v>
@@ -6524,24 +6459,24 @@
         <v>2.1</v>
       </c>
       <c r="M9" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D10" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F10">
         <v>15</v>
@@ -6565,24 +6500,24 @@
         <v>3.6</v>
       </c>
       <c r="M10" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C11" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D11" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E11" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F11">
         <v>17</v>
@@ -6606,24 +6541,24 @@
         <v>2.8</v>
       </c>
       <c r="M11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D12" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F12">
         <v>38</v>
@@ -6647,24 +6582,24 @@
         <v>3.5</v>
       </c>
       <c r="M12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C13" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D13" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E13" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F13">
         <v>8</v>
@@ -6688,24 +6623,24 @@
         <v>3.1</v>
       </c>
       <c r="M13" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C14" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D14" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E14" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F14">
         <v>17</v>
@@ -6729,24 +6664,24 @@
         <v>3.2</v>
       </c>
       <c r="M14" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C15" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D15" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F15">
         <v>8</v>
@@ -6775,19 +6710,19 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C16" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D16" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E16" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F16">
         <v>12</v>
@@ -6811,24 +6746,24 @@
         <v>3.3</v>
       </c>
       <c r="M16" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C17" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D17" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E17" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F17">
         <v>10</v>
@@ -6852,24 +6787,24 @@
         <v>3.3</v>
       </c>
       <c r="M17" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C18" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D18" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E18" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F18">
         <v>7</v>
@@ -6893,24 +6828,24 @@
         <v>2.3</v>
       </c>
       <c r="M18" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F19">
         <v>14</v>
@@ -6939,19 +6874,19 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C20" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D20" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F20">
         <v>10</v>
@@ -6975,24 +6910,24 @@
         <v>3.6</v>
       </c>
       <c r="M20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C21" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D21" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E21" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -7016,24 +6951,24 @@
         <v>3.3</v>
       </c>
       <c r="M21" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D22" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E22" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F22">
         <v>10</v>
@@ -7057,24 +6992,24 @@
         <v>3</v>
       </c>
       <c r="M22" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B23" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C23" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D23" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E23" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F23">
         <v>10</v>
@@ -7098,24 +7033,24 @@
         <v>3.6</v>
       </c>
       <c r="M23" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B24" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C24" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D24" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E24" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F24">
         <v>6</v>
@@ -7139,24 +7074,24 @@
         <v>3.1</v>
       </c>
       <c r="M24" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B25" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C25" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D25" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E25" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F25">
         <v>11</v>
@@ -7180,24 +7115,24 @@
         <v>2.6</v>
       </c>
       <c r="M25" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B26" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C26" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D26" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E26" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F26">
         <v>9</v>
@@ -7226,19 +7161,19 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D27" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E27" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -7267,19 +7202,19 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B28" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D28" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E28" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F28">
         <v>7</v>
@@ -7303,24 +7238,24 @@
         <v>3.5</v>
       </c>
       <c r="M28" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D29" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E29" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F29">
         <v>7</v>
@@ -7344,24 +7279,24 @@
         <v>3.4</v>
       </c>
       <c r="M29" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C30" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D30" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E30" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F30">
         <v>5</v>
@@ -7385,24 +7320,24 @@
         <v>3</v>
       </c>
       <c r="M30" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D31" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E31" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F31">
         <v>5</v>
@@ -7426,24 +7361,24 @@
         <v>3.4</v>
       </c>
       <c r="M31" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C32" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D32" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E32" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F32">
         <v>3</v>
@@ -7467,24 +7402,24 @@
         <v>4.1</v>
       </c>
       <c r="M32" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D33" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E33" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F33">
         <v>6</v>
@@ -7508,24 +7443,24 @@
         <v>2.8</v>
       </c>
       <c r="M33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D34" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E34" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F34">
         <v>6</v>
@@ -7549,24 +7484,24 @@
         <v>3.9</v>
       </c>
       <c r="M34" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C35" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D35" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E35" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F35">
         <v>5</v>
@@ -7590,24 +7525,24 @@
         <v>2.2</v>
       </c>
       <c r="M35" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C36" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D36" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E36" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F36">
         <v>5</v>
@@ -7631,24 +7566,24 @@
         <v>4</v>
       </c>
       <c r="M36" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C37" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D37" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E37" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F37">
         <v>2</v>
@@ -7672,24 +7607,24 @@
         <v>3.7</v>
       </c>
       <c r="M37" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B38" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C38" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D38" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E38" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F38">
         <v>6</v>
@@ -7713,24 +7648,24 @@
         <v>3.3</v>
       </c>
       <c r="M38" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C39" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D39" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E39" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F39">
         <v>5</v>
@@ -7754,24 +7689,24 @@
         <v>3.2</v>
       </c>
       <c r="M39" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B40" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C40" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D40" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E40" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F40">
         <v>4</v>
@@ -7795,24 +7730,24 @@
         <v>3.2</v>
       </c>
       <c r="M40" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C41" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D41" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E41" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -7841,19 +7776,19 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B42" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C42" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D42" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E42" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F42">
         <v>4</v>
@@ -7877,24 +7812,24 @@
         <v>3.6</v>
       </c>
       <c r="M42" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C43" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D43" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E43" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F43">
         <v>2</v>
@@ -7918,24 +7853,24 @@
         <v>3.2</v>
       </c>
       <c r="M43" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B44" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C44" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D44" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E44" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F44">
         <v>2</v>
@@ -7959,24 +7894,24 @@
         <v>3.5</v>
       </c>
       <c r="M44" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B45" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C45" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D45" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E45" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F45">
         <v>2</v>
@@ -8000,24 +7935,24 @@
         <v>3.2</v>
       </c>
       <c r="M45" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B46" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C46" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E46" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F46">
         <v>4</v>
@@ -8046,19 +7981,19 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B47" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C47" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D47" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E47" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -8082,24 +8017,24 @@
         <v>3</v>
       </c>
       <c r="M47" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B48" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C48" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D48" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E48" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F48">
         <v>3</v>
@@ -8123,24 +8058,24 @@
         <v>4.4</v>
       </c>
       <c r="M48" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C49" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D49" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E49" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F49">
         <v>2</v>
@@ -8164,24 +8099,24 @@
         <v>3.6</v>
       </c>
       <c r="M49" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C50" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D50" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E50" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F50">
         <v>8</v>
@@ -8205,24 +8140,24 @@
         <v>3.5</v>
       </c>
       <c r="M50" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B51" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C51" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D51" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E51" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F51">
         <v>2</v>
@@ -8251,19 +8186,19 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B52" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C52" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D52" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E52" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F52">
         <v>2</v>
@@ -8287,24 +8222,24 @@
         <v>3.4</v>
       </c>
       <c r="M52" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C53" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D53" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E53" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -8333,19 +8268,19 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B54" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C54" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D54" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E54" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F54">
         <v>3</v>
@@ -8369,24 +8304,24 @@
         <v>3.4</v>
       </c>
       <c r="M54" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B55" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C55" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D55" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E55" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -8410,24 +8345,24 @@
         <v>3.3</v>
       </c>
       <c r="M55" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B56" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C56" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D56" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E56" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F56">
         <v>3</v>
@@ -8451,24 +8386,24 @@
         <v>3.6</v>
       </c>
       <c r="M56" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B57" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C57" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D57" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E57" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F57">
         <v>2</v>
@@ -8492,24 +8427,24 @@
         <v>2.9</v>
       </c>
       <c r="M57" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B58" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D58" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E58" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F58">
         <v>3</v>
@@ -8533,24 +8468,24 @@
         <v>2.6</v>
       </c>
       <c r="M58" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B59" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C59" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D59" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E59" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F59">
         <v>3</v>
@@ -8574,24 +8509,24 @@
         <v>3</v>
       </c>
       <c r="M59" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C60" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D60" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E60" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F60">
         <v>1</v>
@@ -8620,19 +8555,19 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D61" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E61" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -8656,24 +8591,24 @@
         <v>5.3</v>
       </c>
       <c r="M61" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B62" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C62" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D62" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E62" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -8697,24 +8632,24 @@
         <v>4.4</v>
       </c>
       <c r="M62" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D63" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E63" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -8738,24 +8673,24 @@
         <v>26</v>
       </c>
       <c r="M63" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C64" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D64" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E64" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -8779,24 +8714,24 @@
         <v>3.4</v>
       </c>
       <c r="M64" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C65" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D65" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E65" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -8820,24 +8755,24 @@
         <v>3.4</v>
       </c>
       <c r="M65" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C66" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D66" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E66" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -8861,24 +8796,24 @@
         <v>5</v>
       </c>
       <c r="M66" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B67" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C67" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D67" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E67" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -8902,24 +8837,24 @@
         <v>4.3</v>
       </c>
       <c r="M67" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C68" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D68" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E68" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -8943,24 +8878,24 @@
         <v>26</v>
       </c>
       <c r="M68" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B69" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C69" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D69" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E69" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -8984,7 +8919,7 @@
         <v>3.2</v>
       </c>
       <c r="M69" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -9001,7 +8936,7 @@
         <v>64</v>
       </c>
       <c r="E70" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F70">
         <v>122</v>
@@ -9036,13 +8971,13 @@
         <v>62</v>
       </c>
       <c r="C71" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D71" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E71" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F71">
         <v>58</v>
@@ -9066,7 +9001,7 @@
         <v>3</v>
       </c>
       <c r="M71" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
@@ -9077,13 +9012,13 @@
         <v>62</v>
       </c>
       <c r="C72" t="s">
-        <v>93</v>
+        <v>201</v>
       </c>
       <c r="D72" t="s">
-        <v>94</v>
+        <v>202</v>
       </c>
       <c r="E72" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F72">
         <v>52</v>
@@ -9107,7 +9042,7 @@
         <v>2.9</v>
       </c>
       <c r="M72" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
@@ -9118,13 +9053,13 @@
         <v>62</v>
       </c>
       <c r="C73" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D73" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E73" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F73">
         <v>19</v>
@@ -9148,7 +9083,7 @@
         <v>2.1</v>
       </c>
       <c r="M73" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
@@ -9159,13 +9094,13 @@
         <v>62</v>
       </c>
       <c r="C74" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D74" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E74" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F74">
         <v>17</v>
@@ -9189,7 +9124,7 @@
         <v>2.8</v>
       </c>
       <c r="M74" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
@@ -9200,13 +9135,13 @@
         <v>62</v>
       </c>
       <c r="C75" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D75" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E75" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F75">
         <v>24</v>
@@ -9230,7 +9165,7 @@
         <v>2.4</v>
       </c>
       <c r="M75" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -9241,13 +9176,13 @@
         <v>62</v>
       </c>
       <c r="C76" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D76" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E76" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F76">
         <v>25</v>
@@ -9271,7 +9206,7 @@
         <v>3.1</v>
       </c>
       <c r="M76" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
@@ -9282,13 +9217,13 @@
         <v>62</v>
       </c>
       <c r="C77" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D77" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E77" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F77">
         <v>21</v>
@@ -9312,7 +9247,7 @@
         <v>3.2</v>
       </c>
       <c r="M77" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
@@ -9323,13 +9258,13 @@
         <v>62</v>
       </c>
       <c r="C78" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D78" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E78" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F78">
         <v>16</v>
@@ -9353,7 +9288,7 @@
         <v>2.7</v>
       </c>
       <c r="M78" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
@@ -9364,13 +9299,13 @@
         <v>62</v>
       </c>
       <c r="C79" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D79" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E79" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F79">
         <v>16</v>
@@ -9405,13 +9340,13 @@
         <v>62</v>
       </c>
       <c r="C80" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D80" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E80" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F80">
         <v>17</v>
@@ -9435,7 +9370,7 @@
         <v>2.5</v>
       </c>
       <c r="M80" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -9446,13 +9381,13 @@
         <v>62</v>
       </c>
       <c r="C81" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D81" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E81" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F81">
         <v>20</v>
@@ -9476,7 +9411,7 @@
         <v>2.7</v>
       </c>
       <c r="M81" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
@@ -9487,13 +9422,13 @@
         <v>62</v>
       </c>
       <c r="C82" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D82" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E82" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F82">
         <v>20</v>
@@ -9517,7 +9452,7 @@
         <v>1.7</v>
       </c>
       <c r="M82" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
@@ -9528,13 +9463,13 @@
         <v>62</v>
       </c>
       <c r="C83" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D83" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E83" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F83">
         <v>7</v>
@@ -9558,7 +9493,7 @@
         <v>2.5</v>
       </c>
       <c r="M83" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
@@ -9569,13 +9504,13 @@
         <v>62</v>
       </c>
       <c r="C84" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D84" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E84" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F84">
         <v>17</v>
@@ -9599,7 +9534,7 @@
         <v>2.4</v>
       </c>
       <c r="M84" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
@@ -9610,13 +9545,13 @@
         <v>62</v>
       </c>
       <c r="C85" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D85" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E85" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F85">
         <v>19</v>
@@ -9640,7 +9575,7 @@
         <v>2.3</v>
       </c>
       <c r="M85" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
@@ -9651,13 +9586,13 @@
         <v>62</v>
       </c>
       <c r="C86" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D86" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E86" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F86">
         <v>17</v>
@@ -9681,7 +9616,7 @@
         <v>2.2</v>
       </c>
       <c r="M86" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
@@ -9692,13 +9627,13 @@
         <v>62</v>
       </c>
       <c r="C87" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D87" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E87" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F87">
         <v>11</v>
@@ -9722,7 +9657,7 @@
         <v>2.7</v>
       </c>
       <c r="M87" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
@@ -9733,13 +9668,13 @@
         <v>62</v>
       </c>
       <c r="C88" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D88" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E88" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F88">
         <v>6</v>
@@ -9774,13 +9709,13 @@
         <v>62</v>
       </c>
       <c r="C89" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D89" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E89" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F89">
         <v>18</v>
@@ -9804,7 +9739,7 @@
         <v>2.8</v>
       </c>
       <c r="M89" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
@@ -9815,13 +9750,13 @@
         <v>62</v>
       </c>
       <c r="C90" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D90" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E90" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F90">
         <v>10</v>
@@ -9845,7 +9780,7 @@
         <v>2.7</v>
       </c>
       <c r="M90" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
@@ -9856,13 +9791,13 @@
         <v>62</v>
       </c>
       <c r="C91" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D91" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E91" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F91">
         <v>8</v>
@@ -9886,7 +9821,7 @@
         <v>2.3</v>
       </c>
       <c r="M91" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
@@ -9897,13 +9832,13 @@
         <v>62</v>
       </c>
       <c r="C92" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D92" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E92" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F92">
         <v>15</v>
@@ -9927,7 +9862,7 @@
         <v>2</v>
       </c>
       <c r="M92" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
@@ -9938,13 +9873,13 @@
         <v>62</v>
       </c>
       <c r="C93" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D93" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E93" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F93">
         <v>8</v>
@@ -9968,7 +9903,7 @@
         <v>3.1</v>
       </c>
       <c r="M93" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
@@ -9979,13 +9914,13 @@
         <v>62</v>
       </c>
       <c r="C94" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D94" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E94" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F94">
         <v>11</v>
@@ -10009,7 +9944,7 @@
         <v>2.3</v>
       </c>
       <c r="M94" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
@@ -10020,13 +9955,13 @@
         <v>62</v>
       </c>
       <c r="C95" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D95" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E95" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F95">
         <v>8</v>
@@ -10050,7 +9985,7 @@
         <v>2.5</v>
       </c>
       <c r="M95" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
@@ -10061,13 +9996,13 @@
         <v>62</v>
       </c>
       <c r="C96" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D96" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E96" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F96">
         <v>5</v>
@@ -10091,7 +10026,7 @@
         <v>3.6</v>
       </c>
       <c r="M96" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
@@ -10102,13 +10037,13 @@
         <v>62</v>
       </c>
       <c r="C97" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D97" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E97" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F97">
         <v>18</v>
@@ -10132,7 +10067,7 @@
         <v>2.3</v>
       </c>
       <c r="M97" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
@@ -10143,13 +10078,13 @@
         <v>62</v>
       </c>
       <c r="C98" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D98" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E98" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F98">
         <v>7</v>
@@ -10173,7 +10108,7 @@
         <v>2.9</v>
       </c>
       <c r="M98" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
@@ -10184,13 +10119,13 @@
         <v>62</v>
       </c>
       <c r="C99" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D99" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E99" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F99">
         <v>7</v>
@@ -10214,7 +10149,7 @@
         <v>2.3</v>
       </c>
       <c r="M99" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
@@ -10225,13 +10160,13 @@
         <v>62</v>
       </c>
       <c r="C100" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D100" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E100" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F100">
         <v>5</v>
@@ -10255,7 +10190,7 @@
         <v>1.9</v>
       </c>
       <c r="M100" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
@@ -10266,13 +10201,13 @@
         <v>62</v>
       </c>
       <c r="C101" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D101" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E101" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F101">
         <v>5</v>
@@ -10296,7 +10231,7 @@
         <v>2.3</v>
       </c>
       <c r="M101" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
@@ -10307,13 +10242,13 @@
         <v>62</v>
       </c>
       <c r="C102" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D102" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E102" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F102">
         <v>5</v>
@@ -10348,13 +10283,13 @@
         <v>62</v>
       </c>
       <c r="C103" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D103" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E103" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F103">
         <v>6</v>
@@ -10378,7 +10313,7 @@
         <v>2</v>
       </c>
       <c r="M103" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
@@ -10389,13 +10324,13 @@
         <v>62</v>
       </c>
       <c r="C104" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D104" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E104" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F104">
         <v>8</v>
@@ -10419,7 +10354,7 @@
         <v>3</v>
       </c>
       <c r="M104" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
@@ -10430,13 +10365,13 @@
         <v>62</v>
       </c>
       <c r="C105" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D105" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E105" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F105">
         <v>3</v>
@@ -10460,7 +10395,7 @@
         <v>1.8</v>
       </c>
       <c r="M105" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
@@ -10471,13 +10406,13 @@
         <v>62</v>
       </c>
       <c r="C106" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D106" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E106" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F106">
         <v>4</v>
@@ -10501,7 +10436,7 @@
         <v>2.8</v>
       </c>
       <c r="M106" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
@@ -10512,13 +10447,13 @@
         <v>62</v>
       </c>
       <c r="C107" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D107" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E107" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F107">
         <v>5</v>
@@ -10542,7 +10477,7 @@
         <v>2.9</v>
       </c>
       <c r="M107" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
@@ -10553,13 +10488,13 @@
         <v>62</v>
       </c>
       <c r="C108" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D108" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E108" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F108">
         <v>4</v>
@@ -10583,7 +10518,7 @@
         <v>2.5</v>
       </c>
       <c r="M108" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
@@ -10594,13 +10529,13 @@
         <v>62</v>
       </c>
       <c r="C109" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D109" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E109" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F109">
         <v>8</v>
@@ -10624,7 +10559,7 @@
         <v>2.3</v>
       </c>
       <c r="M109" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
@@ -10635,13 +10570,13 @@
         <v>62</v>
       </c>
       <c r="C110" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D110" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E110" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F110">
         <v>7</v>
@@ -10665,7 +10600,7 @@
         <v>1.9</v>
       </c>
       <c r="M110" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -10676,13 +10611,13 @@
         <v>62</v>
       </c>
       <c r="C111" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D111" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E111" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F111">
         <v>3</v>
@@ -10706,7 +10641,7 @@
         <v>1.5</v>
       </c>
       <c r="M111" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
@@ -10717,13 +10652,13 @@
         <v>62</v>
       </c>
       <c r="C112" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D112" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E112" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F112">
         <v>3</v>
@@ -10747,7 +10682,7 @@
         <v>2</v>
       </c>
       <c r="M112" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
@@ -10758,13 +10693,13 @@
         <v>62</v>
       </c>
       <c r="C113" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D113" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E113" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F113">
         <v>6</v>
@@ -10788,7 +10723,7 @@
         <v>1.7</v>
       </c>
       <c r="M113" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
@@ -10799,13 +10734,13 @@
         <v>62</v>
       </c>
       <c r="C114" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D114" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E114" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F114">
         <v>9</v>
@@ -10840,13 +10775,13 @@
         <v>62</v>
       </c>
       <c r="C115" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D115" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E115" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F115">
         <v>6</v>
@@ -10870,7 +10805,7 @@
         <v>3.1</v>
       </c>
       <c r="M115" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
@@ -10881,13 +10816,13 @@
         <v>62</v>
       </c>
       <c r="C116" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D116" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E116" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F116">
         <v>8</v>
@@ -10922,13 +10857,13 @@
         <v>62</v>
       </c>
       <c r="C117" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D117" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E117" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F117">
         <v>12</v>
@@ -10963,13 +10898,13 @@
         <v>62</v>
       </c>
       <c r="C118" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D118" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E118" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F118">
         <v>5</v>
@@ -10993,7 +10928,7 @@
         <v>2</v>
       </c>
       <c r="M118" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
@@ -11004,13 +10939,13 @@
         <v>62</v>
       </c>
       <c r="C119" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D119" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E119" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F119">
         <v>8</v>
@@ -11034,7 +10969,7 @@
         <v>2.4</v>
       </c>
       <c r="M119" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
@@ -11045,13 +10980,13 @@
         <v>62</v>
       </c>
       <c r="C120" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D120" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E120" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F120">
         <v>5</v>
@@ -11075,7 +11010,7 @@
         <v>3.3</v>
       </c>
       <c r="M120" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
@@ -11086,13 +11021,13 @@
         <v>62</v>
       </c>
       <c r="C121" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D121" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E121" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F121">
         <v>6</v>
@@ -11116,7 +11051,7 @@
         <v>2.4</v>
       </c>
       <c r="M121" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
@@ -11127,13 +11062,13 @@
         <v>62</v>
       </c>
       <c r="C122" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D122" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E122" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F122">
         <v>3</v>
@@ -11157,7 +11092,7 @@
         <v>1.7</v>
       </c>
       <c r="M122" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
@@ -11168,13 +11103,13 @@
         <v>62</v>
       </c>
       <c r="C123" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D123" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E123" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F123">
         <v>3</v>
@@ -11198,7 +11133,7 @@
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
@@ -11209,13 +11144,13 @@
         <v>62</v>
       </c>
       <c r="C124" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D124" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E124" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F124">
         <v>5</v>
@@ -11250,13 +11185,13 @@
         <v>62</v>
       </c>
       <c r="C125" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D125" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E125" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F125">
         <v>5</v>
@@ -11280,7 +11215,7 @@
         <v>1.6</v>
       </c>
       <c r="M125" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
@@ -11291,13 +11226,13 @@
         <v>62</v>
       </c>
       <c r="C126" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D126" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E126" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F126">
         <v>6</v>
@@ -11321,7 +11256,7 @@
         <v>1.9</v>
       </c>
       <c r="M126" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
@@ -11332,13 +11267,13 @@
         <v>62</v>
       </c>
       <c r="C127" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D127" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E127" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F127">
         <v>3</v>
@@ -11373,13 +11308,13 @@
         <v>62</v>
       </c>
       <c r="C128" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D128" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E128" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F128">
         <v>5</v>
@@ -11403,7 +11338,7 @@
         <v>2.2</v>
       </c>
       <c r="M128" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
@@ -11414,13 +11349,13 @@
         <v>62</v>
       </c>
       <c r="C129" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D129" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E129" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F129">
         <v>6</v>
@@ -11444,7 +11379,7 @@
         <v>2.8</v>
       </c>
       <c r="M129" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
@@ -11455,13 +11390,13 @@
         <v>62</v>
       </c>
       <c r="C130" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D130" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E130" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F130">
         <v>2</v>
@@ -11485,7 +11420,7 @@
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
@@ -11496,13 +11431,13 @@
         <v>62</v>
       </c>
       <c r="C131" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D131" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E131" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F131">
         <v>2</v>
@@ -11526,7 +11461,7 @@
         <v>2</v>
       </c>
       <c r="M131" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
@@ -11537,13 +11472,13 @@
         <v>62</v>
       </c>
       <c r="C132" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D132" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E132" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -11567,7 +11502,7 @@
         <v>1</v>
       </c>
       <c r="M132" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -11578,13 +11513,13 @@
         <v>62</v>
       </c>
       <c r="C133" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D133" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E133" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F133">
         <v>3</v>
@@ -11608,7 +11543,7 @@
         <v>2.9</v>
       </c>
       <c r="M133" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
@@ -11619,13 +11554,13 @@
         <v>62</v>
       </c>
       <c r="C134" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D134" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E134" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F134">
         <v>2</v>
@@ -11649,7 +11584,7 @@
         <v>2.8</v>
       </c>
       <c r="M134" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
@@ -11660,13 +11595,13 @@
         <v>62</v>
       </c>
       <c r="C135" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D135" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E135" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F135">
         <v>3</v>
@@ -11690,7 +11625,7 @@
         <v>2.1</v>
       </c>
       <c r="M135" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
@@ -11701,13 +11636,13 @@
         <v>62</v>
       </c>
       <c r="C136" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D136" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E136" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F136">
         <v>2</v>
@@ -11731,7 +11666,7 @@
         <v>1.9</v>
       </c>
       <c r="M136" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
@@ -11742,13 +11677,13 @@
         <v>62</v>
       </c>
       <c r="C137" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D137" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E137" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F137">
         <v>2</v>
@@ -11772,7 +11707,7 @@
         <v>1.5</v>
       </c>
       <c r="M137" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
@@ -11783,13 +11718,13 @@
         <v>62</v>
       </c>
       <c r="C138" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D138" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E138" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -11813,7 +11748,7 @@
         <v>1.9</v>
       </c>
       <c r="M138" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
@@ -11824,13 +11759,13 @@
         <v>62</v>
       </c>
       <c r="C139" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D139" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E139" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F139">
         <v>1</v>
@@ -11854,7 +11789,7 @@
         <v>1.8</v>
       </c>
       <c r="M139" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
@@ -11865,13 +11800,13 @@
         <v>62</v>
       </c>
       <c r="C140" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D140" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E140" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F140">
         <v>2</v>
@@ -11895,7 +11830,7 @@
         <v>3</v>
       </c>
       <c r="M140" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
@@ -11906,13 +11841,13 @@
         <v>62</v>
       </c>
       <c r="C141" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D141" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E141" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F141">
         <v>2</v>
@@ -11936,7 +11871,7 @@
         <v>2.8</v>
       </c>
       <c r="M141" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
@@ -11947,13 +11882,13 @@
         <v>62</v>
       </c>
       <c r="C142" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D142" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E142" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -11977,7 +11912,7 @@
         <v>2.9</v>
       </c>
       <c r="M142" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
@@ -11988,13 +11923,13 @@
         <v>62</v>
       </c>
       <c r="C143" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D143" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E143" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F143">
         <v>1</v>
@@ -12018,7 +11953,7 @@
         <v>3.8</v>
       </c>
       <c r="M143" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
@@ -12029,13 +11964,13 @@
         <v>62</v>
       </c>
       <c r="C144" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D144" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E144" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -12059,7 +11994,7 @@
         <v>3</v>
       </c>
       <c r="M144" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
@@ -12070,13 +12005,13 @@
         <v>62</v>
       </c>
       <c r="C145" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D145" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E145" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -12100,7 +12035,7 @@
         <v>2.7</v>
       </c>
       <c r="M145" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
@@ -12111,13 +12046,13 @@
         <v>62</v>
       </c>
       <c r="C146" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D146" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E146" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -12141,7 +12076,7 @@
         <v>4</v>
       </c>
       <c r="M146" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
@@ -12152,13 +12087,13 @@
         <v>62</v>
       </c>
       <c r="C147" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D147" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E147" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F147">
         <v>0</v>
@@ -12182,7 +12117,7 @@
         <v>2.3</v>
       </c>
       <c r="M147" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
@@ -12193,13 +12128,13 @@
         <v>62</v>
       </c>
       <c r="C148" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D148" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E148" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -12223,7 +12158,7 @@
         <v>26</v>
       </c>
       <c r="M148" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
@@ -12234,13 +12169,13 @@
         <v>62</v>
       </c>
       <c r="C149" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D149" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E149" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -12264,7 +12199,7 @@
         <v>1</v>
       </c>
       <c r="M149" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
@@ -12275,13 +12210,13 @@
         <v>62</v>
       </c>
       <c r="C150" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D150" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E150" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -12305,7 +12240,7 @@
         <v>2.5</v>
       </c>
       <c r="M150" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
@@ -12316,13 +12251,13 @@
         <v>62</v>
       </c>
       <c r="C151" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D151" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E151" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -12346,7 +12281,7 @@
         <v>1</v>
       </c>
       <c r="M151" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
@@ -12357,13 +12292,13 @@
         <v>62</v>
       </c>
       <c r="C152" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D152" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E152" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -12387,7 +12322,7 @@
         <v>1</v>
       </c>
       <c r="M152" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
@@ -12398,13 +12333,13 @@
         <v>62</v>
       </c>
       <c r="C153" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D153" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E153" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -12428,7 +12363,7 @@
         <v>2.5</v>
       </c>
       <c r="M153" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.25">
@@ -12439,13 +12374,13 @@
         <v>62</v>
       </c>
       <c r="C154" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D154" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E154" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -12469,7 +12404,7 @@
         <v>5</v>
       </c>
       <c r="M154" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.25">
@@ -12480,13 +12415,13 @@
         <v>62</v>
       </c>
       <c r="C155" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D155" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E155" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -12510,7 +12445,7 @@
         <v>4.5</v>
       </c>
       <c r="M155" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.25">
@@ -12521,13 +12456,13 @@
         <v>62</v>
       </c>
       <c r="C156" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D156" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E156" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -12551,7 +12486,7 @@
         <v>2.1</v>
       </c>
       <c r="M156" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.25">
@@ -12562,13 +12497,13 @@
         <v>62</v>
       </c>
       <c r="C157" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D157" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E157" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -12592,7 +12527,7 @@
         <v>6</v>
       </c>
       <c r="M157" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.25">
@@ -12603,13 +12538,13 @@
         <v>62</v>
       </c>
       <c r="C158" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D158" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="E158" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -12633,7 +12568,7 @@
         <v>3.2</v>
       </c>
       <c r="M158" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.25">
@@ -12644,13 +12579,13 @@
         <v>62</v>
       </c>
       <c r="C159" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D159" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E159" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -12674,7 +12609,7 @@
         <v>5</v>
       </c>
       <c r="M159" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.25">
@@ -12685,13 +12620,13 @@
         <v>62</v>
       </c>
       <c r="C160" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D160" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E160" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -12715,7 +12650,7 @@
         <v>4.3</v>
       </c>
       <c r="M160" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.25">
@@ -12726,13 +12661,13 @@
         <v>62</v>
       </c>
       <c r="C161" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D161" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E161" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F161">
         <v>0</v>
@@ -12756,7 +12691,7 @@
         <v>2</v>
       </c>
       <c r="M161" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.25">
@@ -12767,13 +12702,13 @@
         <v>62</v>
       </c>
       <c r="C162" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D162" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E162" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -12797,7 +12732,7 @@
         <v>3.3</v>
       </c>
       <c r="M162" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.25">
@@ -12808,13 +12743,13 @@
         <v>62</v>
       </c>
       <c r="C163" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D163" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E163" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -12838,7 +12773,7 @@
         <v>3.3</v>
       </c>
       <c r="M163" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.25">
@@ -12849,13 +12784,13 @@
         <v>62</v>
       </c>
       <c r="C164" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D164" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E164" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -12879,7 +12814,7 @@
         <v>2.6</v>
       </c>
       <c r="M164" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.25">
@@ -12890,13 +12825,13 @@
         <v>62</v>
       </c>
       <c r="C165" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D165" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E165" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F165">
         <v>0</v>
@@ -12920,7 +12855,7 @@
         <v>2.3</v>
       </c>
       <c r="M165" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.25">
@@ -12931,13 +12866,13 @@
         <v>62</v>
       </c>
       <c r="C166" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D166" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E166" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F166">
         <v>0</v>
@@ -12961,7 +12896,7 @@
         <v>2.1</v>
       </c>
       <c r="M166" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.25">
@@ -12972,13 +12907,13 @@
         <v>62</v>
       </c>
       <c r="C167" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D167" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E167" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -13002,7 +12937,7 @@
         <v>2.1</v>
       </c>
       <c r="M167" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.25">
@@ -13013,13 +12948,13 @@
         <v>62</v>
       </c>
       <c r="C168" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D168" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E168" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F168">
         <v>0</v>
@@ -13043,7 +12978,7 @@
         <v>26</v>
       </c>
       <c r="M168" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.25">
@@ -13054,13 +12989,13 @@
         <v>62</v>
       </c>
       <c r="C169" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D169" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E169" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F169">
         <v>0</v>
@@ -13084,7 +13019,7 @@
         <v>3</v>
       </c>
       <c r="M169" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.25">
@@ -13095,13 +13030,13 @@
         <v>62</v>
       </c>
       <c r="C170" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D170" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E170" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -13125,7 +13060,7 @@
         <v>2</v>
       </c>
       <c r="M170" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.25">
@@ -13136,13 +13071,13 @@
         <v>62</v>
       </c>
       <c r="C171" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D171" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E171" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -13166,7 +13101,7 @@
         <v>1</v>
       </c>
       <c r="M171" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
@@ -13177,13 +13112,13 @@
         <v>62</v>
       </c>
       <c r="C172" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D172" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E172" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F172">
         <v>0</v>
@@ -13207,7 +13142,7 @@
         <v>26</v>
       </c>
       <c r="M172" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
@@ -13218,13 +13153,13 @@
         <v>62</v>
       </c>
       <c r="C173" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D173" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E173" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -13248,7 +13183,7 @@
         <v>3.1</v>
       </c>
       <c r="M173" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.25">
@@ -13259,13 +13194,13 @@
         <v>62</v>
       </c>
       <c r="C174" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D174" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E174" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F174">
         <v>0</v>
@@ -13289,7 +13224,7 @@
         <v>5.5</v>
       </c>
       <c r="M174" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
@@ -13300,13 +13235,13 @@
         <v>62</v>
       </c>
       <c r="C175" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D175" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E175" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -13330,7 +13265,7 @@
         <v>1.9</v>
       </c>
       <c r="M175" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">
@@ -13341,13 +13276,13 @@
         <v>21</v>
       </c>
       <c r="C176" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D176" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E176" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F176">
         <v>135</v>
@@ -13371,7 +13306,7 @@
         <v>2.6</v>
       </c>
       <c r="M176" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">
@@ -13382,13 +13317,13 @@
         <v>21</v>
       </c>
       <c r="C177" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D177" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E177" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F177">
         <v>60</v>
@@ -13412,7 +13347,7 @@
         <v>2.4</v>
       </c>
       <c r="M177" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.25">
@@ -13423,13 +13358,13 @@
         <v>21</v>
       </c>
       <c r="C178" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D178" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E178" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F178">
         <v>63</v>
@@ -13453,7 +13388,7 @@
         <v>3.4</v>
       </c>
       <c r="M178" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.25">
@@ -13470,7 +13405,7 @@
         <v>82</v>
       </c>
       <c r="E179" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F179">
         <v>45</v>
@@ -13505,13 +13440,13 @@
         <v>21</v>
       </c>
       <c r="C180" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D180" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E180" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F180">
         <v>35</v>
@@ -13535,7 +13470,7 @@
         <v>2</v>
       </c>
       <c r="M180" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.25">
@@ -13552,7 +13487,7 @@
         <v>72</v>
       </c>
       <c r="E181" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F181">
         <v>37</v>
@@ -13593,7 +13528,7 @@
         <v>88</v>
       </c>
       <c r="E182" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F182">
         <v>43</v>
@@ -13628,13 +13563,13 @@
         <v>21</v>
       </c>
       <c r="C183" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D183" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E183" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F183">
         <v>33</v>
@@ -13658,7 +13593,7 @@
         <v>2.2</v>
       </c>
       <c r="M183" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.25">
@@ -13669,13 +13604,13 @@
         <v>21</v>
       </c>
       <c r="C184" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D184" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E184" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F184">
         <v>21</v>
@@ -13699,7 +13634,7 @@
         <v>2.1</v>
       </c>
       <c r="M184" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.25">
@@ -13716,7 +13651,7 @@
         <v>37</v>
       </c>
       <c r="E185" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F185">
         <v>46</v>
@@ -13751,13 +13686,13 @@
         <v>21</v>
       </c>
       <c r="C186" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D186" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E186" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F186">
         <v>29</v>
@@ -13781,7 +13716,7 @@
         <v>2.8</v>
       </c>
       <c r="M186" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
@@ -13798,7 +13733,7 @@
         <v>46</v>
       </c>
       <c r="E187" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F187">
         <v>79</v>
@@ -13839,7 +13774,7 @@
         <v>91</v>
       </c>
       <c r="E188" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F188">
         <v>15</v>
@@ -13874,13 +13809,13 @@
         <v>21</v>
       </c>
       <c r="C189" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D189" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E189" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F189">
         <v>14</v>
@@ -13904,7 +13839,7 @@
         <v>2.4</v>
       </c>
       <c r="M189" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.25">
@@ -13915,13 +13850,13 @@
         <v>21</v>
       </c>
       <c r="C190" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D190" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E190" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F190">
         <v>6</v>
@@ -13945,7 +13880,7 @@
         <v>3.1</v>
       </c>
       <c r="M190" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.25">
@@ -13962,7 +13897,7 @@
         <v>85</v>
       </c>
       <c r="E191" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F191">
         <v>19</v>
@@ -13997,13 +13932,13 @@
         <v>21</v>
       </c>
       <c r="C192" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D192" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E192" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F192">
         <v>8</v>
@@ -14027,7 +13962,7 @@
         <v>3.2</v>
       </c>
       <c r="M192" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.25">
@@ -14044,7 +13979,7 @@
         <v>78</v>
       </c>
       <c r="E193" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F193">
         <v>21</v>
@@ -14085,7 +14020,7 @@
         <v>34</v>
       </c>
       <c r="E194" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F194">
         <v>21</v>
@@ -14120,13 +14055,13 @@
         <v>21</v>
       </c>
       <c r="C195" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D195" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E195" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F195">
         <v>8</v>
@@ -14150,7 +14085,7 @@
         <v>2.3</v>
       </c>
       <c r="M195" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.25">
@@ -14161,13 +14096,13 @@
         <v>21</v>
       </c>
       <c r="C196" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D196" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E196" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F196">
         <v>10</v>
@@ -14191,7 +14126,7 @@
         <v>2.7</v>
       </c>
       <c r="M196" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.25">
@@ -14202,13 +14137,13 @@
         <v>21</v>
       </c>
       <c r="C197" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D197" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E197" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F197">
         <v>5</v>
@@ -14232,7 +14167,7 @@
         <v>2.1</v>
       </c>
       <c r="M197" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.25">
@@ -14243,13 +14178,13 @@
         <v>21</v>
       </c>
       <c r="C198" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D198" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E198" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F198">
         <v>1</v>
@@ -14273,7 +14208,7 @@
         <v>1.9</v>
       </c>
       <c r="M198" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.25">
@@ -14284,13 +14219,13 @@
         <v>21</v>
       </c>
       <c r="C199" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D199" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E199" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F199">
         <v>5</v>
@@ -14314,7 +14249,7 @@
         <v>2.2</v>
       </c>
       <c r="M199" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.25">
@@ -14325,13 +14260,13 @@
         <v>21</v>
       </c>
       <c r="C200" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D200" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E200" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F200">
         <v>3</v>
@@ -14355,7 +14290,7 @@
         <v>2.6</v>
       </c>
       <c r="M200" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.25">
@@ -14372,7 +14307,7 @@
         <v>31</v>
       </c>
       <c r="E201" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F201">
         <v>41</v>
@@ -14413,7 +14348,7 @@
         <v>58</v>
       </c>
       <c r="E202" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F202">
         <v>11</v>
@@ -14448,13 +14383,13 @@
         <v>21</v>
       </c>
       <c r="C203" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D203" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E203" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F203">
         <v>5</v>
@@ -14478,7 +14413,7 @@
         <v>2.1</v>
       </c>
       <c r="M203" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.25">
@@ -14495,7 +14430,7 @@
         <v>23</v>
       </c>
       <c r="E204" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F204">
         <v>23</v>
@@ -14530,13 +14465,13 @@
         <v>21</v>
       </c>
       <c r="C205" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D205" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E205" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F205">
         <v>3</v>
@@ -14560,7 +14495,7 @@
         <v>2.8</v>
       </c>
       <c r="M205" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.25">
@@ -14571,13 +14506,13 @@
         <v>21</v>
       </c>
       <c r="C206" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D206" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E206" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F206">
         <v>6</v>
@@ -14601,7 +14536,7 @@
         <v>3.3</v>
       </c>
       <c r="M206" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.25">
@@ -14612,13 +14547,13 @@
         <v>21</v>
       </c>
       <c r="C207" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D207" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E207" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F207">
         <v>3</v>
@@ -14642,7 +14577,7 @@
         <v>2.4</v>
       </c>
       <c r="M207" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.25">
@@ -14653,13 +14588,13 @@
         <v>21</v>
       </c>
       <c r="C208" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D208" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E208" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F208">
         <v>5</v>
@@ -14683,7 +14618,7 @@
         <v>2.3</v>
       </c>
       <c r="M208" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.25">
@@ -14694,13 +14629,13 @@
         <v>21</v>
       </c>
       <c r="C209" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D209" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E209" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F209">
         <v>2</v>
@@ -14724,7 +14659,7 @@
         <v>2.5</v>
       </c>
       <c r="M209" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.25">
@@ -14735,13 +14670,13 @@
         <v>21</v>
       </c>
       <c r="C210" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D210" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E210" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F210">
         <v>3</v>
@@ -14765,7 +14700,7 @@
         <v>2.6</v>
       </c>
       <c r="M210" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.25">
@@ -14776,13 +14711,13 @@
         <v>21</v>
       </c>
       <c r="C211" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D211" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E211" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F211">
         <v>2</v>
@@ -14806,7 +14741,7 @@
         <v>2.6</v>
       </c>
       <c r="M211" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.25">
@@ -14817,13 +14752,13 @@
         <v>21</v>
       </c>
       <c r="C212" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D212" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E212" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F212">
         <v>3</v>
@@ -14847,7 +14782,7 @@
         <v>2.5</v>
       </c>
       <c r="M212" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.25">
@@ -14858,13 +14793,13 @@
         <v>21</v>
       </c>
       <c r="C213" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D213" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E213" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F213">
         <v>4</v>
@@ -14888,7 +14823,7 @@
         <v>1.6</v>
       </c>
       <c r="M213" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.25">
@@ -14905,7 +14840,7 @@
         <v>40</v>
       </c>
       <c r="E214" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F214">
         <v>7</v>
@@ -14940,13 +14875,13 @@
         <v>21</v>
       </c>
       <c r="C215" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D215" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E215" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F215">
         <v>2</v>
@@ -14970,7 +14905,7 @@
         <v>2.6</v>
       </c>
       <c r="M215" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.25">
@@ -14981,13 +14916,13 @@
         <v>21</v>
       </c>
       <c r="C216" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D216" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E216" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F216">
         <v>2</v>
@@ -15011,7 +14946,7 @@
         <v>3.3</v>
       </c>
       <c r="M216" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.25">
@@ -15022,13 +14957,13 @@
         <v>21</v>
       </c>
       <c r="C217" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D217" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E217" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F217">
         <v>1</v>
@@ -15052,7 +14987,7 @@
         <v>2.7</v>
       </c>
       <c r="M217" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.25">
@@ -15069,7 +15004,7 @@
         <v>49</v>
       </c>
       <c r="E218" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F218">
         <v>3</v>
@@ -15104,13 +15039,13 @@
         <v>21</v>
       </c>
       <c r="C219" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D219" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E219" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F219">
         <v>2</v>
@@ -15134,7 +15069,7 @@
         <v>3</v>
       </c>
       <c r="M219" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.25">
@@ -15151,7 +15086,7 @@
         <v>43</v>
       </c>
       <c r="E220" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F220">
         <v>5</v>
@@ -15186,13 +15121,13 @@
         <v>21</v>
       </c>
       <c r="C221" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D221" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E221" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F221">
         <v>2</v>
@@ -15216,7 +15151,7 @@
         <v>3.1</v>
       </c>
       <c r="M221" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.25">
@@ -15227,13 +15162,13 @@
         <v>21</v>
       </c>
       <c r="C222" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D222" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E222" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F222">
         <v>1</v>
@@ -15257,7 +15192,7 @@
         <v>2.1</v>
       </c>
       <c r="M222" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.25">
@@ -15274,7 +15209,7 @@
         <v>52</v>
       </c>
       <c r="E223" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F223">
         <v>4</v>
@@ -15309,13 +15244,13 @@
         <v>21</v>
       </c>
       <c r="C224" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D224" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E224" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F224">
         <v>0</v>
@@ -15339,7 +15274,7 @@
         <v>1.7</v>
       </c>
       <c r="M224" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.25">
@@ -15350,13 +15285,13 @@
         <v>21</v>
       </c>
       <c r="C225" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D225" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E225" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F225">
         <v>0</v>
@@ -15380,7 +15315,7 @@
         <v>1.5</v>
       </c>
       <c r="M225" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.25">
@@ -15391,13 +15326,13 @@
         <v>21</v>
       </c>
       <c r="C226" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D226" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E226" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F226">
         <v>0</v>
@@ -15421,7 +15356,7 @@
         <v>1.7</v>
       </c>
       <c r="M226" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.25">
@@ -15438,7 +15373,7 @@
         <v>55</v>
       </c>
       <c r="E227" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F227">
         <v>0</v>

--- a/yandex-direct/audit/2026-09-28-deystviya-po-gruppam.xlsx
+++ b/yandex-direct/audit/2026-09-28-deystviya-po-gruppam.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2334" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2370" uniqueCount="657">
   <si>
     <t>Этап</t>
   </si>
@@ -196,7 +196,103 @@
     <t>[перегородка] [стеллаж] [потолка]</t>
   </si>
   <si>
-    <t>07.10 (до пауз)</t>
+    <t>07.10 (шаг 1)</t>
+  </si>
+  <si>
+    <t>5774336314</t>
+  </si>
+  <si>
+    <t>Перегородки-гармошки</t>
+  </si>
+  <si>
+    <t>ПЕРЕНОС В НЧ 712877525</t>
+  </si>
+  <si>
+    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородки] [гармошка] -заказ -зонирования -купить -межкомнатная -складные -стеклянные», минус-слова группы, объявления). В копии заменить ссылку объявлений: /peregorodki-garmoshka/ → /mezhkomnatnye-peregorodki-na-zakaz/skladnye-peregorodki-na-zakaz/ (UTM-шаблон оставить). Оригинал в СЧ - пауза (шаг 2).</t>
+  </si>
+  <si>
+    <t>Структура «группа = фраза»: спрос «гармошка» переезжает в НЧ вместе со своей группой, а не дописывается в чужую. В НЧ гармошка конвертит лучше: запросы с «гармошка» - 129 визитов / 5 лидов в НЧ против 142 / 2 в СЧ. Разница, вероятно, в посадочной: СЧ ведёт на /peregorodki-garmoshka/ (123 визита, 2 лида), НЧ «Складные | Гармошка» - на /skladnye-peregorodki-na-zakaz/ (109 визитов, 3 лида) [ГИПОТЕЗА, выборка мала]. Конфликта с НЧ 5774336420 [складные] [перегородки] [гармошка] нет: во фразе копии уже стоит -складные.</t>
+  </si>
+  <si>
+    <t>14.10: копия получает показы и клики, CPC ≤ 150 ₽; 04.11: лиды «гармошка» в НЧ ≥ суммы НЧ+СЧ до переноса</t>
+  </si>
+  <si>
+    <t>[перегородки] [гармошка] -заказ -зонирования -купить -межкомнатная -складные -стеклянные</t>
+  </si>
+  <si>
+    <t>07.10 (шаг 2, после копии)</t>
+  </si>
+  <si>
+    <t>Остановить оригинал в СЧ после того, как копия в НЧ прошла модерацию</t>
+  </si>
+  <si>
+    <t>Оригинал заменён копией в НЧ, два одинаковых ключа в двух РК делят бюджет и статистику.</t>
+  </si>
+  <si>
+    <t>14.10: в СЧ по «гармошка» 0 показов</t>
+  </si>
+  <si>
+    <t>5774336315</t>
+  </si>
+  <si>
+    <t>Перегородки-гармошки | Купить</t>
+  </si>
+  <si>
+    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородка] [гармошка] [купить]», минус-слова группы, объявления). В копии заменить ссылку объявлений: /peregorodki-garmoshka/ → /mezhkomnatnye-peregorodki-na-zakaz/skladnye-peregorodki-na-zakaz/ (UTM-шаблон оставить). Оригинал в СЧ - пауза (шаг 2).</t>
+  </si>
+  <si>
+    <t>[перегородка] [гармошка] [купить]</t>
+  </si>
+  <si>
+    <t>5774336316</t>
+  </si>
+  <si>
+    <t>Перегородки-гармошки | Заказ</t>
+  </si>
+  <si>
+    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородки] [гармошка] [заказ]», минус-слова группы, объявления). В копии заменить ссылку объявлений: /peregorodki-garmoshka/ → /mezhkomnatnye-peregorodki-na-zakaz/skladnye-peregorodki-na-zakaz/ (UTM-шаблон оставить). Оригинал в СЧ - пауза (шаг 2).</t>
+  </si>
+  <si>
+    <t>[перегородки] [гармошка] [заказ]</t>
+  </si>
+  <si>
+    <t>5774336317</t>
+  </si>
+  <si>
+    <t>Перегородки-гармошки | Зонирования</t>
+  </si>
+  <si>
+    <t>Зонирование: 0 лидов, в НЧ не переносим.</t>
+  </si>
+  <si>
+    <t>[перегородка] [гармошка] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336318</t>
+  </si>
+  <si>
+    <t>Перегородки-гармошки | Межкомнатная</t>
+  </si>
+  <si>
+    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородка] [гармошка] [межкомнатная]», минус-слова группы, объявления). В копии заменить ссылку объявлений: /peregorodki-garmoshka/ → /mezhkomnatnye-peregorodki-na-zakaz/skladnye-peregorodki-na-zakaz/ (UTM-шаблон оставить). Оригинал в СЧ - пауза (шаг 2).</t>
+  </si>
+  <si>
+    <t>[перегородка] [гармошка] [межкомнатная]</t>
+  </si>
+  <si>
+    <t>5774336319</t>
+  </si>
+  <si>
+    <t>Перегородки-гармошки | Книжка</t>
+  </si>
+  <si>
+    <t>Книжка: 15 кликов, 2 042 ₽, 0 лидов - не переносим.</t>
+  </si>
+  <si>
+    <t>[перегородка] [книжка]</t>
+  </si>
+  <si>
+    <t>07.10</t>
   </si>
   <si>
     <t>НЧ</t>
@@ -205,1054 +301,964 @@
     <t>712877525</t>
   </si>
   <si>
+    <t>5774336417</t>
+  </si>
+  <si>
+    <t>Складные перегородки | Заказ</t>
+  </si>
+  <si>
+    <t>ВЫКЛЮЧИТЬ АВТОТАРГЕТИНГ</t>
+  </si>
+  <si>
+    <t>Выключить автотаргетинг в группе, фразу оставить (группу не останавливать)</t>
+  </si>
+  <si>
+    <t>Фраза группы ни разу не сработала, все клики - автотаргетинг, и он приводит сюда общие запросы базовой группы («складная перегородка», «межкомнатные перегородки складные»): 0 лидов. Без автотаргетинга группа ловит только свои «заказ / цена», остальное уходит в базовую 5774336419 (5 лидов, CPL 1 047). Разделение сохраняется, фразу базовой группы не трогаем.</t>
+  </si>
+  <si>
+    <t>14.10: у группы расход ≈ 0 или только запросы с «заказ / цена»; клики базовой 5774336419 выросли</t>
+  </si>
+  <si>
+    <t>[складные] [перегородки] [заказ]</t>
+  </si>
+  <si>
+    <t>5774336421</t>
+  </si>
+  <si>
+    <t>Складные перегородки | Цена</t>
+  </si>
+  <si>
+    <t>[складные] [перегородки] [цена]</t>
+  </si>
+  <si>
+    <t>5774336418</t>
+  </si>
+  <si>
+    <t>Складные перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>Остановить</t>
+  </si>
+  <si>
+    <t>Интент «зонирование»: 12 кликов, 579 ₽, 0 лидов. По всем РК зонирование - худший кластер (CR 1,1%).</t>
+  </si>
+  <si>
+    <t>04.11: лиды семейства «Складные» не упали</t>
+  </si>
+  <si>
+    <t>[складные] [перегородки] [зонирования]</t>
+  </si>
+  <si>
+    <t>ВЧ</t>
+  </si>
+  <si>
+    <t>712877513</t>
+  </si>
+  <si>
+    <t>5774336274</t>
+  </si>
+  <si>
+    <t>Стеклянные перегородки</t>
+  </si>
+  <si>
+    <t>ПЕРЕНОС В СЧ 712877517</t>
+  </si>
+  <si>
+    <t>Создать в СЧ новую группу «Интерьерные перегородки | Стеклянные общие» копией группы СЧ 5774336335 (её объявления и посадочная /mezhkomnatnye-peregorodki-na-zakaz/), фразу заменить на фразу этой ВЧ-группы: «[стеклянные] [перегородки] -арочные -гармошка -гостиной -дверью -дизайнерские -заказ -зонирования -интерьерные -квартиру -купить -кухни -лофт -межкомнатные -москве -производителя -раздвижные -распашные -складные -студии -телескопические -цена». Оригинал в ВЧ - пауза (шаг 2).</t>
+  </si>
+  <si>
+    <t>Спрос «стеклянные перегородки» закрепляем за СЧ. Копируем не ВЧ-группу, а объявление и посадочную СЧ-группы, потому что именно они конвертят: СЧ 5774336335 ведёт на /mezhkomnatnye-peregorodki-na-zakaz/ (114 визитов, 13 лидов), ВЧ 5774336274 - на /steklyannye-peregorodki/ (11 визитов, 0 лидов, отказ 68%). Фраза переносится с её минус-словами, в них уже есть -интерьерные, поэтому с группами «Интерьерные» конфликта нет.</t>
+  </si>
+  <si>
+    <t>14.10: новая группа получает показы, отказ ≤ 30%; 04.11: CPL ≤ 2 500 ₽</t>
+  </si>
+  <si>
+    <t>[стеклянные] [перегородки] -арочные -гармошка -гостиной -дверью -дизайнерские -заказ -зонирования -интерьерные -квартиру -купить -кухни -лофт -межкомнатные -москве -производителя -раздвижные -распашные -складные -студии -телескопические -цена</t>
+  </si>
+  <si>
+    <t>5774336213</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки</t>
+  </si>
+  <si>
+    <t>Создать в СЧ новую группу «Интерьерные перегородки | Межкомнатные» копией группы СЧ 5774336333 (объявления и посадочная /mezhkomnatnye-peregorodki-na-zakaz/), фразу заменить на фразу этой ВЧ-группы: «[межкомнатные] [перегородки] -гармошка -дверью -заказ -зеркальные -каскадная -квартиру -купить -металлические -москве -производителя -раздвижные -стеклянные -цена». Оригинал в ВЧ - пауза (шаг 2).</t>
+  </si>
+  <si>
+    <t>Запрос «межкомнатные перегородки» дал 2 лида в СЧ 5774336333 (через автотаргетинг), а в ВЧ эта группа: 18 кликов, 2 468 ₽, 0 лидов. Переносим фразу под объявление и посадочную, которые конвертят. Остальные 7 ВЧ-групп «Межкомнатные | ...» (0 лидов) не переносим.</t>
+  </si>
+  <si>
+    <t>14.10: показы новой группы &gt; 0; 04.11: лиды СЧ по «межкомнатные» не упали</t>
+  </si>
+  <si>
+    <t>[межкомнатные] [перегородки] -гармошка -дверью -заказ -зеркальные -каскадная -квартиру -купить -металлические -москве -производителя -раздвижные -стеклянные -цена</t>
+  </si>
+  <si>
+    <t>07.10 (шаг 2, после копий в СЧ)</t>
+  </si>
+  <si>
+    <t>Остановить после того, как новые группы в СЧ прошли модерацию</t>
+  </si>
+  <si>
+    <t>Семейство «Межкомнатные» в ВЧ: 53 клика, 6 680 ₽, 0 лидов. Тот же спрос дал 5 лидов в СЧ. ВЧ упирается в НБ - высвобожденные деньги пойдут раздвижным и дверям.</t>
+  </si>
+  <si>
+    <t>14.10: лиды СЧ по «стеклянным» и «межкомнатным» не упали</t>
+  </si>
+  <si>
+    <t>5774336214</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки | Заказ</t>
+  </si>
+  <si>
+    <t>[межкомнатные] [перегородки] [заказ]</t>
+  </si>
+  <si>
+    <t>5774336215</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки | Купить</t>
+  </si>
+  <si>
+    <t>[межкомнатные] [перегородки] [купить]</t>
+  </si>
+  <si>
+    <t>5774336216</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки | Цена</t>
+  </si>
+  <si>
+    <t>[межкомнатные] [перегородки] [цена]</t>
+  </si>
+  <si>
+    <t>5774336217</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки | Москве</t>
+  </si>
+  <si>
+    <t>[межкомнатные] [перегородки] [москве]</t>
+  </si>
+  <si>
+    <t>5774336218</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки | Производителя</t>
+  </si>
+  <si>
+    <t>[межкомнатные] [перегородки] [производителя]</t>
+  </si>
+  <si>
+    <t>5774336219</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки | Квартиру</t>
+  </si>
+  <si>
+    <t>[межкомнатные] [перегородки] [квартиру]</t>
+  </si>
+  <si>
+    <t>5774336220</t>
+  </si>
+  <si>
+    <t>Межкомнатные перегородки | Стеклянные</t>
+  </si>
+  <si>
+    <t>[стеклянные] [межкомнатные] [перегородки]</t>
+  </si>
+  <si>
+    <t>База ВЧ: 20 кликов, 2 998 ₽, 0 лидов, отказы 68%, позиция 4. Этот спрос конвертит в СЧ «Интерьерные | Стеклянные» (13 лидов).</t>
+  </si>
+  <si>
+    <t>5774336360</t>
+  </si>
+  <si>
+    <t>Дизайнерские перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>Интент «зонирование»: по реальным запросам 380 визитов, 4 лида (CR 1,1%) - худший кластер. У этой группы 0 лидов. Группы зонирования с лидами оставлены.</t>
+  </si>
+  <si>
+    <t>04.11: лиды РК не упали</t>
+  </si>
+  <si>
+    <t>[дизайнерские] [перегородки] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336370</t>
+  </si>
+  <si>
+    <t>Зеркальные перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>[зеркальные] [перегородки] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336382</t>
+  </si>
+  <si>
+    <t>Матовые перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>[матовые] [перегородки] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336407</t>
+  </si>
+  <si>
+    <t>Каскадные перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>[каскадная] [перегородка] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336430</t>
+  </si>
+  <si>
+    <t>Стальные перегородки | Металлические Зонирования</t>
+  </si>
+  <si>
+    <t>[металлические] [перегородки] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336436</t>
+  </si>
+  <si>
+    <t>Стационарные перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>[стационарная] [перегородка] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336449</t>
+  </si>
+  <si>
+    <t>Перегородки для гостиной | Зонирования</t>
+  </si>
+  <si>
+    <t>[перегородки] [для] [зонирования] [гостиной]</t>
+  </si>
+  <si>
+    <t>5774336228</t>
+  </si>
+  <si>
+    <t>Перегородки для зонирования комнаты | Пространства</t>
+  </si>
+  <si>
+    <t>[перегородки] [зонирования] [пространства]</t>
+  </si>
+  <si>
+    <t>5774336255</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>[раздвижные] [перегородки] [зонирования] -комнаты -межкомнатные</t>
+  </si>
+  <si>
+    <t>5774336257</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Межкомнатные Зонирования</t>
+  </si>
+  <si>
+    <t>[раздвижные] [межкомнатные] [перегородки] [зонирования]</t>
+  </si>
+  <si>
+    <t>5774336377</t>
+  </si>
+  <si>
+    <t>Перегородки стекло металл</t>
+  </si>
+  <si>
+    <t>КОРРЕКТИРОВКА −30%</t>
+  </si>
+  <si>
+    <t>Корректировка ставки −30% на смартфоны, ПК, планшеты (вместо паузы)</t>
+  </si>
+  <si>
+    <t>Вариант ФЕНИКСА вместо остановки: CR 3,4% (средний уровень), дорогой только клик - 223 ₽ против 119 ₽ по НЧ. Один из двух лидов - «стеклянные двери в москве на заказ». Снижаем цену клика, не теряя спрос.</t>
+  </si>
+  <si>
+    <t>21.10: CPC группы ≤ 170 ₽; если лидов 0 и расход &gt; 2 CPL - пауза</t>
+  </si>
+  <si>
+    <t>[перегородки] [стекло] [металл] -лофт</t>
+  </si>
+  <si>
+    <t>5774336335</t>
+  </si>
+  <si>
+    <t>Интерьерные перегородки | Стеклянные</t>
+  </si>
+  <si>
+    <t>КОРРЕКТИРОВКА +40%</t>
+  </si>
+  <si>
+    <t>+40% на смартфоны, ПК, планшеты</t>
+  </si>
+  <si>
+    <t>13 лида, CPL 2032 ₽ (среднее 3622 ₽), объём трафика 69 (цель 85+), премиум 42% показов, позиция 2.6. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
+  </si>
+  <si>
+    <t>14.10: объём ≥ 85, CPC рост ≤ 25%; 04.11: CPL группы ≤ 1,3× текущего</t>
+  </si>
+  <si>
+    <t>[интерьерные] [стеклянные] [перегородки]</t>
+  </si>
+  <si>
+    <t>5774336419</t>
+  </si>
+  <si>
+    <t>Складные перегородки</t>
+  </si>
+  <si>
+    <t>КОРРЕКТИРОВКА +25%</t>
+  </si>
+  <si>
+    <t>+25% на смартфоны, ПК, планшеты</t>
+  </si>
+  <si>
+    <t>5 лида, CPL 1047 ₽ (среднее 3622 ₽), объём трафика 80 (цель 85+), премиум 64% показов, позиция 2.9. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
+  </si>
+  <si>
+    <t>[складные] [перегородки] -гармошка -заказ -зонирования -москве -стеклянные -цена</t>
+  </si>
+  <si>
+    <t>5774336333</t>
+  </si>
+  <si>
+    <t>Интерьерные перегородки | Купить</t>
+  </si>
+  <si>
+    <t>4 лида, CPL 1361 ₽ (среднее 3622 ₽), объём трафика 77 (цель 85+), премиум 37% показов, позиция 2. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
+  </si>
+  <si>
+    <t>[интерьерные] [перегородки] [купить]</t>
+  </si>
+  <si>
+    <t>5774336299</t>
+  </si>
+  <si>
+    <t>Перегородки с дверью</t>
+  </si>
+  <si>
+    <t>3 лида, CPL 2040 ₽ (среднее 3622 ₽), объём трафика 70 (цель 85+), премиум 57% показов, позиция 3.4. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
+  </si>
+  <si>
+    <t>[перегородки] [дверью] -арочная -заказ -купить -лофт -маятниковой -межкомнатная -раздвижной -распашной -стеклянные -цена</t>
+  </si>
+  <si>
+    <t>5774336337</t>
+  </si>
+  <si>
+    <t>Интерьерные перегородки | Зонирования</t>
+  </si>
+  <si>
+    <t>3 лида, CPL 2365 ₽ (среднее 3622 ₽), объём трафика 77 (цель 85+), премиум 47% показов, позиция 2.4. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
+  </si>
+  <si>
+    <t>[интерьерные] [перегородки] [зонирования]</t>
+  </si>
+  <si>
+    <t>после решения по НБ ВЧ</t>
+  </si>
+  <si>
+    <t>5774336269</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Стеклянные Двери</t>
+  </si>
+  <si>
+    <t>КОРРЕКТИРОВКА +40% (только если НБ ВЧ поднят)</t>
+  </si>
+  <si>
+    <t>+40% на все устройства, при условии НБ ВЧ 5 000 → 6 000 ₽</t>
+  </si>
+  <si>
+    <t>3 лида, CPL 1507 ₽, объём 66, премиум 84% показов. ВЧ с 17.08 выбирает НБ полностью: без прибавки НБ корректировка только перераспределит деньги внутри ВЧ (замечание ФЕНИКСА).</t>
+  </si>
+  <si>
+    <t>14.10: объём ≥ 80; 04.11: CPL группы ≤ 2 500 ₽</t>
+  </si>
+  <si>
+    <t>[стеклянные] [раздвижные] [двери] [перегородки]</t>
+  </si>
+  <si>
+    <t>5774336374</t>
+  </si>
+  <si>
+    <t>Зеркальные перегородки | Раздвижные</t>
+  </si>
+  <si>
+    <t>2 лида, CPL 926 ₽ (среднее 3622 ₽), объём трафика 80 (цель 85+), премиум 60% показов, позиция 2.7. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
+  </si>
+  <si>
+    <t>[зеркальные] [раздвижные] [перегородки]</t>
+  </si>
+  <si>
+    <t>5774336424</t>
+  </si>
+  <si>
+    <t>Стальные перегородки | Металлические</t>
+  </si>
+  <si>
+    <t>2 лида, CPL 1099 ₽ (среднее 3622 ₽), объём трафика 76 (цель 85+), премиум 61% показов, позиция 3.1. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
+  </si>
+  <si>
+    <t>[металлические] [перегородки] -зонирования -межкомнатные -стеллаж -черные</t>
+  </si>
+  <si>
+    <t>5774336287</t>
+  </si>
+  <si>
+    <t>Лофт перегородки</t>
+  </si>
+  <si>
+    <t>2 лида, CPL 1021 ₽ (среднее 3622 ₽), объём трафика 77 (цель 85+), премиум 48% показов, позиция 2.4. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
+  </si>
+  <si>
+    <t>[лофт] [перегородки] -дверью -заказ -зонирования -купить -производителя -раздвижные -стеклянные -стеллаж -стиле -цена</t>
+  </si>
+  <si>
+    <t>(кампания)</t>
+  </si>
+  <si>
+    <t>Настройки РК</t>
+  </si>
+  <si>
+    <t>СТРАТЕГИЯ</t>
+  </si>
+  <si>
+    <t>Средняя цена клика 108 → 120 ₽ (НБ 9 000 не менять)</t>
+  </si>
+  <si>
+    <t>Фактический CPC 102 ₽ без НДС при лимите 108 ₽. Без запаса корректировки +25…+40% заставят стратегию срезать ставки другим группам. Деньги на повышения высвобождают паузы стеллажей и гармошек (~2,3 т.р./нед).</t>
+  </si>
+  <si>
+    <t>14.10: НБ выбирается ≤ 100%, CPC РК ≤ 120 ₽</t>
+  </si>
+  <si>
+    <t>РЕШЕНИЕ ИВАНА</t>
+  </si>
+  <si>
+    <t>НБ 5 000 → 6 000 ₽ без НДС (+~1 220 ₽/нед с НДС) - или оставить 5 000</t>
+  </si>
+  <si>
+    <t>С 17.08 НБ выбирается на 100%. Рычаг объёма в ВЧ - бюджет, а не корректировки. Паузы «Межкомнатных» и базы «Стеклянные» высвобождают ~1,2 т.р./нед внутри ВЧ - этого может хватить без прибавки.</t>
+  </si>
+  <si>
+    <t>14.10: доля выбора НБ, лиды раздвижных</t>
+  </si>
+  <si>
+    <t>Уровень</t>
+  </si>
+  <si>
+    <t>Минус-фраза</t>
+  </si>
+  <si>
+    <t>НЧ, ВЧ</t>
+  </si>
+  <si>
+    <t>уровень кампании</t>
+  </si>
+  <si>
+    <t>-"стеклянные перегородки"</t>
+  </si>
+  <si>
+    <t>Закрепление общих стеклянных запросов за СЧ. Проверка ФЕНИКСА: под блок в НЧ/ВЧ попадает 4-7% визитов, 0 лидов; эти же запросы дали 8 лидов в СЧ. Добавлять только после фраз в СЧ 5774336335 (этап 2). Как Яндекс применяет кавычки в минус-фразах - сверить в справке.</t>
+  </si>
+  <si>
+    <t>-"стеклянная перегородка"</t>
+  </si>
+  <si>
+    <t>-"перегородки +из стекла"</t>
+  </si>
+  <si>
+    <t>-"стеклянные перегородки +на заказ"</t>
+  </si>
+  <si>
+    <t>-"перегородки +из стекла +на заказ"</t>
+  </si>
+  <si>
+    <t>-"стеклянные перегородки москва"</t>
+  </si>
+  <si>
+    <t>-"изготовление стеклянных перегородок"</t>
+  </si>
+  <si>
+    <t>-"производство перегородок +из стекла"</t>
+  </si>
+  <si>
+    <t>-"стена +из стекла"</t>
+  </si>
+  <si>
+    <t>-"стеклянная межкомнатная перегородка"</t>
+  </si>
+  <si>
+    <t>-"стеклянные перегородки +в квартиру"</t>
+  </si>
+  <si>
+    <t>-"стеклянная перегородка +в комнату"</t>
+  </si>
+  <si>
+    <t>-"межкомнатные перегородки"</t>
+  </si>
+  <si>
+    <t>Запрос дал 2 лида в СЧ «Интерьерные | Купить». Добавить после фразы в СЧ.</t>
+  </si>
+  <si>
+    <t>-офис</t>
+  </si>
+  <si>
+    <t>Офисные запросы в матовых и стационарных: 0 лидов.</t>
+  </si>
+  <si>
+    <t>-офисные</t>
+  </si>
+  <si>
+    <t>-столов</t>
+  </si>
+  <si>
+    <t>-готовые</t>
+  </si>
+  <si>
+    <t>-гармошка</t>
+  </si>
+  <si>
+    <t>После паузы гармошек в СЧ, чтобы автотаргетинг других групп СЧ не подбирал этот спрос. Слово «складные» не минусуем: в СЧ его нет.</t>
+  </si>
+  <si>
+    <t>-книжка</t>
+  </si>
+  <si>
+    <t>Правило</t>
+  </si>
+  <si>
+    <t>Содержание</t>
+  </si>
+  <si>
+    <t>Недельный стоп-кран (каждый понедельник)</t>
+  </si>
+  <si>
+    <t>Если за 7 дней лидов 3 РК &lt; 3 и CPC 3 РК вырос &gt; 20% к базе - откатить последний этап.</t>
+  </si>
+  <si>
+    <t>База для сравнения</t>
+  </si>
+  <si>
+    <t>6 недель до 29.09: 17.08-27.09 (лиды по меткам, расход с НДС). Двухнедельные окна слишком шумные (19 / 15 / 16 / 10 лидов).</t>
+  </si>
+  <si>
+    <t>Быстрые метрики (06.10, 14.10)</t>
+  </si>
+  <si>
+    <t>Клики, CPC, объём трафика, доля премиум-показов, отказы, выбор НБ. По ним решаем, откатывать ли корректировки и паузы.</t>
+  </si>
+  <si>
+    <t>Решение по лидам и CPL</t>
+  </si>
+  <si>
+    <t>Не раньше 4-6 недель после этапа 2: 04.11-18.11. До этого лиды не показатель (мало данных).</t>
+  </si>
+  <si>
+    <t>Правило остановки группы / семейства</t>
+  </si>
+  <si>
+    <t>0 лидов при расходе ≥ 2 CPL (≈ 7 200 ₽) и 100+ кликах - пауза. Проверять раз в неделю для Каскадных, Арочных, Матовых, Стационарных, Для гостиной, Для студии (НЧ).</t>
+  </si>
+  <si>
+    <t>Двери (новые группы)</t>
+  </si>
+  <si>
+    <t>Не запускать до сверки 72 лидов с CRM (BORIS): 23 «дверных» лида - три разных продукта. Домашние РК по подкластерам: «перегородка с дверью» - СЧ, «складные двери / гармошка» - НЧ, «раздвижные / сдвижные стеклянные двери» - ВЧ. Потолок 2 CPL на группу.</t>
+  </si>
+  <si>
+    <t>Первое место (бывшая H4)</t>
+  </si>
+  <si>
+    <t>Не делаем: разница CR по позициям в пределах случайности, 95% интервал допускает, что 1-е место лучше.</t>
+  </si>
+  <si>
+    <t>P0-флаг атрибуции</t>
+  </si>
+  <si>
+    <t>По данным ФЕНИКСА, открыт с 08.07: скрипт записи в Директ через API заблокирован, изменения вносятся вручную в интерфейсе после апрува Ивана или после закрытия флага Иваном.</t>
+  </si>
+  <si>
+    <t>Исполнитель / апрув</t>
+  </si>
+  <si>
+    <t>Исполнитель: специалист по Директу (ТИМУР по ростеру). Апрув каждого этапа: Иван. Отметка о выполнении - в дневнике ведения Директа (Google Таблица), дата снятия = колонка «Проверка».</t>
+  </si>
+  <si>
+    <t>Интент</t>
+  </si>
+  <si>
+    <t>Лиды (метки)</t>
+  </si>
+  <si>
+    <t>Уточнение исполнения</t>
+  </si>
+  <si>
+    <t>Зонирование</t>
+  </si>
+  <si>
+    <t>5774336226</t>
+  </si>
+  <si>
+    <t>Перегородки | Установкой</t>
+  </si>
+  <si>
+    <t>Заказ / покупка</t>
+  </si>
+  <si>
+    <t>без изменений</t>
+  </si>
+  <si>
+    <t>5774336236</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Стеклянные</t>
+  </si>
+  <si>
+    <t>5774336237</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Межкомнатные</t>
+  </si>
+  <si>
+    <t>Помещение</t>
+  </si>
+  <si>
+    <t>Базовый тип</t>
+  </si>
+  <si>
+    <t>5774336221</t>
+  </si>
+  <si>
+    <t>Перегородки | Заказ</t>
+  </si>
+  <si>
+    <t>5774336235</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки</t>
+  </si>
+  <si>
+    <t>5774336263</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Гардеробной</t>
+  </si>
+  <si>
+    <t>5774336227</t>
+  </si>
+  <si>
+    <t>Перегородки для зонирования комнаты</t>
+  </si>
+  <si>
+    <t>5774336240</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Заказ</t>
+  </si>
+  <si>
+    <t>5774336256</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Зонирования Комнаты</t>
+  </si>
+  <si>
+    <t>5774336267</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Вместо Двери</t>
+  </si>
+  <si>
+    <t>5774336246</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Монтажом</t>
+  </si>
+  <si>
+    <t>5774336224</t>
+  </si>
+  <si>
+    <t>Перегородки | Производство Перегородок</t>
+  </si>
+  <si>
+    <t>5774336245</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Установкой</t>
+  </si>
+  <si>
+    <t>5774336242</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Стоимость</t>
+  </si>
+  <si>
+    <t>5774336223</t>
+  </si>
+  <si>
+    <t>Перегородки | Изготовление Перегородок</t>
+  </si>
+  <si>
+    <t>5774336230</t>
+  </si>
+  <si>
+    <t>Перегородки для зонирования комнаты | Купить</t>
+  </si>
+  <si>
+    <t>5774336249</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Производителя</t>
+  </si>
+  <si>
+    <t>5774336262</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Между Комнатой Кухней</t>
+  </si>
+  <si>
+    <t>Цена</t>
+  </si>
+  <si>
+    <t>5774336241</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Заказать</t>
+  </si>
+  <si>
+    <t>5774336258</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Квартиру</t>
+  </si>
+  <si>
+    <t>5774336265</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Москве</t>
+  </si>
+  <si>
+    <t>5774336277</t>
+  </si>
+  <si>
+    <t>Стеклянные перегородки | Цена</t>
+  </si>
+  <si>
+    <t>5774336276</t>
+  </si>
+  <si>
+    <t>Стеклянные перегородки | Купить</t>
+  </si>
+  <si>
+    <t>5774336268</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Стеклянная Комнату</t>
+  </si>
+  <si>
+    <t>5774336275</t>
+  </si>
+  <si>
+    <t>Стеклянные перегородки | Заказ</t>
+  </si>
+  <si>
+    <t>5774336225</t>
+  </si>
+  <si>
+    <t>Перегородки | Ключ</t>
+  </si>
+  <si>
+    <t>5774336278</t>
+  </si>
+  <si>
+    <t>Стеклянные перегородки | Квартиру</t>
+  </si>
+  <si>
+    <t>5774336238</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Купить</t>
+  </si>
+  <si>
+    <t>5774336252</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Недорого</t>
+  </si>
+  <si>
+    <t>5774336239</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Цена</t>
+  </si>
+  <si>
+    <t>5774336250</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Размерам</t>
+  </si>
+  <si>
+    <t>5774336233</t>
+  </si>
+  <si>
+    <t>Перегородки для зонирования комнаты | Стеклянные</t>
+  </si>
+  <si>
+    <t>5774336231</t>
+  </si>
+  <si>
+    <t>Перегородки для зонирования комнаты | Заказ</t>
+  </si>
+  <si>
+    <t>5774336251</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Заказ Размерам</t>
+  </si>
+  <si>
+    <t>5774336280</t>
+  </si>
+  <si>
+    <t>Стеклянные перегородки | Производителя</t>
+  </si>
+  <si>
+    <t>Гео</t>
+  </si>
+  <si>
+    <t>5774336253</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Рассчитать Стоимость</t>
+  </si>
+  <si>
+    <t>5774336279</t>
+  </si>
+  <si>
+    <t>Стеклянные перегородки | Москве</t>
+  </si>
+  <si>
+    <t>5774336271</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Роликах</t>
+  </si>
+  <si>
+    <t>5774336232</t>
+  </si>
+  <si>
+    <t>Перегородки для зонирования комнаты | Цена</t>
+  </si>
+  <si>
+    <t>5774336248</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Производство</t>
+  </si>
+  <si>
+    <t>5774336270</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Купе</t>
+  </si>
+  <si>
+    <t>5774336272</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Направляющих</t>
+  </si>
+  <si>
+    <t>5774336243</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Сколько Стоит</t>
+  </si>
+  <si>
+    <t>5774336266</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Проем</t>
+  </si>
+  <si>
+    <t>5774336261</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Между Кухней Гостиной</t>
+  </si>
+  <si>
+    <t>5774336229</t>
+  </si>
+  <si>
+    <t>Перегородки для зонирования комнаты | Квартиры</t>
+  </si>
+  <si>
+    <t>5774336222</t>
+  </si>
+  <si>
+    <t>Перегородки | Заказ Размерам</t>
+  </si>
+  <si>
+    <t>5774336234</t>
+  </si>
+  <si>
+    <t>Перегородки для зонирования комнаты | Студии</t>
+  </si>
+  <si>
+    <t>5774336244</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Ключ</t>
+  </si>
+  <si>
+    <t>5774336247</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Изготовление</t>
+  </si>
+  <si>
+    <t>5774336254</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Замер</t>
+  </si>
+  <si>
+    <t>5774336259</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Студию</t>
+  </si>
+  <si>
+    <t>5774336260</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Гостиную</t>
+  </si>
+  <si>
+    <t>5774336264</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Офиса</t>
+  </si>
+  <si>
+    <t>5774336273</t>
+  </si>
+  <si>
+    <t>Раздвижные перегородки | Откатные</t>
+  </si>
+  <si>
     <t>5774336420</t>
   </si>
   <si>
     <t>Складные перегородки | Гармошка</t>
-  </si>
-  <si>
-    <t>ДОБАВИТЬ ФРАЗЫ</t>
-  </si>
-  <si>
-    <t>Добавить фразы (все со словом «гармошка», разделение со «Складными» сохраняется): [перегородка] [гармошка] / [перегородки] [гармошка] [межкомнатные] / [дверь] [гармошка] / [дверь] [гармошка] [заказ]</t>
-  </si>
-  <si>
-    <t>Сейчас фраза группы [складные] [перегородки] [гармошка] дала 7 кликов из 120, остальные 113 - автотаргетинг. Лиды пришли по «дверь гармошка на заказ», «перегородка гармошка», «межкомнатные перегородки гармошка». Фразы переводят этот спрос из автотаргетинга в управляемые ключи. Базовая «Складные» 5774336419 их не заберёт: у неё минус-слово «гармошка» на группе. Это и принимающий ключ перед паузой гармошек в СЧ.</t>
-  </si>
-  <si>
-    <t>14.10: клики по новым фразам &gt; 0, доля автотаргетинга в группе &lt; 70%, CPC ≤ 150 ₽</t>
-  </si>
-  <si>
-    <t>[складные] [перегородки] [гармошка]</t>
-  </si>
-  <si>
-    <t>07.10 (после фраз в НЧ)</t>
-  </si>
-  <si>
-    <t>5774336314</t>
-  </si>
-  <si>
-    <t>Перегородки-гармошки</t>
-  </si>
-  <si>
-    <t>Остановить после добавления фраз в НЧ 5774336420</t>
-  </si>
-  <si>
-    <t>Один и тот же спрос «гармошка» покупают две РК: запросы с «гармошка» в НЧ - 129 визитов, 5 лидов; в СЧ - 142 визита, 2 лида. В СЧ-гармошках слово «складные» есть лишь в 2 кликах из 179 - это не складные, а именно гармошки и двери-гармошки. Оставляем спрос в НЧ, где он конвертит лучше. У группы есть лид - остановка как дубль, спрос забирает НЧ 5774336420.</t>
-  </si>
-  <si>
-    <t>14.10 и 04.11: лиды по «гармошка» в НЧ не ниже, чем было суммарно в НЧ+СЧ</t>
-  </si>
-  <si>
-    <t>[перегородки] [гармошка] -заказ -зонирования -купить -межкомнатная -складные -стеклянные</t>
-  </si>
-  <si>
-    <t>5774336315</t>
-  </si>
-  <si>
-    <t>Перегородки-гармошки | Купить</t>
-  </si>
-  <si>
-    <t>Один и тот же спрос «гармошка» покупают две РК: запросы с «гармошка» в НЧ - 129 визитов, 5 лидов; в СЧ - 142 визита, 2 лида. В СЧ-гармошках слово «складные» есть лишь в 2 кликах из 179 - это не складные, а именно гармошки и двери-гармошки. Оставляем спрос в НЧ, где он конвертит лучше.</t>
-  </si>
-  <si>
-    <t>[перегородка] [гармошка] [купить]</t>
-  </si>
-  <si>
-    <t>5774336316</t>
-  </si>
-  <si>
-    <t>Перегородки-гармошки | Заказ</t>
-  </si>
-  <si>
-    <t>[перегородки] [гармошка] [заказ]</t>
-  </si>
-  <si>
-    <t>5774336317</t>
-  </si>
-  <si>
-    <t>Перегородки-гармошки | Зонирования</t>
-  </si>
-  <si>
-    <t>[перегородка] [гармошка] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336318</t>
-  </si>
-  <si>
-    <t>Перегородки-гармошки | Межкомнатная</t>
-  </si>
-  <si>
-    <t>[перегородка] [гармошка] [межкомнатная]</t>
-  </si>
-  <si>
-    <t>5774336319</t>
-  </si>
-  <si>
-    <t>Перегородки-гармошки | Книжка</t>
-  </si>
-  <si>
-    <t>[перегородка] [книжка]</t>
-  </si>
-  <si>
-    <t>07.10</t>
-  </si>
-  <si>
-    <t>5774336417</t>
-  </si>
-  <si>
-    <t>Складные перегородки | Заказ</t>
-  </si>
-  <si>
-    <t>ВЫКЛЮЧИТЬ АВТОТАРГЕТИНГ</t>
-  </si>
-  <si>
-    <t>Выключить автотаргетинг в группе, фразу оставить (группу не останавливать)</t>
-  </si>
-  <si>
-    <t>Фраза группы ни разу не сработала, все клики - автотаргетинг, и он приводит сюда общие запросы базовой группы («складная перегородка», «межкомнатные перегородки складные»): 0 лидов. Без автотаргетинга группа ловит только свои «заказ / цена», остальное уходит в базовую 5774336419 (5 лидов, CPL 1 047). Разделение сохраняется, фразу базовой группы не трогаем.</t>
-  </si>
-  <si>
-    <t>14.10: у группы расход ≈ 0 или только запросы с «заказ / цена»; клики базовой 5774336419 выросли</t>
-  </si>
-  <si>
-    <t>[складные] [перегородки] [заказ]</t>
-  </si>
-  <si>
-    <t>5774336421</t>
-  </si>
-  <si>
-    <t>Складные перегородки | Цена</t>
-  </si>
-  <si>
-    <t>[складные] [перегородки] [цена]</t>
-  </si>
-  <si>
-    <t>5774336418</t>
-  </si>
-  <si>
-    <t>Складные перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>Остановить</t>
-  </si>
-  <si>
-    <t>Интент «зонирование»: 12 кликов, 579 ₽, 0 лидов. По всем РК зонирование - худший кластер (CR 1,1%).</t>
-  </si>
-  <si>
-    <t>04.11: лиды семейства «Складные» не упали</t>
-  </si>
-  <si>
-    <t>[складные] [перегородки] [зонирования]</t>
-  </si>
-  <si>
-    <t>07.10 (до пауз в ВЧ)</t>
-  </si>
-  <si>
-    <t>5774336335</t>
-  </si>
-  <si>
-    <t>Интерьерные перегородки | Стеклянные</t>
-  </si>
-  <si>
-    <t>Добавить фразы: «[стеклянные] [перегородки]», «стеклянная перегородка в комнату», «стеклянные перегородки на заказ»</t>
-  </si>
-  <si>
-    <t>Принимающий ключ для общих стеклянных запросов: сейчас в СЧ нет ключа под «стеклянные перегородки», закрепление держится только на автотаргетинге (замечание ФЕНИКСА). Группа даёт 13 лидов при CPL 2 032 ₽.</t>
-  </si>
-  <si>
-    <t>14.10: показы по новым фразам, CPL группы не выше 2 500 ₽</t>
-  </si>
-  <si>
-    <t>[интерьерные] [стеклянные] [перегородки]</t>
-  </si>
-  <si>
-    <t>5774336333</t>
-  </si>
-  <si>
-    <t>Интерьерные перегородки | Купить</t>
-  </si>
-  <si>
-    <t>ДОБАВИТЬ ФРАЗУ</t>
-  </si>
-  <si>
-    <t>Добавить фразу «[межкомнатные] [перегородки]»</t>
-  </si>
-  <si>
-    <t>Запрос «межкомнатные перегородки» дал 2 лида именно в этой группе. Принимающий ключ перед паузой 8 групп «Межкомнатные» в ВЧ.</t>
-  </si>
-  <si>
-    <t>14.10: показы по фразе &gt; 0</t>
-  </si>
-  <si>
-    <t>[интерьерные] [перегородки] [купить]</t>
-  </si>
-  <si>
-    <t>07.10 (после фраз в СЧ)</t>
-  </si>
-  <si>
-    <t>ВЧ</t>
-  </si>
-  <si>
-    <t>712877513</t>
-  </si>
-  <si>
-    <t>5774336213</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки</t>
-  </si>
-  <si>
-    <t>Остановить после добавления фраз в СЧ 5774336335 и «Купить»</t>
-  </si>
-  <si>
-    <t>Семейство «Межкомнатные» в ВЧ: 53 клика, 6 680 ₽, 0 лидов. Тот же спрос дал 5 лидов в СЧ. ВЧ упирается в НБ - высвобожденные деньги пойдут раздвижным и дверям.</t>
-  </si>
-  <si>
-    <t>14.10: лиды СЧ по «стеклянным» и «межкомнатным» не упали</t>
-  </si>
-  <si>
-    <t>[межкомнатные] [перегородки] -гармошка -дверью -заказ -зеркальные -каскадная -квартиру -купить -металлические -москве -производителя -раздвижные -стеклянные -цена</t>
-  </si>
-  <si>
-    <t>5774336214</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки | Заказ</t>
-  </si>
-  <si>
-    <t>[межкомнатные] [перегородки] [заказ]</t>
-  </si>
-  <si>
-    <t>5774336215</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки | Купить</t>
-  </si>
-  <si>
-    <t>[межкомнатные] [перегородки] [купить]</t>
-  </si>
-  <si>
-    <t>5774336216</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки | Цена</t>
-  </si>
-  <si>
-    <t>[межкомнатные] [перегородки] [цена]</t>
-  </si>
-  <si>
-    <t>5774336217</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки | Москве</t>
-  </si>
-  <si>
-    <t>[межкомнатные] [перегородки] [москве]</t>
-  </si>
-  <si>
-    <t>5774336218</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки | Производителя</t>
-  </si>
-  <si>
-    <t>[межкомнатные] [перегородки] [производителя]</t>
-  </si>
-  <si>
-    <t>5774336219</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки | Квартиру</t>
-  </si>
-  <si>
-    <t>[межкомнатные] [перегородки] [квартиру]</t>
-  </si>
-  <si>
-    <t>5774336220</t>
-  </si>
-  <si>
-    <t>Межкомнатные перегородки | Стеклянные</t>
-  </si>
-  <si>
-    <t>[стеклянные] [межкомнатные] [перегородки]</t>
-  </si>
-  <si>
-    <t>5774336274</t>
-  </si>
-  <si>
-    <t>Стеклянные перегородки</t>
-  </si>
-  <si>
-    <t>База ВЧ: 20 кликов, 2 998 ₽, 0 лидов, отказы 68%, позиция 4. Этот спрос конвертит в СЧ «Интерьерные | Стеклянные» (13 лидов).</t>
-  </si>
-  <si>
-    <t>[стеклянные] [перегородки] -арочные -гармошка -гостиной -дверью -дизайнерские -заказ -зонирования -интерьерные -квартиру -купить -кухни -лофт -межкомнатные -москве -производителя -раздвижные -распашные -складные -студии -телескопические -цена</t>
-  </si>
-  <si>
-    <t>5774336360</t>
-  </si>
-  <si>
-    <t>Дизайнерские перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>Интент «зонирование»: по реальным запросам 380 визитов, 4 лида (CR 1,1%) - худший кластер. У этой группы 0 лидов. Группы зонирования с лидами оставлены.</t>
-  </si>
-  <si>
-    <t>04.11: лиды РК не упали</t>
-  </si>
-  <si>
-    <t>[дизайнерские] [перегородки] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336370</t>
-  </si>
-  <si>
-    <t>Зеркальные перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>[зеркальные] [перегородки] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336382</t>
-  </si>
-  <si>
-    <t>Матовые перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>[матовые] [перегородки] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336407</t>
-  </si>
-  <si>
-    <t>Каскадные перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>[каскадная] [перегородка] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336430</t>
-  </si>
-  <si>
-    <t>Стальные перегородки | Металлические Зонирования</t>
-  </si>
-  <si>
-    <t>[металлические] [перегородки] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336436</t>
-  </si>
-  <si>
-    <t>Стационарные перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>[стационарная] [перегородка] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336449</t>
-  </si>
-  <si>
-    <t>Перегородки для гостиной | Зонирования</t>
-  </si>
-  <si>
-    <t>[перегородки] [для] [зонирования] [гостиной]</t>
-  </si>
-  <si>
-    <t>5774336228</t>
-  </si>
-  <si>
-    <t>Перегородки для зонирования комнаты | Пространства</t>
-  </si>
-  <si>
-    <t>[перегородки] [зонирования] [пространства]</t>
-  </si>
-  <si>
-    <t>5774336255</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>[раздвижные] [перегородки] [зонирования] -комнаты -межкомнатные</t>
-  </si>
-  <si>
-    <t>5774336257</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Межкомнатные Зонирования</t>
-  </si>
-  <si>
-    <t>[раздвижные] [межкомнатные] [перегородки] [зонирования]</t>
-  </si>
-  <si>
-    <t>5774336377</t>
-  </si>
-  <si>
-    <t>Перегородки стекло металл</t>
-  </si>
-  <si>
-    <t>КОРРЕКТИРОВКА −30%</t>
-  </si>
-  <si>
-    <t>Корректировка ставки −30% на смартфоны, ПК, планшеты (вместо паузы)</t>
-  </si>
-  <si>
-    <t>Вариант ФЕНИКСА вместо остановки: CR 3,4% (средний уровень), дорогой только клик - 223 ₽ против 119 ₽ по НЧ. Один из двух лидов - «стеклянные двери в москве на заказ». Снижаем цену клика, не теряя спрос.</t>
-  </si>
-  <si>
-    <t>21.10: CPC группы ≤ 170 ₽; если лидов 0 и расход &gt; 2 CPL - пауза</t>
-  </si>
-  <si>
-    <t>[перегородки] [стекло] [металл] -лофт</t>
-  </si>
-  <si>
-    <t>КОРРЕКТИРОВКА +40%</t>
-  </si>
-  <si>
-    <t>+40% на смартфоны, ПК, планшеты</t>
-  </si>
-  <si>
-    <t>13 лида, CPL 2032 ₽ (среднее 3622 ₽), объём трафика 69 (цель 85+), премиум 42% показов, позиция 2.6. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
-  </si>
-  <si>
-    <t>14.10: объём ≥ 85, CPC рост ≤ 25%; 04.11: CPL группы ≤ 1,3× текущего</t>
-  </si>
-  <si>
-    <t>5774336419</t>
-  </si>
-  <si>
-    <t>Складные перегородки</t>
-  </si>
-  <si>
-    <t>КОРРЕКТИРОВКА +25%</t>
-  </si>
-  <si>
-    <t>+25% на смартфоны, ПК, планшеты</t>
-  </si>
-  <si>
-    <t>5 лида, CPL 1047 ₽ (среднее 3622 ₽), объём трафика 80 (цель 85+), премиум 64% показов, позиция 2.9. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
-  </si>
-  <si>
-    <t>[складные] [перегородки] -гармошка -заказ -зонирования -москве -стеклянные -цена</t>
-  </si>
-  <si>
-    <t>4 лида, CPL 1361 ₽ (среднее 3622 ₽), объём трафика 77 (цель 85+), премиум 37% показов, позиция 2. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
-  </si>
-  <si>
-    <t>5774336299</t>
-  </si>
-  <si>
-    <t>Перегородки с дверью</t>
-  </si>
-  <si>
-    <t>3 лида, CPL 2040 ₽ (среднее 3622 ₽), объём трафика 70 (цель 85+), премиум 57% показов, позиция 3.4. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
-  </si>
-  <si>
-    <t>[перегородки] [дверью] -арочная -заказ -купить -лофт -маятниковой -межкомнатная -раздвижной -распашной -стеклянные -цена</t>
-  </si>
-  <si>
-    <t>5774336337</t>
-  </si>
-  <si>
-    <t>Интерьерные перегородки | Зонирования</t>
-  </si>
-  <si>
-    <t>3 лида, CPL 2365 ₽ (среднее 3622 ₽), объём трафика 77 (цель 85+), премиум 47% показов, позиция 2.4. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
-  </si>
-  <si>
-    <t>[интерьерные] [перегородки] [зонирования]</t>
-  </si>
-  <si>
-    <t>после решения по НБ ВЧ</t>
-  </si>
-  <si>
-    <t>5774336269</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Стеклянные Двери</t>
-  </si>
-  <si>
-    <t>КОРРЕКТИРОВКА +40% (только если НБ ВЧ поднят)</t>
-  </si>
-  <si>
-    <t>+40% на все устройства, при условии НБ ВЧ 5 000 → 6 000 ₽</t>
-  </si>
-  <si>
-    <t>3 лида, CPL 1507 ₽, объём 66, премиум 84% показов. ВЧ с 17.08 выбирает НБ полностью: без прибавки НБ корректировка только перераспределит деньги внутри ВЧ (замечание ФЕНИКСА).</t>
-  </si>
-  <si>
-    <t>14.10: объём ≥ 80; 04.11: CPL группы ≤ 2 500 ₽</t>
-  </si>
-  <si>
-    <t>[стеклянные] [раздвижные] [двери] [перегородки]</t>
-  </si>
-  <si>
-    <t>5774336374</t>
-  </si>
-  <si>
-    <t>Зеркальные перегородки | Раздвижные</t>
-  </si>
-  <si>
-    <t>2 лида, CPL 926 ₽ (среднее 3622 ₽), объём трафика 80 (цель 85+), премиум 60% показов, позиция 2.7. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
-  </si>
-  <si>
-    <t>[зеркальные] [раздвижные] [перегородки]</t>
-  </si>
-  <si>
-    <t>5774336424</t>
-  </si>
-  <si>
-    <t>Стальные перегородки | Металлические</t>
-  </si>
-  <si>
-    <t>2 лида, CPL 1099 ₽ (среднее 3622 ₽), объём трафика 76 (цель 85+), премиум 61% показов, позиция 3.1. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
-  </si>
-  <si>
-    <t>[металлические] [перегородки] -зонирования -межкомнатные -стеллаж -черные</t>
-  </si>
-  <si>
-    <t>5774336287</t>
-  </si>
-  <si>
-    <t>Лофт перегородки</t>
-  </si>
-  <si>
-    <t>2 лида, CPL 1021 ₽ (среднее 3622 ₽), объём трафика 77 (цель 85+), премиум 48% показов, позиция 2.4. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
-  </si>
-  <si>
-    <t>[лофт] [перегородки] -дверью -заказ -зонирования -купить -производителя -раздвижные -стеклянные -стеллаж -стиле -цена</t>
-  </si>
-  <si>
-    <t>(кампания)</t>
-  </si>
-  <si>
-    <t>Настройки РК</t>
-  </si>
-  <si>
-    <t>СТРАТЕГИЯ</t>
-  </si>
-  <si>
-    <t>Средняя цена клика 108 → 120 ₽ (НБ 9 000 не менять)</t>
-  </si>
-  <si>
-    <t>Фактический CPC 102 ₽ без НДС при лимите 108 ₽. Без запаса корректировки +25…+40% заставят стратегию срезать ставки другим группам. Деньги на повышения высвобождают паузы стеллажей и гармошек (~2,3 т.р./нед).</t>
-  </si>
-  <si>
-    <t>14.10: НБ выбирается ≤ 100%, CPC РК ≤ 120 ₽</t>
-  </si>
-  <si>
-    <t>РЕШЕНИЕ ИВАНА</t>
-  </si>
-  <si>
-    <t>НБ 5 000 → 6 000 ₽ без НДС (+~1 220 ₽/нед с НДС) - или оставить 5 000</t>
-  </si>
-  <si>
-    <t>С 17.08 НБ выбирается на 100%. Рычаг объёма в ВЧ - бюджет, а не корректировки. Паузы «Межкомнатных» и базы «Стеклянные» высвобождают ~1,2 т.р./нед внутри ВЧ - этого может хватить без прибавки.</t>
-  </si>
-  <si>
-    <t>14.10: доля выбора НБ, лиды раздвижных</t>
-  </si>
-  <si>
-    <t>Уровень</t>
-  </si>
-  <si>
-    <t>Минус-фраза</t>
-  </si>
-  <si>
-    <t>НЧ, ВЧ</t>
-  </si>
-  <si>
-    <t>уровень кампании</t>
-  </si>
-  <si>
-    <t>-"стеклянные перегородки"</t>
-  </si>
-  <si>
-    <t>Закрепление общих стеклянных запросов за СЧ. Проверка ФЕНИКСА: под блок в НЧ/ВЧ попадает 4-7% визитов, 0 лидов; эти же запросы дали 8 лидов в СЧ. Добавлять только после фраз в СЧ 5774336335 (этап 2). Как Яндекс применяет кавычки в минус-фразах - сверить в справке.</t>
-  </si>
-  <si>
-    <t>-"стеклянная перегородка"</t>
-  </si>
-  <si>
-    <t>-"перегородки +из стекла"</t>
-  </si>
-  <si>
-    <t>-"стеклянные перегородки +на заказ"</t>
-  </si>
-  <si>
-    <t>-"перегородки +из стекла +на заказ"</t>
-  </si>
-  <si>
-    <t>-"стеклянные перегородки москва"</t>
-  </si>
-  <si>
-    <t>-"изготовление стеклянных перегородок"</t>
-  </si>
-  <si>
-    <t>-"производство перегородок +из стекла"</t>
-  </si>
-  <si>
-    <t>-"стена +из стекла"</t>
-  </si>
-  <si>
-    <t>-"стеклянная межкомнатная перегородка"</t>
-  </si>
-  <si>
-    <t>-"стеклянные перегородки +в квартиру"</t>
-  </si>
-  <si>
-    <t>-"стеклянная перегородка +в комнату"</t>
-  </si>
-  <si>
-    <t>-"межкомнатные перегородки"</t>
-  </si>
-  <si>
-    <t>Запрос дал 2 лида в СЧ «Интерьерные | Купить». Добавить после фразы в СЧ.</t>
-  </si>
-  <si>
-    <t>-офис</t>
-  </si>
-  <si>
-    <t>Офисные запросы в матовых и стационарных: 0 лидов.</t>
-  </si>
-  <si>
-    <t>-офисные</t>
-  </si>
-  <si>
-    <t>-столов</t>
-  </si>
-  <si>
-    <t>-готовые</t>
-  </si>
-  <si>
-    <t>-гармошка</t>
-  </si>
-  <si>
-    <t>После паузы гармошек в СЧ, чтобы автотаргетинг других групп СЧ не подбирал этот спрос. Слово «складные» не минусуем: в СЧ его нет.</t>
-  </si>
-  <si>
-    <t>-книжка</t>
-  </si>
-  <si>
-    <t>Правило</t>
-  </si>
-  <si>
-    <t>Содержание</t>
-  </si>
-  <si>
-    <t>Недельный стоп-кран (каждый понедельник)</t>
-  </si>
-  <si>
-    <t>Если за 7 дней лидов 3 РК &lt; 3 и CPC 3 РК вырос &gt; 20% к базе - откатить последний этап.</t>
-  </si>
-  <si>
-    <t>База для сравнения</t>
-  </si>
-  <si>
-    <t>6 недель до 29.09: 17.08-27.09 (лиды по меткам, расход с НДС). Двухнедельные окна слишком шумные (19 / 15 / 16 / 10 лидов).</t>
-  </si>
-  <si>
-    <t>Быстрые метрики (06.10, 14.10)</t>
-  </si>
-  <si>
-    <t>Клики, CPC, объём трафика, доля премиум-показов, отказы, выбор НБ. По ним решаем, откатывать ли корректировки и паузы.</t>
-  </si>
-  <si>
-    <t>Решение по лидам и CPL</t>
-  </si>
-  <si>
-    <t>Не раньше 4-6 недель после этапа 2: 04.11-18.11. До этого лиды не показатель (мало данных).</t>
-  </si>
-  <si>
-    <t>Правило остановки группы / семейства</t>
-  </si>
-  <si>
-    <t>0 лидов при расходе ≥ 2 CPL (≈ 7 200 ₽) и 100+ кликах - пауза. Проверять раз в неделю для Каскадных, Арочных, Матовых, Стационарных, Для гостиной, Для студии (НЧ).</t>
-  </si>
-  <si>
-    <t>Двери (новые группы)</t>
-  </si>
-  <si>
-    <t>Не запускать до сверки 72 лидов с CRM (BORIS): 23 «дверных» лида - три разных продукта. Домашние РК по подкластерам: «перегородка с дверью» - СЧ, «складные двери / гармошка» - НЧ, «раздвижные / сдвижные стеклянные двери» - ВЧ. Потолок 2 CPL на группу.</t>
-  </si>
-  <si>
-    <t>Первое место (бывшая H4)</t>
-  </si>
-  <si>
-    <t>Не делаем: разница CR по позициям в пределах случайности, 95% интервал допускает, что 1-е место лучше.</t>
-  </si>
-  <si>
-    <t>P0-флаг атрибуции</t>
-  </si>
-  <si>
-    <t>По данным ФЕНИКСА, открыт с 08.07: скрипт записи в Директ через API заблокирован, изменения вносятся вручную в интерфейсе после апрува Ивана или после закрытия флага Иваном.</t>
-  </si>
-  <si>
-    <t>Исполнитель / апрув</t>
-  </si>
-  <si>
-    <t>Исполнитель: специалист по Директу (ТИМУР по ростеру). Апрув каждого этапа: Иван. Отметка о выполнении - в дневнике ведения Директа (Google Таблица), дата снятия = колонка «Проверка».</t>
-  </si>
-  <si>
-    <t>Интент</t>
-  </si>
-  <si>
-    <t>Лиды (метки)</t>
-  </si>
-  <si>
-    <t>Уточнение исполнения</t>
-  </si>
-  <si>
-    <t>Зонирование</t>
-  </si>
-  <si>
-    <t>5774336226</t>
-  </si>
-  <si>
-    <t>Перегородки | Установкой</t>
-  </si>
-  <si>
-    <t>Заказ / покупка</t>
-  </si>
-  <si>
-    <t>без изменений</t>
-  </si>
-  <si>
-    <t>5774336236</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Стеклянные</t>
-  </si>
-  <si>
-    <t>5774336237</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Межкомнатные</t>
-  </si>
-  <si>
-    <t>Помещение</t>
-  </si>
-  <si>
-    <t>Базовый тип</t>
-  </si>
-  <si>
-    <t>5774336221</t>
-  </si>
-  <si>
-    <t>Перегородки | Заказ</t>
-  </si>
-  <si>
-    <t>5774336235</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки</t>
-  </si>
-  <si>
-    <t>5774336263</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Гардеробной</t>
-  </si>
-  <si>
-    <t>5774336227</t>
-  </si>
-  <si>
-    <t>Перегородки для зонирования комнаты</t>
-  </si>
-  <si>
-    <t>5774336240</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Заказ</t>
-  </si>
-  <si>
-    <t>5774336256</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Зонирования Комнаты</t>
-  </si>
-  <si>
-    <t>5774336267</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Вместо Двери</t>
-  </si>
-  <si>
-    <t>5774336246</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Монтажом</t>
-  </si>
-  <si>
-    <t>5774336224</t>
-  </si>
-  <si>
-    <t>Перегородки | Производство Перегородок</t>
-  </si>
-  <si>
-    <t>5774336245</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Установкой</t>
-  </si>
-  <si>
-    <t>5774336242</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Стоимость</t>
-  </si>
-  <si>
-    <t>5774336223</t>
-  </si>
-  <si>
-    <t>Перегородки | Изготовление Перегородок</t>
-  </si>
-  <si>
-    <t>5774336230</t>
-  </si>
-  <si>
-    <t>Перегородки для зонирования комнаты | Купить</t>
-  </si>
-  <si>
-    <t>5774336249</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Производителя</t>
-  </si>
-  <si>
-    <t>5774336262</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Между Комнатой Кухней</t>
-  </si>
-  <si>
-    <t>Цена</t>
-  </si>
-  <si>
-    <t>5774336241</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Заказать</t>
-  </si>
-  <si>
-    <t>5774336258</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Квартиру</t>
-  </si>
-  <si>
-    <t>5774336265</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Москве</t>
-  </si>
-  <si>
-    <t>5774336277</t>
-  </si>
-  <si>
-    <t>Стеклянные перегородки | Цена</t>
-  </si>
-  <si>
-    <t>5774336276</t>
-  </si>
-  <si>
-    <t>Стеклянные перегородки | Купить</t>
-  </si>
-  <si>
-    <t>5774336268</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Стеклянная Комнату</t>
-  </si>
-  <si>
-    <t>5774336275</t>
-  </si>
-  <si>
-    <t>Стеклянные перегородки | Заказ</t>
-  </si>
-  <si>
-    <t>5774336225</t>
-  </si>
-  <si>
-    <t>Перегородки | Ключ</t>
-  </si>
-  <si>
-    <t>5774336278</t>
-  </si>
-  <si>
-    <t>Стеклянные перегородки | Квартиру</t>
-  </si>
-  <si>
-    <t>5774336238</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Купить</t>
-  </si>
-  <si>
-    <t>5774336252</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Недорого</t>
-  </si>
-  <si>
-    <t>5774336239</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Цена</t>
-  </si>
-  <si>
-    <t>5774336250</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Размерам</t>
-  </si>
-  <si>
-    <t>5774336233</t>
-  </si>
-  <si>
-    <t>Перегородки для зонирования комнаты | Стеклянные</t>
-  </si>
-  <si>
-    <t>5774336231</t>
-  </si>
-  <si>
-    <t>Перегородки для зонирования комнаты | Заказ</t>
-  </si>
-  <si>
-    <t>5774336251</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Заказ Размерам</t>
-  </si>
-  <si>
-    <t>5774336280</t>
-  </si>
-  <si>
-    <t>Стеклянные перегородки | Производителя</t>
-  </si>
-  <si>
-    <t>Гео</t>
-  </si>
-  <si>
-    <t>5774336253</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Рассчитать Стоимость</t>
-  </si>
-  <si>
-    <t>5774336279</t>
-  </si>
-  <si>
-    <t>Стеклянные перегородки | Москве</t>
-  </si>
-  <si>
-    <t>5774336271</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Роликах</t>
-  </si>
-  <si>
-    <t>5774336232</t>
-  </si>
-  <si>
-    <t>Перегородки для зонирования комнаты | Цена</t>
-  </si>
-  <si>
-    <t>5774336248</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Производство</t>
-  </si>
-  <si>
-    <t>5774336270</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Купе</t>
-  </si>
-  <si>
-    <t>5774336272</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Направляющих</t>
-  </si>
-  <si>
-    <t>5774336243</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Сколько Стоит</t>
-  </si>
-  <si>
-    <t>5774336266</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Проем</t>
-  </si>
-  <si>
-    <t>5774336261</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Между Кухней Гостиной</t>
-  </si>
-  <si>
-    <t>5774336229</t>
-  </si>
-  <si>
-    <t>Перегородки для зонирования комнаты | Квартиры</t>
-  </si>
-  <si>
-    <t>5774336222</t>
-  </si>
-  <si>
-    <t>Перегородки | Заказ Размерам</t>
-  </si>
-  <si>
-    <t>5774336234</t>
-  </si>
-  <si>
-    <t>Перегородки для зонирования комнаты | Студии</t>
-  </si>
-  <si>
-    <t>5774336244</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Ключ</t>
-  </si>
-  <si>
-    <t>5774336247</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Изготовление</t>
-  </si>
-  <si>
-    <t>5774336254</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Замер</t>
-  </si>
-  <si>
-    <t>5774336259</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Студию</t>
-  </si>
-  <si>
-    <t>5774336260</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Гостиную</t>
-  </si>
-  <si>
-    <t>5774336264</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Офиса</t>
-  </si>
-  <si>
-    <t>5774336273</t>
-  </si>
-  <si>
-    <t>Раздвижные перегородки | Откатные</t>
   </si>
   <si>
     <t>5774336443</t>
@@ -1998,7 +2004,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2013,11 +2019,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBE7E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F0FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -2048,7 +2049,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2066,9 +2067,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2410,7 +2408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S55"/>
+  <dimension ref="A1:S58"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3147,52 +3145,52 @@
         <v>60</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="I13" s="2">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="J13" s="2">
-        <v>16439</v>
+        <v>3936</v>
       </c>
       <c r="K13" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2">
-        <v>4110</v>
+        <v>3936</v>
       </c>
       <c r="M13" s="2">
         <v>87</v>
       </c>
       <c r="N13" s="2">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O13" s="2">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="R13" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="S13" s="2" t="s">
         <v>26</v>
@@ -3203,7 +3201,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>20</v>
@@ -3212,16 +3210,16 @@
         <v>21</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I14" s="2">
         <v>37</v>
@@ -3245,13 +3243,13 @@
         <v>2.7</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>26</v>
@@ -3262,7 +3260,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>20</v>
@@ -3271,16 +3269,16 @@
         <v>21</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>24</v>
+        <v>73</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I15" s="2">
         <v>21</v>
@@ -3304,13 +3302,13 @@
         <v>2.2</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="Q15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="R15" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>26</v>
@@ -3321,7 +3319,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>20</v>
@@ -3330,46 +3328,46 @@
         <v>21</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I16" s="2">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="J16" s="2">
-        <v>5867</v>
+        <v>1406</v>
       </c>
       <c r="K16" s="2">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2">
-        <v>5867</v>
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="M16" s="2">
         <v>89</v>
       </c>
       <c r="N16" s="2">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="O16" s="2">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="R16" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="S16" s="2" t="s">
         <v>26</v>
@@ -3380,7 +3378,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>20</v>
@@ -3389,46 +3387,46 @@
         <v>21</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>24</v>
+        <v>77</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I17" s="2">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="J17" s="2">
-        <v>1501</v>
+        <v>5867</v>
       </c>
       <c r="K17" s="2">
-        <v>0</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>26</v>
+        <v>1</v>
+      </c>
+      <c r="L17" s="2">
+        <v>5867</v>
       </c>
       <c r="M17" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N17" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O17" s="2">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="P17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="R17" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>26</v>
@@ -3439,7 +3437,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>20</v>
@@ -3448,46 +3446,46 @@
         <v>21</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I18" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J18" s="2">
-        <v>3892</v>
+        <v>5867</v>
       </c>
       <c r="K18" s="2">
         <v>1</v>
       </c>
       <c r="L18" s="2">
-        <v>3892</v>
+        <v>5867</v>
       </c>
       <c r="M18" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N18" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="O18" s="2">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="S18" s="2" t="s">
         <v>26</v>
@@ -3498,7 +3496,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>20</v>
@@ -3507,22 +3505,22 @@
         <v>21</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I19" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J19" s="2">
-        <v>2042</v>
+        <v>1501</v>
       </c>
       <c r="K19" s="2">
         <v>0</v>
@@ -3531,22 +3529,22 @@
         <v>26</v>
       </c>
       <c r="M19" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N19" s="2">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="O19" s="2">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>26</v>
@@ -3557,55 +3555,55 @@
         <v>2</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I20" s="2">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="J20" s="2">
-        <v>1774</v>
+        <v>3892</v>
       </c>
       <c r="K20" s="2">
-        <v>0</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>26</v>
+        <v>1</v>
+      </c>
+      <c r="L20" s="2">
+        <v>3892</v>
       </c>
       <c r="M20" s="2">
         <v>88</v>
       </c>
       <c r="N20" s="2">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="O20" s="2">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S20" s="2" t="s">
         <v>26</v>
@@ -3616,55 +3614,55 @@
         <v>2</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="I21" s="2">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="J21" s="2">
-        <v>531</v>
+        <v>3892</v>
       </c>
       <c r="K21" s="2">
-        <v>0</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>26</v>
+        <v>1</v>
+      </c>
+      <c r="L21" s="2">
+        <v>3892</v>
       </c>
       <c r="M21" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N21" s="2">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="O21" s="2">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>26</v>
@@ -3675,31 +3673,31 @@
         <v>2</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="I22" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J22" s="2">
-        <v>579</v>
+        <v>2042</v>
       </c>
       <c r="K22" s="2">
         <v>0</v>
@@ -3708,22 +3706,22 @@
         <v>26</v>
       </c>
       <c r="M22" s="2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="N22" s="2">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="O22" s="2">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="S22" s="2" t="s">
         <v>26</v>
@@ -3734,55 +3732,55 @@
         <v>2</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I23" s="2">
         <v>20</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I23" s="2">
-        <v>135</v>
-      </c>
       <c r="J23" s="2">
-        <v>26421</v>
+        <v>1774</v>
       </c>
       <c r="K23" s="2">
-        <v>13</v>
-      </c>
-      <c r="L23" s="2">
-        <v>2032</v>
+        <v>0</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="M23" s="2">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="N23" s="2">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="O23" s="2">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>26</v>
@@ -3793,55 +3791,55 @@
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>119</v>
+        <v>103</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="I24" s="2">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="J24" s="2">
-        <v>5443</v>
+        <v>531</v>
       </c>
       <c r="K24" s="2">
-        <v>4</v>
-      </c>
-      <c r="L24" s="2">
-        <v>1361</v>
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="M24" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="N24" s="2">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="O24" s="2">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="S24" s="2" t="s">
         <v>26</v>
@@ -3852,31 +3850,31 @@
         <v>2</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="I25" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J25" s="2">
-        <v>2468</v>
+        <v>579</v>
       </c>
       <c r="K25" s="2">
         <v>0</v>
@@ -3885,22 +3883,22 @@
         <v>26</v>
       </c>
       <c r="M25" s="2">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="N25" s="2">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="O25" s="2">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="S25" s="2" t="s">
         <v>26</v>
@@ -3911,31 +3909,31 @@
         <v>2</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>24</v>
+        <v>114</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="I26" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J26" s="2">
-        <v>192</v>
+        <v>2998</v>
       </c>
       <c r="K26" s="2">
         <v>0</v>
@@ -3944,22 +3942,22 @@
         <v>26</v>
       </c>
       <c r="M26" s="2">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N26" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O26" s="2">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="S26" s="2" t="s">
         <v>26</v>
@@ -3970,55 +3968,55 @@
         <v>2</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I27" s="2">
+        <v>18</v>
+      </c>
+      <c r="J27" s="2">
+        <v>2468</v>
+      </c>
+      <c r="K27" s="2">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="2">
+        <v>56</v>
+      </c>
+      <c r="N27" s="2">
+        <v>61</v>
+      </c>
+      <c r="O27" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q27" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="R27" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I27" s="2">
-        <v>14</v>
-      </c>
-      <c r="J27" s="2">
-        <v>1191</v>
-      </c>
-      <c r="K27" s="2">
-        <v>0</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" s="2">
-        <v>76</v>
-      </c>
-      <c r="N27" s="2">
-        <v>29</v>
-      </c>
-      <c r="O27" s="2">
-        <v>2.2</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="R27" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="S27" s="2" t="s">
         <v>26</v>
@@ -4029,55 +4027,55 @@
         <v>2</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I28" s="2">
+        <v>18</v>
+      </c>
+      <c r="J28" s="2">
+        <v>2468</v>
+      </c>
+      <c r="K28" s="2">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="2">
+        <v>56</v>
+      </c>
+      <c r="N28" s="2">
+        <v>61</v>
+      </c>
+      <c r="O28" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q28" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I28" s="2">
-        <v>9</v>
-      </c>
-      <c r="J28" s="2">
-        <v>965</v>
-      </c>
-      <c r="K28" s="2">
-        <v>0</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M28" s="2">
-        <v>72</v>
-      </c>
-      <c r="N28" s="2">
-        <v>51</v>
-      </c>
-      <c r="O28" s="2">
-        <v>2.8</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="R28" s="2" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="S28" s="2" t="s">
         <v>26</v>
@@ -4088,55 +4086,55 @@
         <v>2</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>192</v>
+      </c>
+      <c r="K29" s="2">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="2">
+        <v>60</v>
+      </c>
+      <c r="N29" s="2">
+        <v>74</v>
+      </c>
+      <c r="O29" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q29" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I29" s="2">
-        <v>4</v>
-      </c>
-      <c r="J29" s="2">
-        <v>410</v>
-      </c>
-      <c r="K29" s="2">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="2">
-        <v>58</v>
-      </c>
-      <c r="N29" s="2">
-        <v>93</v>
-      </c>
-      <c r="O29" s="2">
-        <v>3.8</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="R29" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="S29" s="2" t="s">
         <v>26</v>
@@ -4147,55 +4145,55 @@
         <v>2</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I30" s="2">
+        <v>14</v>
+      </c>
+      <c r="J30" s="2">
+        <v>1191</v>
+      </c>
+      <c r="K30" s="2">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30" s="2">
+        <v>76</v>
+      </c>
+      <c r="N30" s="2">
+        <v>29</v>
+      </c>
+      <c r="O30" s="2">
+        <v>2.2</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q30" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I30" s="2">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2">
-        <v>23</v>
-      </c>
-      <c r="K30" s="2">
-        <v>0</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M30" s="2">
-        <v>52</v>
-      </c>
-      <c r="N30" s="2">
-        <v>83</v>
-      </c>
-      <c r="O30" s="2">
-        <v>4.4</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="R30" s="2" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="S30" s="2" t="s">
         <v>26</v>
@@ -4206,55 +4204,55 @@
         <v>2</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H31" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I31" s="2">
+        <v>9</v>
+      </c>
+      <c r="J31" s="2">
+        <v>965</v>
+      </c>
+      <c r="K31" s="2">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="2">
+        <v>72</v>
+      </c>
+      <c r="N31" s="2">
+        <v>51</v>
+      </c>
+      <c r="O31" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q31" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I31" s="2">
-        <v>1</v>
-      </c>
-      <c r="J31" s="2">
-        <v>483</v>
-      </c>
-      <c r="K31" s="2">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" s="2">
-        <v>79</v>
-      </c>
-      <c r="N31" s="2">
-        <v>80</v>
-      </c>
-      <c r="O31" s="2">
-        <v>3</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="R31" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>26</v>
@@ -4265,55 +4263,55 @@
         <v>2</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H32" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I32" s="2">
+        <v>4</v>
+      </c>
+      <c r="J32" s="2">
+        <v>410</v>
+      </c>
+      <c r="K32" s="2">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" s="2">
+        <v>58</v>
+      </c>
+      <c r="N32" s="2">
+        <v>93</v>
+      </c>
+      <c r="O32" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q32" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I32" s="2">
-        <v>5</v>
-      </c>
-      <c r="J32" s="2">
-        <v>949</v>
-      </c>
-      <c r="K32" s="2">
-        <v>0</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M32" s="2">
-        <v>63</v>
-      </c>
-      <c r="N32" s="2">
-        <v>55</v>
-      </c>
-      <c r="O32" s="2">
-        <v>3.3</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="R32" s="2" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="S32" s="2" t="s">
         <v>26</v>
@@ -4324,55 +4322,55 @@
         <v>2</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H33" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I33" s="2">
+        <v>1</v>
+      </c>
+      <c r="J33" s="2">
+        <v>23</v>
+      </c>
+      <c r="K33" s="2">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" s="2">
+        <v>52</v>
+      </c>
+      <c r="N33" s="2">
+        <v>83</v>
+      </c>
+      <c r="O33" s="2">
+        <v>4.4</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q33" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I33" s="2">
-        <v>20</v>
-      </c>
-      <c r="J33" s="2">
-        <v>2998</v>
-      </c>
-      <c r="K33" s="2">
-        <v>0</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" s="2">
-        <v>57</v>
-      </c>
-      <c r="N33" s="2">
-        <v>75</v>
-      </c>
-      <c r="O33" s="2">
-        <v>4</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="R33" s="2" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="S33" s="2" t="s">
         <v>26</v>
@@ -4383,31 +4381,31 @@
         <v>2</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="I34" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J34" s="2">
-        <v>586</v>
+        <v>483</v>
       </c>
       <c r="K34" s="2">
         <v>0</v>
@@ -4416,22 +4414,22 @@
         <v>26</v>
       </c>
       <c r="M34" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="N34" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="O34" s="2">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="S34" s="2" t="s">
         <v>26</v>
@@ -4442,31 +4440,31 @@
         <v>2</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="I35" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J35" s="2">
-        <v>609</v>
+        <v>949</v>
       </c>
       <c r="K35" s="2">
         <v>0</v>
@@ -4475,22 +4473,22 @@
         <v>26</v>
       </c>
       <c r="M35" s="2">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="N35" s="2">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="O35" s="2">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="S35" s="2" t="s">
         <v>26</v>
@@ -4501,31 +4499,31 @@
         <v>2</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="I36" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J36" s="2">
-        <v>1338</v>
+        <v>2998</v>
       </c>
       <c r="K36" s="2">
         <v>0</v>
@@ -4534,22 +4532,22 @@
         <v>26</v>
       </c>
       <c r="M36" s="2">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="N36" s="2">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="O36" s="2">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="S36" s="2" t="s">
         <v>26</v>
@@ -4560,31 +4558,31 @@
         <v>2</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I37" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J37" s="2">
-        <v>432</v>
+        <v>586</v>
       </c>
       <c r="K37" s="2">
         <v>0</v>
@@ -4593,22 +4591,22 @@
         <v>26</v>
       </c>
       <c r="M37" s="2">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="N37" s="2">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="O37" s="2">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="S37" s="2" t="s">
         <v>26</v>
@@ -4619,31 +4617,31 @@
         <v>2</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I38" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J38" s="2">
-        <v>1803</v>
+        <v>609</v>
       </c>
       <c r="K38" s="2">
         <v>0</v>
@@ -4652,22 +4650,22 @@
         <v>26</v>
       </c>
       <c r="M38" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="N38" s="2">
         <v>78</v>
       </c>
       <c r="O38" s="2">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>26</v>
@@ -4678,31 +4676,31 @@
         <v>2</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I39" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J39" s="2">
-        <v>760</v>
+        <v>1338</v>
       </c>
       <c r="K39" s="2">
         <v>0</v>
@@ -4711,22 +4709,22 @@
         <v>26</v>
       </c>
       <c r="M39" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N39" s="2">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="O39" s="2">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="S39" s="2" t="s">
         <v>26</v>
@@ -4737,31 +4735,31 @@
         <v>2</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I40" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J40" s="2">
-        <v>481</v>
+        <v>432</v>
       </c>
       <c r="K40" s="2">
         <v>0</v>
@@ -4770,22 +4768,22 @@
         <v>26</v>
       </c>
       <c r="M40" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="N40" s="2">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O40" s="2">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="S40" s="2" t="s">
         <v>26</v>
@@ -4796,31 +4794,31 @@
         <v>2</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I41" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J41" s="2">
-        <v>231</v>
+        <v>1803</v>
       </c>
       <c r="K41" s="2">
         <v>0</v>
@@ -4829,22 +4827,22 @@
         <v>26</v>
       </c>
       <c r="M41" s="2">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="N41" s="2">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="O41" s="2">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="S41" s="2" t="s">
         <v>26</v>
@@ -4855,31 +4853,31 @@
         <v>2</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I42" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J42" s="2">
-        <v>1650</v>
+        <v>760</v>
       </c>
       <c r="K42" s="2">
         <v>0</v>
@@ -4888,22 +4886,22 @@
         <v>26</v>
       </c>
       <c r="M42" s="2">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="N42" s="2">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="O42" s="2">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="S42" s="2" t="s">
         <v>26</v>
@@ -4914,31 +4912,31 @@
         <v>2</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="D43" s="2" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I43" s="2">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="J43" s="2">
-        <v>3870</v>
+        <v>481</v>
       </c>
       <c r="K43" s="2">
         <v>0</v>
@@ -4947,22 +4945,22 @@
         <v>26</v>
       </c>
       <c r="M43" s="2">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="N43" s="2">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="O43" s="2">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="S43" s="2" t="s">
         <v>26</v>
@@ -4973,55 +4971,55 @@
         <v>2</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I44" s="2">
+        <v>2</v>
+      </c>
+      <c r="J44" s="2">
+        <v>231</v>
+      </c>
+      <c r="K44" s="2">
+        <v>0</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M44" s="2">
         <v>62</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I44" s="2">
-        <v>58</v>
-      </c>
-      <c r="J44" s="2">
-        <v>12949</v>
-      </c>
-      <c r="K44" s="2">
-        <v>2</v>
-      </c>
-      <c r="L44" s="2">
-        <v>6475</v>
-      </c>
-      <c r="M44" s="2">
-        <v>68</v>
-      </c>
       <c r="N44" s="2">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="O44" s="2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="S44" s="2" t="s">
         <v>26</v>
@@ -5029,58 +5027,58 @@
     </row>
     <row r="45" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>197</v>
+        <v>179</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="I45" s="2">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="J45" s="2">
-        <v>26421</v>
+        <v>1650</v>
       </c>
       <c r="K45" s="2">
-        <v>13</v>
-      </c>
-      <c r="L45" s="2">
-        <v>2032</v>
+        <v>0</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="M45" s="2">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="N45" s="2">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="O45" s="2">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>116</v>
+        <v>180</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>26</v>
@@ -5088,58 +5086,58 @@
     </row>
     <row r="46" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>203</v>
+        <v>182</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>204</v>
+        <v>107</v>
       </c>
       <c r="I46" s="2">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="J46" s="2">
-        <v>5233</v>
+        <v>3870</v>
       </c>
       <c r="K46" s="2">
-        <v>5</v>
-      </c>
-      <c r="L46" s="2">
-        <v>1047</v>
+        <v>0</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="M46" s="2">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="N46" s="2">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="O46" s="2">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="S46" s="2" t="s">
         <v>26</v>
@@ -5147,58 +5145,58 @@
     </row>
     <row r="47" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
+        <v>2</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="I47" s="2">
+        <v>58</v>
+      </c>
+      <c r="J47" s="2">
+        <v>12949</v>
+      </c>
+      <c r="K47" s="2">
+        <v>2</v>
+      </c>
+      <c r="L47" s="2">
+        <v>6475</v>
+      </c>
+      <c r="M47" s="2">
+        <v>68</v>
+      </c>
+      <c r="N47" s="2">
+        <v>87</v>
+      </c>
+      <c r="O47" s="2">
         <v>3</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="I47" s="2">
-        <v>35</v>
-      </c>
-      <c r="J47" s="2">
-        <v>5443</v>
-      </c>
-      <c r="K47" s="2">
-        <v>4</v>
-      </c>
-      <c r="L47" s="2">
-        <v>1361</v>
-      </c>
-      <c r="M47" s="2">
-        <v>77</v>
-      </c>
-      <c r="N47" s="2">
-        <v>37</v>
-      </c>
-      <c r="O47" s="2">
-        <v>2</v>
-      </c>
       <c r="P47" s="2" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>123</v>
+        <v>190</v>
       </c>
       <c r="S47" s="2" t="s">
         <v>26</v>
@@ -5209,7 +5207,7 @@
         <v>3</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>20</v>
@@ -5218,46 +5216,46 @@
         <v>21</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G48" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I48" s="2">
+        <v>135</v>
+      </c>
+      <c r="J48" s="2">
+        <v>26421</v>
+      </c>
+      <c r="K48" s="2">
+        <v>13</v>
+      </c>
+      <c r="L48" s="2">
+        <v>2032</v>
+      </c>
+      <c r="M48" s="2">
+        <v>69</v>
+      </c>
+      <c r="N48" s="2">
+        <v>42</v>
+      </c>
+      <c r="O48" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="R48" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I48" s="2">
-        <v>63</v>
-      </c>
-      <c r="J48" s="2">
-        <v>6121</v>
-      </c>
-      <c r="K48" s="2">
-        <v>3</v>
-      </c>
-      <c r="L48" s="2">
-        <v>2040</v>
-      </c>
-      <c r="M48" s="2">
-        <v>70</v>
-      </c>
-      <c r="N48" s="2">
-        <v>57</v>
-      </c>
-      <c r="O48" s="2">
-        <v>3.4</v>
-      </c>
-      <c r="P48" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q48" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="R48" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="S48" s="2" t="s">
         <v>26</v>
@@ -5268,55 +5266,55 @@
         <v>3</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="D49" s="2" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G49" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I49" s="2">
+        <v>52</v>
+      </c>
+      <c r="J49" s="2">
+        <v>5233</v>
+      </c>
+      <c r="K49" s="2">
+        <v>5</v>
+      </c>
+      <c r="L49" s="2">
+        <v>1047</v>
+      </c>
+      <c r="M49" s="2">
+        <v>80</v>
+      </c>
+      <c r="N49" s="2">
+        <v>64</v>
+      </c>
+      <c r="O49" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="R49" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="I49" s="2">
-        <v>60</v>
-      </c>
-      <c r="J49" s="2">
-        <v>7096</v>
-      </c>
-      <c r="K49" s="2">
-        <v>3</v>
-      </c>
-      <c r="L49" s="2">
-        <v>2365</v>
-      </c>
-      <c r="M49" s="2">
-        <v>77</v>
-      </c>
-      <c r="N49" s="2">
-        <v>47</v>
-      </c>
-      <c r="O49" s="2">
-        <v>2.4</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q49" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="R49" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="S49" s="2" t="s">
         <v>26</v>
@@ -5327,55 +5325,55 @@
         <v>3</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>216</v>
+        <v>92</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>219</v>
+        <v>205</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="I50" s="2">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J50" s="2">
-        <v>4522</v>
+        <v>5443</v>
       </c>
       <c r="K50" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L50" s="2">
-        <v>1507</v>
+        <v>1361</v>
       </c>
       <c r="M50" s="2">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="N50" s="2">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="O50" s="2">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="S50" s="2" t="s">
         <v>26</v>
@@ -5386,55 +5384,55 @@
         <v>3</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="I51" s="2">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="J51" s="2">
-        <v>1852</v>
+        <v>6121</v>
       </c>
       <c r="K51" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51" s="2">
-        <v>926</v>
+        <v>2040</v>
       </c>
       <c r="M51" s="2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N51" s="2">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="O51" s="2">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="S51" s="2" t="s">
         <v>26</v>
@@ -5445,55 +5443,55 @@
         <v>3</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>203</v>
+        <v>213</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I52" s="2">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="J52" s="2">
-        <v>2198</v>
+        <v>7096</v>
       </c>
       <c r="K52" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L52" s="2">
-        <v>1099</v>
+        <v>2365</v>
       </c>
       <c r="M52" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N52" s="2">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="O52" s="2">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="S52" s="2" t="s">
         <v>26</v>
@@ -5504,55 +5502,55 @@
         <v>3</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>93</v>
+        <v>216</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>203</v>
+        <v>218</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="I53" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J53" s="2">
-        <v>2041</v>
+        <v>4522</v>
       </c>
       <c r="K53" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L53" s="2">
-        <v>1021</v>
+        <v>1507</v>
       </c>
       <c r="M53" s="2">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N53" s="2">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="O53" s="2">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="S53" s="2" t="s">
         <v>26</v>
@@ -5563,55 +5561,55 @@
         <v>3</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="D54" s="2" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>238</v>
+        <v>225</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N54" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O54" s="2" t="s">
-        <v>26</v>
+        <v>201</v>
+      </c>
+      <c r="I54" s="2">
+        <v>16</v>
+      </c>
+      <c r="J54" s="2">
+        <v>1852</v>
+      </c>
+      <c r="K54" s="2">
+        <v>2</v>
+      </c>
+      <c r="L54" s="2">
+        <v>926</v>
+      </c>
+      <c r="M54" s="2">
+        <v>80</v>
+      </c>
+      <c r="N54" s="2">
+        <v>60</v>
+      </c>
+      <c r="O54" s="2">
+        <v>2.7</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>241</v>
+        <v>196</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>26</v>
+        <v>227</v>
       </c>
       <c r="S54" s="2" t="s">
         <v>26</v>
@@ -5622,57 +5620,234 @@
         <v>3</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="D55" s="2" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="E55" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I55" s="2">
+        <v>25</v>
+      </c>
+      <c r="J55" s="2">
+        <v>2198</v>
+      </c>
+      <c r="K55" s="2">
+        <v>2</v>
+      </c>
+      <c r="L55" s="2">
+        <v>1099</v>
+      </c>
+      <c r="M55" s="2">
+        <v>76</v>
+      </c>
+      <c r="N55" s="2">
+        <v>61</v>
+      </c>
+      <c r="O55" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>3</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I56" s="2">
+        <v>14</v>
+      </c>
+      <c r="J56" s="2">
+        <v>2041</v>
+      </c>
+      <c r="K56" s="2">
+        <v>2</v>
+      </c>
+      <c r="L56" s="2">
+        <v>1021</v>
+      </c>
+      <c r="M56" s="2">
+        <v>77</v>
+      </c>
+      <c r="N56" s="2">
+        <v>48</v>
+      </c>
+      <c r="O56" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="R56" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="S56" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>3</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F57" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="G55" s="5" t="s">
+      <c r="G57" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>3</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G58" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H58" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="I55" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O55" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P55" s="2" t="s">
+      <c r="I58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P58" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="Q55" s="2" t="s">
+      <c r="Q58" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="R55" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="S55" s="2" t="s">
+      <c r="R58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S58" s="2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -5878,7 +6053,7 @@
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>249</v>
@@ -5892,7 +6067,7 @@
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>249</v>
@@ -5906,7 +6081,7 @@
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>249</v>
@@ -5920,7 +6095,7 @@
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>249</v>
@@ -5934,7 +6109,7 @@
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>249</v>
@@ -6136,10 +6311,10 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
         <v>217</v>
@@ -6177,16 +6352,16 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E3" t="s">
         <v>296</v>
@@ -6218,10 +6393,10 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
         <v>297</v>
@@ -6259,10 +6434,10 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
         <v>301</v>
@@ -6300,10 +6475,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C6" t="s">
         <v>303</v>
@@ -6341,16 +6516,16 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C7" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
         <v>306</v>
@@ -6382,16 +6557,16 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
         <v>305</v>
@@ -6423,10 +6598,10 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C9" t="s">
         <v>307</v>
@@ -6464,10 +6639,10 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
         <v>309</v>
@@ -6505,10 +6680,10 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C11" t="s">
         <v>311</v>
@@ -6546,10 +6721,10 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
         <v>313</v>
@@ -6587,10 +6762,10 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C13" t="s">
         <v>315</v>
@@ -6628,10 +6803,10 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
         <v>317</v>
@@ -6669,16 +6844,16 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D15" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E15" t="s">
         <v>296</v>
@@ -6710,10 +6885,10 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C16" t="s">
         <v>319</v>
@@ -6751,10 +6926,10 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C17" t="s">
         <v>321</v>
@@ -6792,10 +6967,10 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C18" t="s">
         <v>323</v>
@@ -6833,16 +7008,16 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E19" t="s">
         <v>299</v>
@@ -6874,10 +7049,10 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
         <v>325</v>
@@ -6915,10 +7090,10 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B21" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
         <v>327</v>
@@ -6956,10 +7131,10 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B22" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
         <v>329</v>
@@ -6997,10 +7172,10 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C23" t="s">
         <v>331</v>
@@ -7038,10 +7213,10 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
         <v>333</v>
@@ -7079,10 +7254,10 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
         <v>335</v>
@@ -7120,16 +7295,16 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E26" t="s">
         <v>337</v>
@@ -7161,16 +7336,16 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C27" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D27" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E27" t="s">
         <v>305</v>
@@ -7202,10 +7377,10 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s">
         <v>338</v>
@@ -7243,10 +7418,10 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s">
         <v>340</v>
@@ -7284,10 +7459,10 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
         <v>342</v>
@@ -7325,10 +7500,10 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B31" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
         <v>344</v>
@@ -7366,10 +7541,10 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s">
         <v>346</v>
@@ -7407,10 +7582,10 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C33" t="s">
         <v>348</v>
@@ -7448,10 +7623,10 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
         <v>350</v>
@@ -7489,10 +7664,10 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B35" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C35" t="s">
         <v>352</v>
@@ -7530,10 +7705,10 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B36" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C36" t="s">
         <v>354</v>
@@ -7571,10 +7746,10 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B37" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C37" t="s">
         <v>356</v>
@@ -7612,10 +7787,10 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
         <v>358</v>
@@ -7653,10 +7828,10 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s">
         <v>360</v>
@@ -7694,10 +7869,10 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
         <v>362</v>
@@ -7735,16 +7910,16 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B41" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C41" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D41" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E41" t="s">
         <v>305</v>
@@ -7776,10 +7951,10 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B42" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C42" t="s">
         <v>364</v>
@@ -7817,10 +7992,10 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
         <v>366</v>
@@ -7858,10 +8033,10 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B44" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
         <v>368</v>
@@ -7899,10 +8074,10 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B45" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
         <v>370</v>
@@ -7940,16 +8115,16 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B46" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C46" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D46" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E46" t="s">
         <v>372</v>
@@ -7981,10 +8156,10 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B47" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C47" t="s">
         <v>373</v>
@@ -8022,10 +8197,10 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B48" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
         <v>375</v>
@@ -8063,10 +8238,10 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C49" t="s">
         <v>377</v>
@@ -8104,10 +8279,10 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C50" t="s">
         <v>379</v>
@@ -8145,16 +8320,16 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C51" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D51" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E51" t="s">
         <v>296</v>
@@ -8186,10 +8361,10 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B52" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C52" t="s">
         <v>381</v>
@@ -8227,16 +8402,16 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B53" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C53" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D53" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E53" t="s">
         <v>299</v>
@@ -8268,10 +8443,10 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B54" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C54" t="s">
         <v>383</v>
@@ -8309,10 +8484,10 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B55" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C55" t="s">
         <v>385</v>
@@ -8350,10 +8525,10 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C56" t="s">
         <v>387</v>
@@ -8391,10 +8566,10 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B57" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C57" t="s">
         <v>389</v>
@@ -8432,10 +8607,10 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B58" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C58" t="s">
         <v>391</v>
@@ -8473,10 +8648,10 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B59" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C59" t="s">
         <v>393</v>
@@ -8514,16 +8689,16 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B60" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C60" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D60" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E60" t="s">
         <v>299</v>
@@ -8555,10 +8730,10 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C61" t="s">
         <v>395</v>
@@ -8596,10 +8771,10 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B62" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C62" t="s">
         <v>397</v>
@@ -8637,10 +8812,10 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C63" t="s">
         <v>399</v>
@@ -8678,10 +8853,10 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B64" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C64" t="s">
         <v>401</v>
@@ -8719,10 +8894,10 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B65" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C65" t="s">
         <v>403</v>
@@ -8760,10 +8935,10 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B66" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C66" t="s">
         <v>405</v>
@@ -8801,10 +8976,10 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B67" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C67" t="s">
         <v>407</v>
@@ -8842,10 +9017,10 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B68" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C68" t="s">
         <v>409</v>
@@ -8883,10 +9058,10 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B69" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="C69" t="s">
         <v>411</v>
@@ -8924,16 +9099,16 @@
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B70" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
-        <v>63</v>
+        <v>413</v>
       </c>
       <c r="D70" t="s">
-        <v>64</v>
+        <v>414</v>
       </c>
       <c r="E70" t="s">
         <v>295</v>
@@ -8960,21 +9135,21 @@
         <v>2.6</v>
       </c>
       <c r="M70" t="s">
-        <v>65</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B71" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D71" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E71" t="s">
         <v>295</v>
@@ -9001,21 +9176,21 @@
         <v>3</v>
       </c>
       <c r="M71" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B72" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C72" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D72" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E72" t="s">
         <v>306</v>
@@ -9042,21 +9217,21 @@
         <v>2.9</v>
       </c>
       <c r="M72" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B73" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C73" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D73" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E73" t="s">
         <v>305</v>
@@ -9088,16 +9263,16 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B74" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C74" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D74" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E74" t="s">
         <v>306</v>
@@ -9129,16 +9304,16 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B75" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C75" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D75" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E75" t="s">
         <v>295</v>
@@ -9170,10 +9345,10 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B76" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C76" t="s">
         <v>228</v>
@@ -9206,21 +9381,21 @@
         <v>3.1</v>
       </c>
       <c r="M76" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B77" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C77" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D77" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E77" t="s">
         <v>306</v>
@@ -9252,10 +9427,10 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B78" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C78" t="s">
         <v>224</v>
@@ -9288,21 +9463,21 @@
         <v>2.7</v>
       </c>
       <c r="M78" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C79" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D79" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E79" t="s">
         <v>296</v>
@@ -9334,16 +9509,16 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B80" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C80" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D80" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E80" t="s">
         <v>306</v>
@@ -9375,16 +9550,16 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B81" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C81" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D81" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E81" t="s">
         <v>299</v>
@@ -9411,21 +9586,21 @@
         <v>2.7</v>
       </c>
       <c r="M81" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B82" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C82" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D82" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E82" t="s">
         <v>295</v>
@@ -9457,16 +9632,16 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B83" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C83" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D83" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E83" t="s">
         <v>299</v>
@@ -9498,16 +9673,16 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B84" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C84" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D84" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E84" t="s">
         <v>372</v>
@@ -9539,16 +9714,16 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B85" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C85" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D85" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E85" t="s">
         <v>299</v>
@@ -9580,16 +9755,16 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C86" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D86" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E86" t="s">
         <v>305</v>
@@ -9621,16 +9796,16 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C87" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D87" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E87" t="s">
         <v>306</v>
@@ -9662,16 +9837,16 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C88" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D88" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E88" t="s">
         <v>296</v>
@@ -9703,16 +9878,16 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B89" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C89" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D89" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E89" t="s">
         <v>305</v>
@@ -9744,16 +9919,16 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D90" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E90" t="s">
         <v>299</v>
@@ -9785,16 +9960,16 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B91" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C91" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D91" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E91" t="s">
         <v>337</v>
@@ -9826,16 +10001,16 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C92" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D92" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E92" t="s">
         <v>305</v>
@@ -9867,16 +10042,16 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C93" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D93" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E93" t="s">
         <v>306</v>
@@ -9908,16 +10083,16 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C94" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D94" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E94" t="s">
         <v>305</v>
@@ -9949,16 +10124,16 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C95" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D95" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E95" t="s">
         <v>295</v>
@@ -9990,16 +10165,16 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B96" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D96" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E96" t="s">
         <v>295</v>
@@ -10031,16 +10206,16 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C97" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D97" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E97" t="s">
         <v>305</v>
@@ -10072,16 +10247,16 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B98" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C98" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D98" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E98" t="s">
         <v>306</v>
@@ -10113,16 +10288,16 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B99" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C99" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D99" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E99" t="s">
         <v>306</v>
@@ -10154,16 +10329,16 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B100" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C100" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D100" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E100" t="s">
         <v>295</v>
@@ -10195,16 +10370,16 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B101" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C101" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D101" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E101" t="s">
         <v>305</v>
@@ -10236,16 +10411,16 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B102" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C102" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D102" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E102" t="s">
         <v>296</v>
@@ -10277,16 +10452,16 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B103" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C103" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D103" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E103" t="s">
         <v>305</v>
@@ -10318,16 +10493,16 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B104" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C104" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D104" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E104" t="s">
         <v>306</v>
@@ -10359,16 +10534,16 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B105" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C105" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D105" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E105" t="s">
         <v>295</v>
@@ -10400,16 +10575,16 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B106" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C106" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D106" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E106" t="s">
         <v>337</v>
@@ -10441,16 +10616,16 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B107" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C107" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D107" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E107" t="s">
         <v>337</v>
@@ -10482,16 +10657,16 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B108" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C108" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D108" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E108" t="s">
         <v>299</v>
@@ -10523,16 +10698,16 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B109" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C109" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D109" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E109" t="s">
         <v>306</v>
@@ -10564,16 +10739,16 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B110" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C110" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D110" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E110" t="s">
         <v>295</v>
@@ -10605,16 +10780,16 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B111" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C111" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D111" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E111" t="s">
         <v>295</v>
@@ -10646,16 +10821,16 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B112" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C112" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D112" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E112" t="s">
         <v>306</v>
@@ -10687,16 +10862,16 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B113" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C113" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D113" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E113" t="s">
         <v>299</v>
@@ -10728,16 +10903,16 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B114" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C114" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D114" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E114" t="s">
         <v>296</v>
@@ -10769,16 +10944,16 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B115" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C115" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D115" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E115" t="s">
         <v>306</v>
@@ -10810,16 +10985,16 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B116" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C116" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D116" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E116" t="s">
         <v>296</v>
@@ -10851,16 +11026,16 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B117" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C117" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D117" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E117" t="s">
         <v>296</v>
@@ -10892,16 +11067,16 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B118" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C118" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D118" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E118" t="s">
         <v>299</v>
@@ -10933,16 +11108,16 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B119" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C119" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D119" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E119" t="s">
         <v>337</v>
@@ -10969,21 +11144,21 @@
         <v>2.4</v>
       </c>
       <c r="M119" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B120" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C120" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D120" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E120" t="s">
         <v>306</v>
@@ -11015,16 +11190,16 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B121" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C121" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D121" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E121" t="s">
         <v>305</v>
@@ -11056,16 +11231,16 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B122" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C122" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D122" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E122" t="s">
         <v>299</v>
@@ -11097,16 +11272,16 @@
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B123" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C123" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D123" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E123" t="s">
         <v>372</v>
@@ -11138,16 +11313,16 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B124" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C124" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D124" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E124" t="s">
         <v>296</v>
@@ -11179,16 +11354,16 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B125" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C125" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D125" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E125" t="s">
         <v>295</v>
@@ -11220,16 +11395,16 @@
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B126" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C126" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D126" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E126" t="s">
         <v>305</v>
@@ -11261,16 +11436,16 @@
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B127" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C127" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D127" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E127" t="s">
         <v>296</v>
@@ -11302,16 +11477,16 @@
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B128" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C128" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D128" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E128" t="s">
         <v>372</v>
@@ -11343,16 +11518,16 @@
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B129" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C129" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D129" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E129" t="s">
         <v>299</v>
@@ -11384,16 +11559,16 @@
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B130" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C130" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D130" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E130" t="s">
         <v>299</v>
@@ -11425,16 +11600,16 @@
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B131" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C131" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D131" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E131" t="s">
         <v>295</v>
@@ -11466,16 +11641,16 @@
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B132" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C132" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D132" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E132" t="s">
         <v>299</v>
@@ -11507,16 +11682,16 @@
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B133" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C133" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D133" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E133" t="s">
         <v>299</v>
@@ -11548,16 +11723,16 @@
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B134" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C134" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D134" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E134" t="s">
         <v>372</v>
@@ -11589,16 +11764,16 @@
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B135" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C135" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D135" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E135" t="s">
         <v>299</v>
@@ -11630,16 +11805,16 @@
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B136" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C136" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D136" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E136" t="s">
         <v>305</v>
@@ -11671,16 +11846,16 @@
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B137" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C137" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D137" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E137" t="s">
         <v>299</v>
@@ -11712,16 +11887,16 @@
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B138" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C138" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D138" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E138" t="s">
         <v>299</v>
@@ -11753,16 +11928,16 @@
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B139" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C139" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D139" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E139" t="s">
         <v>295</v>
@@ -11794,16 +11969,16 @@
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B140" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C140" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D140" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E140" t="s">
         <v>299</v>
@@ -11835,16 +12010,16 @@
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B141" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C141" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D141" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E141" t="s">
         <v>306</v>
@@ -11876,16 +12051,16 @@
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B142" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C142" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D142" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E142" t="s">
         <v>299</v>
@@ -11917,16 +12092,16 @@
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B143" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C143" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D143" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E143" t="s">
         <v>306</v>
@@ -11958,16 +12133,16 @@
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B144" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C144" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D144" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E144" t="s">
         <v>299</v>
@@ -11999,16 +12174,16 @@
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B145" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C145" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D145" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E145" t="s">
         <v>299</v>
@@ -12040,16 +12215,16 @@
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B146" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C146" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D146" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E146" t="s">
         <v>295</v>
@@ -12081,16 +12256,16 @@
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B147" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C147" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D147" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E147" t="s">
         <v>337</v>
@@ -12122,16 +12297,16 @@
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B148" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C148" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D148" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E148" t="s">
         <v>299</v>
@@ -12163,16 +12338,16 @@
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B149" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C149" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D149" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E149" t="s">
         <v>295</v>
@@ -12204,16 +12379,16 @@
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B150" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C150" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D150" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E150" t="s">
         <v>299</v>
@@ -12245,16 +12420,16 @@
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B151" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C151" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D151" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E151" t="s">
         <v>337</v>
@@ -12286,16 +12461,16 @@
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B152" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C152" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D152" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E152" t="s">
         <v>372</v>
@@ -12327,16 +12502,16 @@
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B153" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C153" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D153" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E153" t="s">
         <v>295</v>
@@ -12368,16 +12543,16 @@
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B154" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C154" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D154" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E154" t="s">
         <v>299</v>
@@ -12409,16 +12584,16 @@
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B155" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C155" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D155" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E155" t="s">
         <v>337</v>
@@ -12450,16 +12625,16 @@
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B156" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C156" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D156" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E156" t="s">
         <v>372</v>
@@ -12491,16 +12666,16 @@
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B157" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C157" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D157" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E157" t="s">
         <v>337</v>
@@ -12532,16 +12707,16 @@
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B158" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C158" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D158" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E158" t="s">
         <v>295</v>
@@ -12573,16 +12748,16 @@
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B159" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C159" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D159" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E159" t="s">
         <v>299</v>
@@ -12614,16 +12789,16 @@
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B160" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C160" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D160" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E160" t="s">
         <v>372</v>
@@ -12655,16 +12830,16 @@
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B161" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C161" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D161" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E161" t="s">
         <v>295</v>
@@ -12696,16 +12871,16 @@
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B162" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C162" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D162" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E162" t="s">
         <v>296</v>
@@ -12737,16 +12912,16 @@
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B163" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C163" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D163" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E163" t="s">
         <v>299</v>
@@ -12778,16 +12953,16 @@
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B164" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C164" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D164" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E164" t="s">
         <v>306</v>
@@ -12819,16 +12994,16 @@
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B165" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C165" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D165" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E165" t="s">
         <v>306</v>
@@ -12860,16 +13035,16 @@
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B166" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C166" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D166" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E166" t="s">
         <v>299</v>
@@ -12901,16 +13076,16 @@
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B167" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C167" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D167" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E167" t="s">
         <v>295</v>
@@ -12942,16 +13117,16 @@
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B168" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C168" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D168" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E168" t="s">
         <v>295</v>
@@ -12983,16 +13158,16 @@
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B169" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C169" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D169" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E169" t="s">
         <v>299</v>
@@ -13024,16 +13199,16 @@
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B170" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C170" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D170" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E170" t="s">
         <v>306</v>
@@ -13065,16 +13240,16 @@
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B171" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C171" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D171" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E171" t="s">
         <v>337</v>
@@ -13106,16 +13281,16 @@
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B172" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C172" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D172" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E172" t="s">
         <v>299</v>
@@ -13147,16 +13322,16 @@
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B173" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C173" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D173" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E173" t="s">
         <v>305</v>
@@ -13188,16 +13363,16 @@
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B174" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C174" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D174" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E174" t="s">
         <v>299</v>
@@ -13229,16 +13404,16 @@
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B175" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C175" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D175" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E175" t="s">
         <v>305</v>
@@ -13276,10 +13451,10 @@
         <v>21</v>
       </c>
       <c r="C176" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="D176" t="s">
-        <v>112</v>
+        <v>192</v>
       </c>
       <c r="E176" t="s">
         <v>295</v>
@@ -13306,7 +13481,7 @@
         <v>2.6</v>
       </c>
       <c r="M176" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">
@@ -13347,7 +13522,7 @@
         <v>2.4</v>
       </c>
       <c r="M177" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.25">
@@ -13388,7 +13563,7 @@
         <v>3.4</v>
       </c>
       <c r="M178" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.25">
@@ -13399,10 +13574,10 @@
         <v>21</v>
       </c>
       <c r="C179" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D179" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E179" t="s">
         <v>299</v>
@@ -13440,10 +13615,10 @@
         <v>21</v>
       </c>
       <c r="C180" t="s">
-        <v>117</v>
+        <v>204</v>
       </c>
       <c r="D180" t="s">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="E180" t="s">
         <v>299</v>
@@ -13470,7 +13645,7 @@
         <v>2</v>
       </c>
       <c r="M180" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.25">
@@ -13481,10 +13656,10 @@
         <v>21</v>
       </c>
       <c r="C181" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D181" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E181" t="s">
         <v>306</v>
@@ -13522,10 +13697,10 @@
         <v>21</v>
       </c>
       <c r="C182" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D182" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E182" t="s">
         <v>305</v>
@@ -13563,10 +13738,10 @@
         <v>21</v>
       </c>
       <c r="C183" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D183" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E183" t="s">
         <v>306</v>
@@ -13604,10 +13779,10 @@
         <v>21</v>
       </c>
       <c r="C184" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D184" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="E184" t="s">
         <v>372</v>
@@ -13686,10 +13861,10 @@
         <v>21</v>
       </c>
       <c r="C186" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D186" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E186" t="s">
         <v>295</v>
@@ -13768,10 +13943,10 @@
         <v>21</v>
       </c>
       <c r="C188" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D188" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E188" t="s">
         <v>306</v>
@@ -13839,7 +14014,7 @@
         <v>2.4</v>
       </c>
       <c r="M189" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.25">
@@ -13850,10 +14025,10 @@
         <v>21</v>
       </c>
       <c r="C190" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D190" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E190" t="s">
         <v>295</v>
@@ -13891,10 +14066,10 @@
         <v>21</v>
       </c>
       <c r="C191" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D191" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E191" t="s">
         <v>296</v>
@@ -13932,10 +14107,10 @@
         <v>21</v>
       </c>
       <c r="C192" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D192" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E192" t="s">
         <v>295</v>
@@ -13973,10 +14148,10 @@
         <v>21</v>
       </c>
       <c r="C193" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D193" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E193" t="s">
         <v>299</v>
@@ -14055,10 +14230,10 @@
         <v>21</v>
       </c>
       <c r="C195" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D195" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E195" t="s">
         <v>296</v>
@@ -14096,10 +14271,10 @@
         <v>21</v>
       </c>
       <c r="C196" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D196" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E196" t="s">
         <v>337</v>
@@ -14137,10 +14312,10 @@
         <v>21</v>
       </c>
       <c r="C197" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D197" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E197" t="s">
         <v>295</v>
@@ -14178,10 +14353,10 @@
         <v>21</v>
       </c>
       <c r="C198" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D198" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E198" t="s">
         <v>372</v>
@@ -14219,10 +14394,10 @@
         <v>21</v>
       </c>
       <c r="C199" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D199" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E199" t="s">
         <v>299</v>
@@ -14260,10 +14435,10 @@
         <v>21</v>
       </c>
       <c r="C200" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D200" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E200" t="s">
         <v>295</v>
@@ -14383,10 +14558,10 @@
         <v>21</v>
       </c>
       <c r="C203" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D203" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E203" t="s">
         <v>295</v>
@@ -14465,10 +14640,10 @@
         <v>21</v>
       </c>
       <c r="C205" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D205" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E205" t="s">
         <v>299</v>
@@ -14506,10 +14681,10 @@
         <v>21</v>
       </c>
       <c r="C206" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D206" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E206" t="s">
         <v>299</v>
@@ -14547,10 +14722,10 @@
         <v>21</v>
       </c>
       <c r="C207" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D207" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E207" t="s">
         <v>337</v>
@@ -14588,10 +14763,10 @@
         <v>21</v>
       </c>
       <c r="C208" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D208" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E208" t="s">
         <v>299</v>
@@ -14629,10 +14804,10 @@
         <v>21</v>
       </c>
       <c r="C209" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D209" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E209" t="s">
         <v>299</v>
@@ -14670,10 +14845,10 @@
         <v>21</v>
       </c>
       <c r="C210" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D210" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E210" t="s">
         <v>337</v>
@@ -14711,10 +14886,10 @@
         <v>21</v>
       </c>
       <c r="C211" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D211" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E211" t="s">
         <v>295</v>
@@ -14752,10 +14927,10 @@
         <v>21</v>
       </c>
       <c r="C212" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D212" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E212" t="s">
         <v>295</v>
@@ -14793,10 +14968,10 @@
         <v>21</v>
       </c>
       <c r="C213" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D213" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E213" t="s">
         <v>295</v>
@@ -14875,10 +15050,10 @@
         <v>21</v>
       </c>
       <c r="C215" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D215" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E215" t="s">
         <v>299</v>
@@ -14916,10 +15091,10 @@
         <v>21</v>
       </c>
       <c r="C216" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D216" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E216" t="s">
         <v>295</v>
@@ -14957,10 +15132,10 @@
         <v>21</v>
       </c>
       <c r="C217" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D217" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E217" t="s">
         <v>295</v>
@@ -15039,10 +15214,10 @@
         <v>21</v>
       </c>
       <c r="C219" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D219" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E219" t="s">
         <v>305</v>
@@ -15121,10 +15296,10 @@
         <v>21</v>
       </c>
       <c r="C221" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D221" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E221" t="s">
         <v>295</v>
@@ -15162,10 +15337,10 @@
         <v>21</v>
       </c>
       <c r="C222" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D222" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E222" t="s">
         <v>295</v>
@@ -15244,10 +15419,10 @@
         <v>21</v>
       </c>
       <c r="C224" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D224" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E224" t="s">
         <v>295</v>
@@ -15285,10 +15460,10 @@
         <v>21</v>
       </c>
       <c r="C225" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D225" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E225" t="s">
         <v>295</v>
@@ -15326,10 +15501,10 @@
         <v>21</v>
       </c>
       <c r="C226" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D226" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E226" t="s">
         <v>299</v>

--- a/yandex-direct/audit/2026-09-28-deystviya-po-gruppam.xlsx
+++ b/yandex-direct/audit/2026-09-28-deystviya-po-gruppam.xlsx
@@ -208,10 +208,10 @@
     <t>ПЕРЕНОС В НЧ 712877525</t>
   </si>
   <si>
-    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородки] [гармошка] -заказ -зонирования -купить -межкомнатная -складные -стеклянные», минус-слова группы, объявления). В копии заменить ссылку объявлений: /peregorodki-garmoshka/ → /mezhkomnatnye-peregorodki-na-zakaz/skladnye-peregorodki-na-zakaz/ (UTM-шаблон оставить). Оригинал в СЧ - пауза (шаг 2).</t>
-  </si>
-  <si>
-    <t>Структура «группа = фраза»: спрос «гармошка» переезжает в НЧ вместе со своей группой, а не дописывается в чужую. В НЧ гармошка конвертит лучше: запросы с «гармошка» - 129 визитов / 5 лидов в НЧ против 142 / 2 в СЧ. Разница, вероятно, в посадочной: СЧ ведёт на /peregorodki-garmoshka/ (123 визита, 2 лида), НЧ «Складные | Гармошка» - на /skladnye-peregorodki-na-zakaz/ (109 визитов, 3 лида) [ГИПОТЕЗА, выборка мала]. Конфликта с НЧ 5774336420 [складные] [перегородки] [гармошка] нет: во фразе копии уже стоит -складные.</t>
+    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородки] [гармошка] -заказ -зонирования -купить -межкомнатная -складные -стеклянные», минус-слова группы, объявления). Ссылку объявлений оставить /peregorodki-garmoshka/ (страница под слово «гармошка»). В НЧ это отдельный блок «Гармошка», в «Складные» не сливать. Оригинал в СЧ - пауза (шаг 2).</t>
+  </si>
+  <si>
+    <t>Выдача Яндекса (Keys.so, топ-10): «складная перегородка» и «перегородка гармошка» - один продукт, соседние интенты: 2 общих URL и 4 общих домена, мост между ними - «стеклянная перегородка гармошка» (4-5 общих URL с обоими). Значит, это две группы, но в одной РК: сейчас один продукт куплен в двух РК с разными бюджетами. НЧ - дом механизмов, туда и переносим отдельным блоком. Посадочные: СЧ /peregorodki-garmoshka/ 123 визита / 2 лида, НЧ /skladnye.../ 109 / 3 - разница в пределах случайности, поэтому страницу не меняем, сравним 04.11. Конфликта с НЧ 5774336420 [складные] [перегородки] [гармошка] нет: во фразе копии стоит -складные.</t>
   </si>
   <si>
     <t>14.10: копия получает показы и клики, CPC ≤ 150 ₽; 04.11: лиды «гармошка» в НЧ ≥ суммы НЧ+СЧ до переноса</t>
@@ -238,7 +238,7 @@
     <t>Перегородки-гармошки | Купить</t>
   </si>
   <si>
-    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородка] [гармошка] [купить]», минус-слова группы, объявления). В копии заменить ссылку объявлений: /peregorodki-garmoshka/ → /mezhkomnatnye-peregorodki-na-zakaz/skladnye-peregorodki-na-zakaz/ (UTM-шаблон оставить). Оригинал в СЧ - пауза (шаг 2).</t>
+    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородка] [гармошка] [купить]», минус-слова группы, объявления). Ссылку объявлений оставить /peregorodki-garmoshka/ (страница под слово «гармошка»). В НЧ это отдельный блок «Гармошка», в «Складные» не сливать. Оригинал в СЧ - пауза (шаг 2).</t>
   </si>
   <si>
     <t>[перегородка] [гармошка] [купить]</t>
@@ -250,7 +250,7 @@
     <t>Перегородки-гармошки | Заказ</t>
   </si>
   <si>
-    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородки] [гармошка] [заказ]», минус-слова группы, объявления). В копии заменить ссылку объявлений: /peregorodki-garmoshka/ → /mezhkomnatnye-peregorodki-na-zakaz/skladnye-peregorodki-na-zakaz/ (UTM-шаблон оставить). Оригинал в СЧ - пауза (шаг 2).</t>
+    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородки] [гармошка] [заказ]», минус-слова группы, объявления). Ссылку объявлений оставить /peregorodki-garmoshka/ (страница под слово «гармошка»). В НЧ это отдельный блок «Гармошка», в «Складные» не сливать. Оригинал в СЧ - пауза (шаг 2).</t>
   </si>
   <si>
     <t>[перегородки] [гармошка] [заказ]</t>
@@ -274,7 +274,7 @@
     <t>Перегородки-гармошки | Межкомнатная</t>
   </si>
   <si>
-    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородка] [гармошка] [межкомнатная]», минус-слова группы, объявления). В копии заменить ссылку объявлений: /peregorodki-garmoshka/ → /mezhkomnatnye-peregorodki-na-zakaz/skladnye-peregorodki-na-zakaz/ (UTM-шаблон оставить). Оригинал в СЧ - пауза (шаг 2).</t>
+    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородка] [гармошка] [межкомнатная]», минус-слова группы, объявления). Ссылку объявлений оставить /peregorodki-garmoshka/ (страница под слово «гармошка»). В НЧ это отдельный блок «Гармошка», в «Складные» не сливать. Оригинал в СЧ - пауза (шаг 2).</t>
   </si>
   <si>
     <t>[перегородка] [гармошка] [межкомнатная]</t>
